--- a/data/movimientos.xlsx
+++ b/data/movimientos.xlsx
@@ -1,33 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User Win\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5688E59A-9D2A-473F-BB2B-C4A20ED89224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{71CC6275-5ECF-4682-9C27-B5D6599341DE}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="8505" windowHeight="7185"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -252,7 +242,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -319,7 +309,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -331,7 +321,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -378,23 +368,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -430,23 +403,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -598,7 +554,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4166BD85-A8BA-474D-A667-198E88D7D65B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -690,7 +646,7 @@
         <v>10</v>
       </c>
       <c r="L2">
-        <v>1069.7588000000001</v>
+        <v>99999</v>
       </c>
       <c r="M2">
         <v>14</v>
@@ -743,7 +699,7 @@
         <v>10</v>
       </c>
       <c r="L3">
-        <v>1069.7588000000001</v>
+        <v>99999</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -796,7 +752,7 @@
         <v>20</v>
       </c>
       <c r="L4">
-        <v>699.36659999999995</v>
+        <v>99999</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -849,7 +805,7 @@
         <v>20</v>
       </c>
       <c r="L5">
-        <v>699.36659999999995</v>
+        <v>99999</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -902,7 +858,7 @@
         <v>14</v>
       </c>
       <c r="L6">
-        <v>949.70479999999998</v>
+        <v>99999</v>
       </c>
       <c r="M6">
         <v>233</v>
@@ -955,7 +911,7 @@
         <v>14</v>
       </c>
       <c r="L7">
-        <v>949.70479999999998</v>
+        <v>99999</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -1008,7 +964,7 @@
         <v>75</v>
       </c>
       <c r="L8">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M8">
         <v>266</v>
@@ -1061,7 +1017,7 @@
         <v>75</v>
       </c>
       <c r="L9">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -1114,7 +1070,7 @@
         <v>68</v>
       </c>
       <c r="L10">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M10">
         <v>505</v>
@@ -1167,7 +1123,7 @@
         <v>68</v>
       </c>
       <c r="L11">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -1220,7 +1176,7 @@
         <v>70</v>
       </c>
       <c r="L12">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M12">
         <v>1018</v>
@@ -1273,7 +1229,7 @@
         <v>70</v>
       </c>
       <c r="L13">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -1326,7 +1282,7 @@
         <v>28</v>
       </c>
       <c r="L14">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M14">
         <v>90</v>
@@ -1379,7 +1335,7 @@
         <v>28</v>
       </c>
       <c r="L15">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -1432,7 +1388,7 @@
         <v>26</v>
       </c>
       <c r="L16">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M16">
         <v>2130</v>
@@ -1485,7 +1441,7 @@
         <v>26</v>
       </c>
       <c r="L17">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -1538,7 +1494,7 @@
         <v>25</v>
       </c>
       <c r="L18">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M18">
         <v>1221</v>
@@ -1591,7 +1547,7 @@
         <v>25</v>
       </c>
       <c r="L19">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -1644,7 +1600,7 @@
         <v>27</v>
       </c>
       <c r="L20">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M20">
         <v>675</v>
@@ -1697,7 +1653,7 @@
         <v>27</v>
       </c>
       <c r="L21">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -1750,7 +1706,7 @@
         <v>24</v>
       </c>
       <c r="L22">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M22">
         <v>566</v>
@@ -1803,7 +1759,7 @@
         <v>24</v>
       </c>
       <c r="L23">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1856,7 +1812,7 @@
         <v>29</v>
       </c>
       <c r="L24">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M24">
         <v>127</v>
@@ -1909,7 +1865,7 @@
         <v>29</v>
       </c>
       <c r="L25">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -1962,7 +1918,7 @@
         <v>30</v>
       </c>
       <c r="L26">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M26">
         <v>525</v>
@@ -2015,7 +1971,7 @@
         <v>30</v>
       </c>
       <c r="L27">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2068,7 +2024,7 @@
         <v>110</v>
       </c>
       <c r="L28">
-        <v>796.93</v>
+        <v>99999</v>
       </c>
       <c r="M28">
         <v>94</v>
@@ -2121,7 +2077,7 @@
         <v>110</v>
       </c>
       <c r="L29">
-        <v>796.93</v>
+        <v>99999</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -2174,7 +2130,7 @@
         <v>25</v>
       </c>
       <c r="L30">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M30">
         <v>63</v>
@@ -2227,7 +2183,7 @@
         <v>25</v>
       </c>
       <c r="L31">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -2280,7 +2236,7 @@
         <v>22</v>
       </c>
       <c r="L32">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M32">
         <v>150</v>
@@ -2333,7 +2289,7 @@
         <v>22</v>
       </c>
       <c r="L33">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -2386,7 +2342,7 @@
         <v>22</v>
       </c>
       <c r="L34">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M34">
         <v>44</v>
@@ -2439,7 +2395,7 @@
         <v>22</v>
       </c>
       <c r="L35">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -2492,7 +2448,7 @@
         <v>25</v>
       </c>
       <c r="L36">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M36">
         <v>51</v>
@@ -2545,7 +2501,7 @@
         <v>25</v>
       </c>
       <c r="L37">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -2598,7 +2554,7 @@
         <v>110</v>
       </c>
       <c r="L38">
-        <v>796.93</v>
+        <v>99999</v>
       </c>
       <c r="M38">
         <v>28</v>
@@ -2651,7 +2607,7 @@
         <v>110</v>
       </c>
       <c r="L39">
-        <v>796.93</v>
+        <v>99999</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -2704,7 +2660,7 @@
         <v>25</v>
       </c>
       <c r="L40">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M40">
         <v>418</v>
@@ -2757,7 +2713,7 @@
         <v>25</v>
       </c>
       <c r="L41">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -2810,7 +2766,7 @@
         <v>24</v>
       </c>
       <c r="L42">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M42">
         <v>159</v>
@@ -2863,7 +2819,7 @@
         <v>24</v>
       </c>
       <c r="L43">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -2916,7 +2872,7 @@
         <v>26</v>
       </c>
       <c r="L44">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M44">
         <v>93</v>
@@ -2969,7 +2925,7 @@
         <v>26</v>
       </c>
       <c r="L45">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M45">
         <v>0</v>
@@ -3022,7 +2978,7 @@
         <v>72</v>
       </c>
       <c r="L46">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M46">
         <v>31</v>
@@ -3075,7 +3031,7 @@
         <v>72</v>
       </c>
       <c r="L47">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M47">
         <v>0</v>

--- a/data/movimientos.xlsx
+++ b/data/movimientos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos junio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7C1694-46F0-4624-BAF5-D0F62F8B4672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C53129B-3C5A-4706-887E-F79E55FD40B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{249E1106-8FC9-4B8F-B3E8-2D248D474B09}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2843" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2853" uniqueCount="515">
   <si>
     <t>stockmov_fecha</t>
   </si>
@@ -1576,6 +1576,9 @@
   </si>
   <si>
     <t>MATARAZZO 3 VEG PENNE RIGATE 15x500</t>
+  </si>
+  <si>
+    <t>STX000100000529</t>
   </si>
 </sst>
 </file>
@@ -1928,7 +1931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB891DA9-3C1D-4D87-8AA3-023BBF7004F3}">
-  <dimension ref="A1:Q687"/>
+  <dimension ref="A1:Q689"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -2019,7 +2022,7 @@
         <v>24</v>
       </c>
       <c r="L2">
-        <v>463.5</v>
+        <v>99999</v>
       </c>
       <c r="M2">
         <v>7</v>
@@ -2072,7 +2075,7 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>99999</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -2122,7 +2125,7 @@
         <v>14</v>
       </c>
       <c r="L4">
-        <v>1803.1241</v>
+        <v>99999</v>
       </c>
       <c r="M4">
         <v>4</v>
@@ -2172,7 +2175,7 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>1065.9349</v>
+        <v>99999</v>
       </c>
       <c r="M5">
         <v>123</v>
@@ -2222,7 +2225,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>1711.1813999999999</v>
+        <v>99999</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -2272,7 +2275,7 @@
         <v>10</v>
       </c>
       <c r="L7">
-        <v>852.8</v>
+        <v>99999</v>
       </c>
       <c r="M7">
         <v>4</v>
@@ -2322,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="L8">
-        <v>5601.5420000000004</v>
+        <v>99999</v>
       </c>
       <c r="M8">
         <v>32</v>
@@ -2372,7 +2375,7 @@
         <v>20</v>
       </c>
       <c r="L9">
-        <v>893.55550000000005</v>
+        <v>99999</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -2422,7 +2425,7 @@
         <v>15</v>
       </c>
       <c r="L10">
-        <v>10992</v>
+        <v>99999</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -2472,7 +2475,7 @@
         <v>20</v>
       </c>
       <c r="L11">
-        <v>1668.2052000000001</v>
+        <v>99999</v>
       </c>
       <c r="M11">
         <v>8</v>
@@ -2522,7 +2525,7 @@
         <v>20</v>
       </c>
       <c r="L12">
-        <v>894.31859999999995</v>
+        <v>99999</v>
       </c>
       <c r="M12">
         <v>34</v>
@@ -2572,7 +2575,7 @@
         <v>15</v>
       </c>
       <c r="L13">
-        <v>888.02359999999999</v>
+        <v>99999</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -2622,7 +2625,7 @@
         <v>15</v>
       </c>
       <c r="L14">
-        <v>894.31859999999995</v>
+        <v>99999</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -2672,7 +2675,7 @@
         <v>15</v>
       </c>
       <c r="L15">
-        <v>747.81010000000003</v>
+        <v>99999</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -2722,7 +2725,7 @@
         <v>10</v>
       </c>
       <c r="L16">
-        <v>949.52</v>
+        <v>99999</v>
       </c>
       <c r="M16">
         <v>722</v>
@@ -2772,7 +2775,7 @@
         <v>56</v>
       </c>
       <c r="L17">
-        <v>1068.08</v>
+        <v>99999</v>
       </c>
       <c r="M17">
         <v>3</v>
@@ -2822,7 +2825,7 @@
         <v>24</v>
       </c>
       <c r="L18">
-        <v>1675</v>
+        <v>99999</v>
       </c>
       <c r="M18">
         <v>8</v>
@@ -2872,7 +2875,7 @@
         <v>24</v>
       </c>
       <c r="L19">
-        <v>1675</v>
+        <v>99999</v>
       </c>
       <c r="M19">
         <v>8</v>
@@ -2922,7 +2925,7 @@
         <v>168</v>
       </c>
       <c r="L20">
-        <v>573.60140000000001</v>
+        <v>99999</v>
       </c>
       <c r="M20">
         <v>11</v>
@@ -2972,7 +2975,7 @@
         <v>12</v>
       </c>
       <c r="L21">
-        <v>3229.0722999999998</v>
+        <v>99999</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -3022,7 +3025,7 @@
         <v>12</v>
       </c>
       <c r="L22">
-        <v>3229.0722999999998</v>
+        <v>99999</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -3072,7 +3075,7 @@
         <v>12</v>
       </c>
       <c r="L23">
-        <v>3229.0722999999998</v>
+        <v>99999</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -3122,7 +3125,7 @@
         <v>168</v>
       </c>
       <c r="L24">
-        <v>573.60140000000001</v>
+        <v>99999</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -3172,7 +3175,7 @@
         <v>10</v>
       </c>
       <c r="L25">
-        <v>3055</v>
+        <v>99999</v>
       </c>
       <c r="M25">
         <v>23</v>
@@ -3222,7 +3225,7 @@
         <v>10</v>
       </c>
       <c r="L26">
-        <v>3055</v>
+        <v>99999</v>
       </c>
       <c r="M26">
         <v>22</v>
@@ -3272,7 +3275,7 @@
         <v>12</v>
       </c>
       <c r="L27">
-        <v>3801.2190000000001</v>
+        <v>99999</v>
       </c>
       <c r="M27">
         <v>41</v>
@@ -3322,7 +3325,7 @@
         <v>15</v>
       </c>
       <c r="L28">
-        <v>2400.2878000000001</v>
+        <v>99999</v>
       </c>
       <c r="M28">
         <v>170</v>
@@ -3372,7 +3375,7 @@
         <v>12</v>
       </c>
       <c r="L29">
-        <v>1195.8832</v>
+        <v>99999</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -3422,7 +3425,7 @@
         <v>12</v>
       </c>
       <c r="L30">
-        <v>2551.4175</v>
+        <v>99999</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -3472,7 +3475,7 @@
         <v>12</v>
       </c>
       <c r="L31">
-        <v>1549.4155000000001</v>
+        <v>99999</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -3522,7 +3525,7 @@
         <v>12</v>
       </c>
       <c r="L32">
-        <v>2711.0832999999998</v>
+        <v>99999</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -3572,7 +3575,7 @@
         <v>12</v>
       </c>
       <c r="L33">
-        <v>5925.6410999999998</v>
+        <v>99999</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -3622,7 +3625,7 @@
         <v>12</v>
       </c>
       <c r="L34">
-        <v>1735.2118</v>
+        <v>99999</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -3672,7 +3675,7 @@
         <v>15</v>
       </c>
       <c r="L35">
-        <v>1903.0409999999999</v>
+        <v>99999</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -3722,7 +3725,7 @@
         <v>12</v>
       </c>
       <c r="L36">
-        <v>5859.3910999999998</v>
+        <v>99999</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -3772,7 +3775,7 @@
         <v>12</v>
       </c>
       <c r="L37">
-        <v>3217.2997999999998</v>
+        <v>99999</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -3822,7 +3825,7 @@
         <v>12</v>
       </c>
       <c r="L38">
-        <v>2747.2109</v>
+        <v>99999</v>
       </c>
       <c r="M38">
         <v>12</v>
@@ -3872,7 +3875,7 @@
         <v>12</v>
       </c>
       <c r="L39">
-        <v>2053.0014999999999</v>
+        <v>99999</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -3922,7 +3925,7 @@
         <v>12</v>
       </c>
       <c r="L40">
-        <v>2053.0014999999999</v>
+        <v>99999</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -3972,7 +3975,7 @@
         <v>12</v>
       </c>
       <c r="L41">
-        <v>2464.1235000000001</v>
+        <v>99999</v>
       </c>
       <c r="M41">
         <v>2</v>
@@ -4022,7 +4025,7 @@
         <v>12</v>
       </c>
       <c r="L42">
-        <v>2483.3744999999999</v>
+        <v>99999</v>
       </c>
       <c r="M42">
         <v>13</v>
@@ -4072,7 +4075,7 @@
         <v>12</v>
       </c>
       <c r="L43">
-        <v>2483.3744999999999</v>
+        <v>99999</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -4122,7 +4125,7 @@
         <v>15</v>
       </c>
       <c r="L44">
-        <v>1082.8625</v>
+        <v>99999</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -4172,7 +4175,7 @@
         <v>15</v>
       </c>
       <c r="L45">
-        <v>763.98839999999996</v>
+        <v>99999</v>
       </c>
       <c r="M45">
         <v>1</v>
@@ -4222,7 +4225,7 @@
         <v>15</v>
       </c>
       <c r="L46">
-        <v>763.98839999999996</v>
+        <v>99999</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -4272,7 +4275,7 @@
         <v>15</v>
       </c>
       <c r="L47">
-        <v>763.98839999999996</v>
+        <v>99999</v>
       </c>
       <c r="M47">
         <v>42</v>
@@ -4322,7 +4325,7 @@
         <v>15</v>
       </c>
       <c r="L48">
-        <v>894.31859999999995</v>
+        <v>99999</v>
       </c>
       <c r="M48">
         <v>27</v>
@@ -4372,7 +4375,7 @@
         <v>15</v>
       </c>
       <c r="L49">
-        <v>1303.2759000000001</v>
+        <v>99999</v>
       </c>
       <c r="M49">
         <v>39</v>
@@ -4422,7 +4425,7 @@
         <v>15</v>
       </c>
       <c r="L50">
-        <v>763.98839999999996</v>
+        <v>99999</v>
       </c>
       <c r="M50">
         <v>0</v>
@@ -4472,7 +4475,7 @@
         <v>20</v>
       </c>
       <c r="L51">
-        <v>405.6</v>
+        <v>99999</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -4522,7 +4525,7 @@
         <v>15</v>
       </c>
       <c r="L52">
-        <v>436.61219999999997</v>
+        <v>99999</v>
       </c>
       <c r="M52">
         <v>588</v>
@@ -4572,7 +4575,7 @@
         <v>15</v>
       </c>
       <c r="L53">
-        <v>594.36990000000003</v>
+        <v>99999</v>
       </c>
       <c r="M53">
         <v>18</v>
@@ -4622,7 +4625,7 @@
         <v>15</v>
       </c>
       <c r="L54">
-        <v>993.27650000000006</v>
+        <v>99999</v>
       </c>
       <c r="M54">
         <v>32</v>
@@ -4672,7 +4675,7 @@
         <v>15</v>
       </c>
       <c r="L55">
-        <v>594.36990000000003</v>
+        <v>99999</v>
       </c>
       <c r="M55">
         <v>8</v>
@@ -4722,7 +4725,7 @@
         <v>15</v>
       </c>
       <c r="L56">
-        <v>1303.2759000000001</v>
+        <v>99999</v>
       </c>
       <c r="M56">
         <v>39</v>
@@ -4772,7 +4775,7 @@
         <v>15</v>
       </c>
       <c r="L57">
-        <v>894.31859999999995</v>
+        <v>99999</v>
       </c>
       <c r="M57">
         <v>98</v>
@@ -4822,7 +4825,7 @@
         <v>15</v>
       </c>
       <c r="L58">
-        <v>894.31859999999995</v>
+        <v>99999</v>
       </c>
       <c r="M58">
         <v>94</v>
@@ -4872,7 +4875,7 @@
         <v>12</v>
       </c>
       <c r="L59">
-        <v>2483.3744999999999</v>
+        <v>99999</v>
       </c>
       <c r="M59">
         <v>0</v>
@@ -4922,7 +4925,7 @@
         <v>12</v>
       </c>
       <c r="L60">
-        <v>2483.3744999999999</v>
+        <v>99999</v>
       </c>
       <c r="M60">
         <v>0</v>
@@ -4972,7 +4975,7 @@
         <v>15</v>
       </c>
       <c r="L61">
-        <v>1082.8625</v>
+        <v>99999</v>
       </c>
       <c r="M61">
         <v>0</v>
@@ -5022,7 +5025,7 @@
         <v>20</v>
       </c>
       <c r="L62">
-        <v>491.54329999999999</v>
+        <v>99999</v>
       </c>
       <c r="M62">
         <v>1</v>
@@ -5072,7 +5075,7 @@
         <v>20</v>
       </c>
       <c r="L63">
-        <v>491.54329999999999</v>
+        <v>99999</v>
       </c>
       <c r="M63">
         <v>2</v>
@@ -5122,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="L64">
-        <v>491.54329999999999</v>
+        <v>99999</v>
       </c>
       <c r="M64">
         <v>30</v>
@@ -5172,7 +5175,7 @@
         <v>15</v>
       </c>
       <c r="L65">
-        <v>491.54329999999999</v>
+        <v>99999</v>
       </c>
       <c r="M65">
         <v>131</v>
@@ -5222,7 +5225,7 @@
         <v>15</v>
       </c>
       <c r="L66">
-        <v>491.54329999999999</v>
+        <v>99999</v>
       </c>
       <c r="M66">
         <v>0</v>
@@ -5272,7 +5275,7 @@
         <v>15</v>
       </c>
       <c r="L67">
-        <v>1083.0704000000001</v>
+        <v>99999</v>
       </c>
       <c r="M67">
         <v>86</v>
@@ -5322,7 +5325,7 @@
         <v>15</v>
       </c>
       <c r="L68">
-        <v>491.54329999999999</v>
+        <v>99999</v>
       </c>
       <c r="M68">
         <v>111</v>
@@ -5372,7 +5375,7 @@
         <v>16</v>
       </c>
       <c r="L69">
-        <v>1209.52</v>
+        <v>99999</v>
       </c>
       <c r="M69">
         <v>0</v>
@@ -5422,7 +5425,7 @@
         <v>16</v>
       </c>
       <c r="L70">
-        <v>1209.52</v>
+        <v>99999</v>
       </c>
       <c r="M70">
         <v>0</v>
@@ -5472,7 +5475,7 @@
         <v>15</v>
       </c>
       <c r="L71">
-        <v>763.98839999999996</v>
+        <v>99999</v>
       </c>
       <c r="M71">
         <v>75</v>
@@ -5522,7 +5525,7 @@
         <v>15</v>
       </c>
       <c r="L72">
-        <v>1519.8955000000001</v>
+        <v>99999</v>
       </c>
       <c r="M72">
         <v>5</v>
@@ -5572,7 +5575,7 @@
         <v>20</v>
       </c>
       <c r="L73">
-        <v>1193.5631000000001</v>
+        <v>99999</v>
       </c>
       <c r="M73">
         <v>57</v>
@@ -5622,7 +5625,7 @@
         <v>20</v>
       </c>
       <c r="L74">
-        <v>1668.2049999999999</v>
+        <v>99999</v>
       </c>
       <c r="M74">
         <v>0</v>
@@ -5672,7 +5675,7 @@
         <v>15</v>
       </c>
       <c r="L75">
-        <v>1193.5631000000001</v>
+        <v>99999</v>
       </c>
       <c r="M75">
         <v>13</v>
@@ -5722,7 +5725,7 @@
         <v>15</v>
       </c>
       <c r="L76">
-        <v>594.36990000000003</v>
+        <v>99999</v>
       </c>
       <c r="M76">
         <v>29</v>
@@ -5772,7 +5775,7 @@
         <v>15</v>
       </c>
       <c r="L77">
-        <v>1033.6348</v>
+        <v>99999</v>
       </c>
       <c r="M77">
         <v>161</v>
@@ -5822,7 +5825,7 @@
         <v>15</v>
       </c>
       <c r="L78">
-        <v>970.54899999999998</v>
+        <v>99999</v>
       </c>
       <c r="M78">
         <v>15</v>
@@ -5872,7 +5875,7 @@
         <v>20</v>
       </c>
       <c r="L79">
-        <v>970.54899999999998</v>
+        <v>99999</v>
       </c>
       <c r="M79">
         <v>0</v>
@@ -5922,7 +5925,7 @@
         <v>12</v>
       </c>
       <c r="L80">
-        <v>1847.7345</v>
+        <v>99999</v>
       </c>
       <c r="M80">
         <v>2</v>
@@ -5972,7 +5975,7 @@
         <v>12</v>
       </c>
       <c r="L81">
-        <v>1847.7345</v>
+        <v>99999</v>
       </c>
       <c r="M81">
         <v>0</v>
@@ -6022,7 +6025,7 @@
         <v>20</v>
       </c>
       <c r="L82">
-        <v>1847.7345</v>
+        <v>99999</v>
       </c>
       <c r="M82">
         <v>1</v>
@@ -6072,7 +6075,7 @@
         <v>15</v>
       </c>
       <c r="L83">
-        <v>763.98839999999996</v>
+        <v>99999</v>
       </c>
       <c r="M83">
         <v>15</v>
@@ -6122,7 +6125,7 @@
         <v>15</v>
       </c>
       <c r="L84">
-        <v>983.65840000000003</v>
+        <v>99999</v>
       </c>
       <c r="M84">
         <v>0</v>
@@ -6172,7 +6175,7 @@
         <v>20</v>
       </c>
       <c r="L85">
-        <v>763.98839999999996</v>
+        <v>99999</v>
       </c>
       <c r="M85">
         <v>13</v>
@@ -6222,7 +6225,7 @@
         <v>15</v>
       </c>
       <c r="L86">
-        <v>763.98839999999996</v>
+        <v>99999</v>
       </c>
       <c r="M86">
         <v>1</v>
@@ -6272,7 +6275,7 @@
         <v>15</v>
       </c>
       <c r="L87">
-        <v>894.31859999999995</v>
+        <v>99999</v>
       </c>
       <c r="M87">
         <v>22</v>
@@ -6322,7 +6325,7 @@
         <v>15</v>
       </c>
       <c r="L88">
-        <v>894.31859999999995</v>
+        <v>99999</v>
       </c>
       <c r="M88">
         <v>124</v>
@@ -6372,7 +6375,7 @@
         <v>20</v>
       </c>
       <c r="L89">
-        <v>894.31859999999995</v>
+        <v>99999</v>
       </c>
       <c r="M89">
         <v>175</v>
@@ -6422,7 +6425,7 @@
         <v>20</v>
       </c>
       <c r="L90">
-        <v>894.31859999999995</v>
+        <v>99999</v>
       </c>
       <c r="M90">
         <v>9</v>
@@ -6472,7 +6475,7 @@
         <v>20</v>
       </c>
       <c r="L91">
-        <v>894.31859999999995</v>
+        <v>99999</v>
       </c>
       <c r="M91">
         <v>82</v>
@@ -6522,7 +6525,7 @@
         <v>15</v>
       </c>
       <c r="L92">
-        <v>763.98839999999996</v>
+        <v>99999</v>
       </c>
       <c r="M92">
         <v>0</v>
@@ -6572,7 +6575,7 @@
         <v>20</v>
       </c>
       <c r="L93">
-        <v>763.98839999999996</v>
+        <v>99999</v>
       </c>
       <c r="M93">
         <v>138</v>
@@ -6622,7 +6625,7 @@
         <v>20</v>
       </c>
       <c r="L94">
-        <v>763.98839999999996</v>
+        <v>99999</v>
       </c>
       <c r="M94">
         <v>125</v>
@@ -6672,7 +6675,7 @@
         <v>15</v>
       </c>
       <c r="L95">
-        <v>594.36990000000003</v>
+        <v>99999</v>
       </c>
       <c r="M95">
         <v>42</v>
@@ -6722,7 +6725,7 @@
         <v>15</v>
       </c>
       <c r="L96">
-        <v>594.36990000000003</v>
+        <v>99999</v>
       </c>
       <c r="M96">
         <v>19</v>
@@ -6775,7 +6778,7 @@
         <v>15</v>
       </c>
       <c r="L97">
-        <v>594.36990000000003</v>
+        <v>99999</v>
       </c>
       <c r="M97">
         <v>0</v>
@@ -6828,7 +6831,7 @@
         <v>15</v>
       </c>
       <c r="L98">
-        <v>594.36990000000003</v>
+        <v>99999</v>
       </c>
       <c r="M98">
         <v>0</v>
@@ -6878,7 +6881,7 @@
         <v>20</v>
       </c>
       <c r="L99">
-        <v>594.36990000000003</v>
+        <v>99999</v>
       </c>
       <c r="M99">
         <v>89</v>
@@ -6928,7 +6931,7 @@
         <v>20</v>
       </c>
       <c r="L100">
-        <v>594.36990000000003</v>
+        <v>99999</v>
       </c>
       <c r="M100">
         <v>14</v>
@@ -6978,7 +6981,7 @@
         <v>15</v>
       </c>
       <c r="L101">
-        <v>714.24639999999999</v>
+        <v>99999</v>
       </c>
       <c r="M101">
         <v>100</v>
@@ -7028,7 +7031,7 @@
         <v>20</v>
       </c>
       <c r="L102">
-        <v>1668.2052000000001</v>
+        <v>99999</v>
       </c>
       <c r="M102">
         <v>5</v>
@@ -7078,7 +7081,7 @@
         <v>20</v>
       </c>
       <c r="L103">
-        <v>1668.2052000000001</v>
+        <v>99999</v>
       </c>
       <c r="M103">
         <v>1</v>
@@ -7128,7 +7131,7 @@
         <v>20</v>
       </c>
       <c r="L104">
-        <v>1668.2052000000001</v>
+        <v>99999</v>
       </c>
       <c r="M104">
         <v>0</v>
@@ -7178,7 +7181,7 @@
         <v>12</v>
       </c>
       <c r="L105">
-        <v>2119.0708</v>
+        <v>99999</v>
       </c>
       <c r="M105">
         <v>0</v>
@@ -7228,7 +7231,7 @@
         <v>20</v>
       </c>
       <c r="L106">
-        <v>1937.1711</v>
+        <v>99999</v>
       </c>
       <c r="M106">
         <v>0</v>
@@ -7278,7 +7281,7 @@
         <v>15</v>
       </c>
       <c r="L107">
-        <v>1519.8955000000001</v>
+        <v>99999</v>
       </c>
       <c r="M107">
         <v>12</v>
@@ -7328,7 +7331,7 @@
         <v>20</v>
       </c>
       <c r="L108">
-        <v>1519.8955000000001</v>
+        <v>99999</v>
       </c>
       <c r="M108">
         <v>10</v>
@@ -7378,7 +7381,7 @@
         <v>18</v>
       </c>
       <c r="L109">
-        <v>1519.8955000000001</v>
+        <v>99999</v>
       </c>
       <c r="M109">
         <v>15</v>
@@ -7428,7 +7431,7 @@
         <v>20</v>
       </c>
       <c r="L110">
-        <v>1519.8955000000001</v>
+        <v>99999</v>
       </c>
       <c r="M110">
         <v>0</v>
@@ -7478,7 +7481,7 @@
         <v>15</v>
       </c>
       <c r="L111">
-        <v>1625.52</v>
+        <v>99999</v>
       </c>
       <c r="M111">
         <v>55</v>
@@ -7528,7 +7531,7 @@
         <v>6</v>
       </c>
       <c r="L112">
-        <v>1657.9138</v>
+        <v>99999</v>
       </c>
       <c r="M112">
         <v>0</v>
@@ -7578,7 +7581,7 @@
         <v>6</v>
       </c>
       <c r="L113">
-        <v>917.55</v>
+        <v>99999</v>
       </c>
       <c r="M113">
         <v>0</v>
@@ -7628,7 +7631,7 @@
         <v>6</v>
       </c>
       <c r="L114">
-        <v>1107.335</v>
+        <v>99999</v>
       </c>
       <c r="M114">
         <v>0</v>
@@ -7678,7 +7681,7 @@
         <v>6</v>
       </c>
       <c r="L115">
-        <v>1107.335</v>
+        <v>99999</v>
       </c>
       <c r="M115">
         <v>0</v>
@@ -7728,7 +7731,7 @@
         <v>28</v>
       </c>
       <c r="L116">
-        <v>1033.6348</v>
+        <v>99999</v>
       </c>
       <c r="M116">
         <v>0</v>
@@ -7778,7 +7781,7 @@
         <v>20</v>
       </c>
       <c r="L117">
-        <v>1572.9222</v>
+        <v>99999</v>
       </c>
       <c r="M117">
         <v>0</v>
@@ -7828,7 +7831,7 @@
         <v>15</v>
       </c>
       <c r="L118">
-        <v>972.64300000000003</v>
+        <v>99999</v>
       </c>
       <c r="M118">
         <v>124</v>
@@ -7878,7 +7881,7 @@
         <v>15</v>
       </c>
       <c r="L119">
-        <v>972.64300000000003</v>
+        <v>99999</v>
       </c>
       <c r="M119">
         <v>109</v>
@@ -7928,7 +7931,7 @@
         <v>20</v>
       </c>
       <c r="L120">
-        <v>972.64300000000003</v>
+        <v>99999</v>
       </c>
       <c r="M120">
         <v>0</v>
@@ -7978,7 +7981,7 @@
         <v>20</v>
       </c>
       <c r="L121">
-        <v>1937.1711</v>
+        <v>99999</v>
       </c>
       <c r="M121">
         <v>9</v>
@@ -8028,7 +8031,7 @@
         <v>15</v>
       </c>
       <c r="L122">
-        <v>1668.2052000000001</v>
+        <v>99999</v>
       </c>
       <c r="M122">
         <v>0</v>
@@ -8078,7 +8081,7 @@
         <v>15</v>
       </c>
       <c r="L123">
-        <v>1303.2759000000001</v>
+        <v>99999</v>
       </c>
       <c r="M123">
         <v>213</v>
@@ -8128,7 +8131,7 @@
         <v>1</v>
       </c>
       <c r="L124">
-        <v>8092.7587999999996</v>
+        <v>99999</v>
       </c>
       <c r="M124">
         <v>0</v>
@@ -8178,7 +8181,7 @@
         <v>10</v>
       </c>
       <c r="L125">
-        <v>1324.4821999999999</v>
+        <v>99999</v>
       </c>
       <c r="M125">
         <v>15</v>
@@ -8228,7 +8231,7 @@
         <v>10</v>
       </c>
       <c r="L126">
-        <v>504.4</v>
+        <v>99999</v>
       </c>
       <c r="M126">
         <v>0</v>
@@ -8278,7 +8281,7 @@
         <v>10</v>
       </c>
       <c r="L127">
-        <v>447.92469999999997</v>
+        <v>99999</v>
       </c>
       <c r="M127">
         <v>6</v>
@@ -8328,7 +8331,7 @@
         <v>90</v>
       </c>
       <c r="L128">
-        <v>532.93470000000002</v>
+        <v>99999</v>
       </c>
       <c r="M128">
         <v>0</v>
@@ -8378,7 +8381,7 @@
         <v>90</v>
       </c>
       <c r="L129">
-        <v>532.93470000000002</v>
+        <v>99999</v>
       </c>
       <c r="M129">
         <v>0</v>
@@ -8428,7 +8431,7 @@
         <v>228</v>
       </c>
       <c r="L130">
-        <v>477.66879999999998</v>
+        <v>99999</v>
       </c>
       <c r="M130">
         <v>0</v>
@@ -8478,7 +8481,7 @@
         <v>6</v>
       </c>
       <c r="L131">
-        <v>2848</v>
+        <v>99999</v>
       </c>
       <c r="M131">
         <v>8</v>
@@ -8528,7 +8531,7 @@
         <v>228</v>
       </c>
       <c r="L132">
-        <v>462.8</v>
+        <v>99999</v>
       </c>
       <c r="M132">
         <v>0</v>
@@ -8578,7 +8581,7 @@
         <v>168</v>
       </c>
       <c r="L133">
-        <v>462.8</v>
+        <v>99999</v>
       </c>
       <c r="M133">
         <v>0</v>
@@ -8628,7 +8631,7 @@
         <v>56</v>
       </c>
       <c r="L134">
-        <v>1156.6555000000001</v>
+        <v>99999</v>
       </c>
       <c r="M134">
         <v>0</v>
@@ -8678,7 +8681,7 @@
         <v>12</v>
       </c>
       <c r="L135">
-        <v>880.72410000000002</v>
+        <v>99999</v>
       </c>
       <c r="M135">
         <v>0</v>
@@ -8728,7 +8731,7 @@
         <v>12</v>
       </c>
       <c r="L136">
-        <v>1018.2015</v>
+        <v>99999</v>
       </c>
       <c r="M136">
         <v>6</v>
@@ -8778,7 +8781,7 @@
         <v>56</v>
       </c>
       <c r="L137">
-        <v>1156.6555000000001</v>
+        <v>99999</v>
       </c>
       <c r="M137">
         <v>9</v>
@@ -8828,7 +8831,7 @@
         <v>12</v>
       </c>
       <c r="L138">
-        <v>1667.0017</v>
+        <v>99999</v>
       </c>
       <c r="M138">
         <v>0</v>
@@ -8878,7 +8881,7 @@
         <v>72</v>
       </c>
       <c r="L139">
-        <v>710.83169999999996</v>
+        <v>99999</v>
       </c>
       <c r="M139">
         <v>0</v>
@@ -8928,7 +8931,7 @@
         <v>72</v>
       </c>
       <c r="L140">
-        <v>533.64580000000001</v>
+        <v>99999</v>
       </c>
       <c r="M140">
         <v>0</v>
@@ -8978,7 +8981,7 @@
         <v>72</v>
       </c>
       <c r="L141">
-        <v>533.64580000000001</v>
+        <v>99999</v>
       </c>
       <c r="M141">
         <v>0</v>
@@ -9028,7 +9031,7 @@
         <v>72</v>
       </c>
       <c r="L142">
-        <v>710.76620000000003</v>
+        <v>99999</v>
       </c>
       <c r="M142">
         <v>0</v>
@@ -9078,7 +9081,7 @@
         <v>72</v>
       </c>
       <c r="L143">
-        <v>533.59690000000001</v>
+        <v>99999</v>
       </c>
       <c r="M143">
         <v>0</v>
@@ -9128,7 +9131,7 @@
         <v>168</v>
       </c>
       <c r="L144">
-        <v>442.6968</v>
+        <v>99999</v>
       </c>
       <c r="M144">
         <v>0</v>
@@ -9178,7 +9181,7 @@
         <v>168</v>
       </c>
       <c r="L145">
-        <v>442.6968</v>
+        <v>99999</v>
       </c>
       <c r="M145">
         <v>0</v>
@@ -9228,7 +9231,7 @@
         <v>168</v>
       </c>
       <c r="L146">
-        <v>442.6968</v>
+        <v>99999</v>
       </c>
       <c r="M146">
         <v>0</v>
@@ -9278,7 +9281,7 @@
         <v>168</v>
       </c>
       <c r="L147">
-        <v>442.6968</v>
+        <v>99999</v>
       </c>
       <c r="M147">
         <v>2</v>
@@ -9328,7 +9331,7 @@
         <v>48</v>
       </c>
       <c r="L148">
-        <v>974.98760000000004</v>
+        <v>99999</v>
       </c>
       <c r="M148">
         <v>1</v>
@@ -9381,7 +9384,7 @@
         <v>48</v>
       </c>
       <c r="L149">
-        <v>974.98760000000004</v>
+        <v>99999</v>
       </c>
       <c r="M149">
         <v>0</v>
@@ -9434,7 +9437,7 @@
         <v>48</v>
       </c>
       <c r="L150">
-        <v>974.98760000000004</v>
+        <v>99999</v>
       </c>
       <c r="M150">
         <v>0</v>
@@ -9484,7 +9487,7 @@
         <v>60</v>
       </c>
       <c r="L151">
-        <v>570.44650000000001</v>
+        <v>99999</v>
       </c>
       <c r="M151">
         <v>0</v>
@@ -9534,7 +9537,7 @@
         <v>56</v>
       </c>
       <c r="L152">
-        <v>1026.2520999999999</v>
+        <v>99999</v>
       </c>
       <c r="M152">
         <v>0</v>
@@ -9584,7 +9587,7 @@
         <v>60</v>
       </c>
       <c r="L153">
-        <v>1026.2520999999999</v>
+        <v>99999</v>
       </c>
       <c r="M153">
         <v>0</v>
@@ -9634,7 +9637,7 @@
         <v>60</v>
       </c>
       <c r="L154">
-        <v>570.44650000000001</v>
+        <v>99999</v>
       </c>
       <c r="M154">
         <v>0</v>
@@ -9684,7 +9687,7 @@
         <v>56</v>
       </c>
       <c r="L155">
-        <v>1026.2520999999999</v>
+        <v>99999</v>
       </c>
       <c r="M155">
         <v>1</v>
@@ -9734,7 +9737,7 @@
         <v>228</v>
       </c>
       <c r="L156">
-        <v>441.95</v>
+        <v>99999</v>
       </c>
       <c r="M156">
         <v>1</v>
@@ -9787,7 +9790,7 @@
         <v>228</v>
       </c>
       <c r="L157">
-        <v>441.95</v>
+        <v>99999</v>
       </c>
       <c r="M157">
         <v>0</v>
@@ -9840,7 +9843,7 @@
         <v>228</v>
       </c>
       <c r="L158">
-        <v>441.95</v>
+        <v>99999</v>
       </c>
       <c r="M158">
         <v>0</v>
@@ -9890,7 +9893,7 @@
         <v>12</v>
       </c>
       <c r="L159">
-        <v>1357.2</v>
+        <v>99999</v>
       </c>
       <c r="M159">
         <v>0</v>
@@ -9940,7 +9943,7 @@
         <v>12</v>
       </c>
       <c r="L160">
-        <v>1357.2</v>
+        <v>99999</v>
       </c>
       <c r="M160">
         <v>0</v>
@@ -9990,7 +9993,7 @@
         <v>90</v>
       </c>
       <c r="L161">
-        <v>705.33109999999999</v>
+        <v>99999</v>
       </c>
       <c r="M161">
         <v>11</v>
@@ -10040,7 +10043,7 @@
         <v>90</v>
       </c>
       <c r="L162">
-        <v>705.32449999999994</v>
+        <v>99999</v>
       </c>
       <c r="M162">
         <v>29</v>
@@ -10090,7 +10093,7 @@
         <v>90</v>
       </c>
       <c r="L163">
-        <v>705.32449999999994</v>
+        <v>99999</v>
       </c>
       <c r="M163">
         <v>0</v>
@@ -10140,7 +10143,7 @@
         <v>90</v>
       </c>
       <c r="L164">
-        <v>705.32449999999994</v>
+        <v>99999</v>
       </c>
       <c r="M164">
         <v>10</v>
@@ -10190,7 +10193,7 @@
         <v>10</v>
       </c>
       <c r="L165">
-        <v>1295.9346</v>
+        <v>99999</v>
       </c>
       <c r="M165">
         <v>0</v>
@@ -10240,7 +10243,7 @@
         <v>10</v>
       </c>
       <c r="L166">
-        <v>891.09159999999997</v>
+        <v>99999</v>
       </c>
       <c r="M166">
         <v>0</v>
@@ -10290,7 +10293,7 @@
         <v>10</v>
       </c>
       <c r="L167">
-        <v>1187.4241999999999</v>
+        <v>99999</v>
       </c>
       <c r="M167">
         <v>22</v>
@@ -10340,7 +10343,7 @@
         <v>10</v>
       </c>
       <c r="L168">
-        <v>626.00819999999999</v>
+        <v>99999</v>
       </c>
       <c r="M168">
         <v>14</v>
@@ -10390,7 +10393,7 @@
         <v>10</v>
       </c>
       <c r="L169">
-        <v>984.25419999999997</v>
+        <v>99999</v>
       </c>
       <c r="M169">
         <v>25</v>
@@ -10440,7 +10443,7 @@
         <v>10</v>
       </c>
       <c r="L170">
-        <v>509.31479999999999</v>
+        <v>99999</v>
       </c>
       <c r="M170">
         <v>22</v>
@@ -10490,7 +10493,7 @@
         <v>10</v>
       </c>
       <c r="L171">
-        <v>1070.9425000000001</v>
+        <v>99999</v>
       </c>
       <c r="M171">
         <v>67</v>
@@ -10540,7 +10543,7 @@
         <v>10</v>
       </c>
       <c r="L172">
-        <v>564.85389999999995</v>
+        <v>99999</v>
       </c>
       <c r="M172">
         <v>0</v>
@@ -10590,7 +10593,7 @@
         <v>10</v>
       </c>
       <c r="L173">
-        <v>1977.3168000000001</v>
+        <v>99999</v>
       </c>
       <c r="M173">
         <v>8</v>
@@ -10640,7 +10643,7 @@
         <v>10</v>
       </c>
       <c r="L174">
-        <v>1402.96</v>
+        <v>99999</v>
       </c>
       <c r="M174">
         <v>1</v>
@@ -10690,7 +10693,7 @@
         <v>10</v>
       </c>
       <c r="L175">
-        <v>1402.96</v>
+        <v>99999</v>
       </c>
       <c r="M175">
         <v>0</v>
@@ -10740,7 +10743,7 @@
         <v>10</v>
       </c>
       <c r="L176">
-        <v>660.07539999999995</v>
+        <v>99999</v>
       </c>
       <c r="M176">
         <v>0</v>
@@ -10790,7 +10793,7 @@
         <v>10</v>
       </c>
       <c r="L177">
-        <v>1818.5301999999999</v>
+        <v>99999</v>
       </c>
       <c r="M177">
         <v>0</v>
@@ -10840,7 +10843,7 @@
         <v>1</v>
       </c>
       <c r="L178">
-        <v>4480.3198000000002</v>
+        <v>99999</v>
       </c>
       <c r="M178">
         <v>0</v>
@@ -10890,7 +10893,7 @@
         <v>10</v>
       </c>
       <c r="L179">
-        <v>1692.0355</v>
+        <v>99999</v>
       </c>
       <c r="M179">
         <v>0</v>
@@ -10940,7 +10943,7 @@
         <v>10</v>
       </c>
       <c r="L180">
-        <v>1692.8009</v>
+        <v>99999</v>
       </c>
       <c r="M180">
         <v>8</v>
@@ -10990,7 +10993,7 @@
         <v>10</v>
       </c>
       <c r="L181">
-        <v>1692.0355</v>
+        <v>99999</v>
       </c>
       <c r="M181">
         <v>0</v>
@@ -11040,7 +11043,7 @@
         <v>56</v>
       </c>
       <c r="L182">
-        <v>1202.24</v>
+        <v>99999</v>
       </c>
       <c r="M182">
         <v>0</v>
@@ -11090,7 +11093,7 @@
         <v>228</v>
       </c>
       <c r="L183">
-        <v>441.9511</v>
+        <v>99999</v>
       </c>
       <c r="M183">
         <v>0</v>
@@ -11140,7 +11143,7 @@
         <v>228</v>
       </c>
       <c r="L184">
-        <v>442.4117</v>
+        <v>99999</v>
       </c>
       <c r="M184">
         <v>0</v>
@@ -11190,7 +11193,7 @@
         <v>12</v>
       </c>
       <c r="L185">
-        <v>1112.1605</v>
+        <v>99999</v>
       </c>
       <c r="M185">
         <v>10</v>
@@ -11240,7 +11243,7 @@
         <v>12</v>
       </c>
       <c r="L186">
-        <v>1112.1605</v>
+        <v>99999</v>
       </c>
       <c r="M186">
         <v>0</v>
@@ -11290,7 +11293,7 @@
         <v>12</v>
       </c>
       <c r="L187">
-        <v>1112.1605</v>
+        <v>99999</v>
       </c>
       <c r="M187">
         <v>6</v>
@@ -11340,7 +11343,7 @@
         <v>12</v>
       </c>
       <c r="L188">
-        <v>1112</v>
+        <v>99999</v>
       </c>
       <c r="M188">
         <v>0</v>
@@ -11390,7 +11393,7 @@
         <v>12</v>
       </c>
       <c r="L189">
-        <v>1156.48</v>
+        <v>99999</v>
       </c>
       <c r="M189">
         <v>0</v>
@@ -11440,7 +11443,7 @@
         <v>90</v>
       </c>
       <c r="L190">
-        <v>530.4</v>
+        <v>99999</v>
       </c>
       <c r="M190">
         <v>0</v>
@@ -11490,7 +11493,7 @@
         <v>90</v>
       </c>
       <c r="L191">
-        <v>553.80690000000004</v>
+        <v>99999</v>
       </c>
       <c r="M191">
         <v>7</v>
@@ -11540,7 +11543,7 @@
         <v>90</v>
       </c>
       <c r="L192">
-        <v>509.35419999999999</v>
+        <v>99999</v>
       </c>
       <c r="M192">
         <v>11</v>
@@ -11590,7 +11593,7 @@
         <v>90</v>
       </c>
       <c r="L193">
-        <v>530.4</v>
+        <v>99999</v>
       </c>
       <c r="M193">
         <v>1</v>
@@ -11640,7 +11643,7 @@
         <v>90</v>
       </c>
       <c r="L194">
-        <v>532.50670000000002</v>
+        <v>99999</v>
       </c>
       <c r="M194">
         <v>2</v>
@@ -11690,7 +11693,7 @@
         <v>90</v>
       </c>
       <c r="L195">
-        <v>553.80690000000004</v>
+        <v>99999</v>
       </c>
       <c r="M195">
         <v>1</v>
@@ -11740,7 +11743,7 @@
         <v>90</v>
       </c>
       <c r="L196">
-        <v>509.35419999999999</v>
+        <v>99999</v>
       </c>
       <c r="M196">
         <v>0</v>
@@ -11790,7 +11793,7 @@
         <v>90</v>
       </c>
       <c r="L197">
-        <v>532.50670000000002</v>
+        <v>99999</v>
       </c>
       <c r="M197">
         <v>1</v>
@@ -11840,7 +11843,7 @@
         <v>12</v>
       </c>
       <c r="L198">
-        <v>2180.6039999999998</v>
+        <v>99999</v>
       </c>
       <c r="M198">
         <v>0</v>
@@ -11890,7 +11893,7 @@
         <v>10</v>
       </c>
       <c r="L199">
-        <v>3187.4625999999998</v>
+        <v>99999</v>
       </c>
       <c r="M199">
         <v>0</v>
@@ -11940,7 +11943,7 @@
         <v>12</v>
       </c>
       <c r="L200">
-        <v>2174.7143999999998</v>
+        <v>99999</v>
       </c>
       <c r="M200">
         <v>0</v>
@@ -11990,7 +11993,7 @@
         <v>12</v>
       </c>
       <c r="L201">
-        <v>2284.3699000000001</v>
+        <v>99999</v>
       </c>
       <c r="M201">
         <v>0</v>
@@ -12040,7 +12043,7 @@
         <v>12</v>
       </c>
       <c r="L202">
-        <v>1602.8861999999999</v>
+        <v>99999</v>
       </c>
       <c r="M202">
         <v>0</v>
@@ -12090,7 +12093,7 @@
         <v>12</v>
       </c>
       <c r="L203">
-        <v>1946.3997999999999</v>
+        <v>99999</v>
       </c>
       <c r="M203">
         <v>1</v>
@@ -12140,7 +12143,7 @@
         <v>12</v>
       </c>
       <c r="L204">
-        <v>1602.8861999999999</v>
+        <v>99999</v>
       </c>
       <c r="M204">
         <v>14</v>
@@ -12190,7 +12193,7 @@
         <v>12</v>
       </c>
       <c r="L205">
-        <v>1602.8861999999999</v>
+        <v>99999</v>
       </c>
       <c r="M205">
         <v>0</v>
@@ -12240,7 +12243,7 @@
         <v>12</v>
       </c>
       <c r="L206">
-        <v>1602.8861999999999</v>
+        <v>99999</v>
       </c>
       <c r="M206">
         <v>11</v>
@@ -12290,7 +12293,7 @@
         <v>18</v>
       </c>
       <c r="L207">
-        <v>805.7319</v>
+        <v>99999</v>
       </c>
       <c r="M207">
         <v>0</v>
@@ -12340,7 +12343,7 @@
         <v>12</v>
       </c>
       <c r="L208">
-        <v>1400.6261</v>
+        <v>99999</v>
       </c>
       <c r="M208">
         <v>0</v>
@@ -12390,7 +12393,7 @@
         <v>10</v>
       </c>
       <c r="L209">
-        <v>1336.4</v>
+        <v>99999</v>
       </c>
       <c r="M209">
         <v>13</v>
@@ -12440,7 +12443,7 @@
         <v>10</v>
       </c>
       <c r="L210">
-        <v>1608.5582999999999</v>
+        <v>99999</v>
       </c>
       <c r="M210">
         <v>0</v>
@@ -12490,7 +12493,7 @@
         <v>10</v>
       </c>
       <c r="L211">
-        <v>682.47850000000005</v>
+        <v>99999</v>
       </c>
       <c r="M211">
         <v>48</v>
@@ -12540,7 +12543,7 @@
         <v>10</v>
       </c>
       <c r="L212">
-        <v>574.02930000000003</v>
+        <v>99999</v>
       </c>
       <c r="M212">
         <v>0</v>
@@ -12590,7 +12593,7 @@
         <v>20</v>
       </c>
       <c r="L213">
-        <v>904.64790000000005</v>
+        <v>99999</v>
       </c>
       <c r="M213">
         <v>0</v>
@@ -12640,7 +12643,7 @@
         <v>20</v>
       </c>
       <c r="L214">
-        <v>904.64790000000005</v>
+        <v>99999</v>
       </c>
       <c r="M214">
         <v>28</v>
@@ -12690,7 +12693,7 @@
         <v>1</v>
       </c>
       <c r="L215">
-        <v>8195.8446999999996</v>
+        <v>99999</v>
       </c>
       <c r="M215">
         <v>6</v>
@@ -12740,7 +12743,7 @@
         <v>20</v>
       </c>
       <c r="L216">
-        <v>1035.4226000000001</v>
+        <v>99999</v>
       </c>
       <c r="M216">
         <v>6</v>
@@ -12790,7 +12793,7 @@
         <v>20</v>
       </c>
       <c r="L217">
-        <v>1035.4226000000001</v>
+        <v>99999</v>
       </c>
       <c r="M217">
         <v>2</v>
@@ -12840,7 +12843,7 @@
         <v>20</v>
       </c>
       <c r="L218">
-        <v>1363.3378</v>
+        <v>99999</v>
       </c>
       <c r="M218">
         <v>1</v>
@@ -12890,7 +12893,7 @@
         <v>9</v>
       </c>
       <c r="L219">
-        <v>2550.7656000000002</v>
+        <v>99999</v>
       </c>
       <c r="M219">
         <v>0</v>
@@ -12940,7 +12943,7 @@
         <v>20</v>
       </c>
       <c r="L220">
-        <v>705.21709999999996</v>
+        <v>99999</v>
       </c>
       <c r="M220">
         <v>0</v>
@@ -12990,7 +12993,7 @@
         <v>20</v>
       </c>
       <c r="L221">
-        <v>710</v>
+        <v>99999</v>
       </c>
       <c r="M221">
         <v>0</v>
@@ -13040,7 +13043,7 @@
         <v>9</v>
       </c>
       <c r="L222">
-        <v>1412</v>
+        <v>99999</v>
       </c>
       <c r="M222">
         <v>0</v>
@@ -13090,7 +13093,7 @@
         <v>20</v>
       </c>
       <c r="L223">
-        <v>562.85619999999994</v>
+        <v>99999</v>
       </c>
       <c r="M223">
         <v>0</v>
@@ -13140,7 +13143,7 @@
         <v>6</v>
       </c>
       <c r="L224">
-        <v>2389.1260000000002</v>
+        <v>99999</v>
       </c>
       <c r="M224">
         <v>227</v>
@@ -13190,7 +13193,7 @@
         <v>10</v>
       </c>
       <c r="L225">
-        <v>1004.0559</v>
+        <v>99999</v>
       </c>
       <c r="M225">
         <v>642</v>
@@ -13240,7 +13243,7 @@
         <v>12</v>
       </c>
       <c r="L226">
-        <v>1281.3013000000001</v>
+        <v>99999</v>
       </c>
       <c r="M226">
         <v>8</v>
@@ -13290,7 +13293,7 @@
         <v>12</v>
       </c>
       <c r="L227">
-        <v>2400.5156000000002</v>
+        <v>99999</v>
       </c>
       <c r="M227">
         <v>12</v>
@@ -13340,7 +13343,7 @@
         <v>12</v>
       </c>
       <c r="L228">
-        <v>791.29020000000003</v>
+        <v>99999</v>
       </c>
       <c r="M228">
         <v>25</v>
@@ -13390,7 +13393,7 @@
         <v>10</v>
       </c>
       <c r="L229">
-        <v>1252.066</v>
+        <v>99999</v>
       </c>
       <c r="M229">
         <v>706</v>
@@ -13440,7 +13443,7 @@
         <v>12</v>
       </c>
       <c r="L230">
-        <v>998.4</v>
+        <v>99999</v>
       </c>
       <c r="M230">
         <v>0</v>
@@ -13490,7 +13493,7 @@
         <v>12</v>
       </c>
       <c r="L231">
-        <v>1510</v>
+        <v>99999</v>
       </c>
       <c r="M231">
         <v>0</v>
@@ -13540,7 +13543,7 @@
         <v>12</v>
       </c>
       <c r="L232">
-        <v>1837.6528000000001</v>
+        <v>99999</v>
       </c>
       <c r="M232">
         <v>0</v>
@@ -13590,7 +13593,7 @@
         <v>10</v>
       </c>
       <c r="L233">
-        <v>1124.4902</v>
+        <v>99999</v>
       </c>
       <c r="M233">
         <v>0</v>
@@ -13640,7 +13643,7 @@
         <v>8</v>
       </c>
       <c r="L234">
-        <v>1148.402</v>
+        <v>99999</v>
       </c>
       <c r="M234">
         <v>0</v>
@@ -13690,7 +13693,7 @@
         <v>10</v>
       </c>
       <c r="L235">
-        <v>565.19069999999999</v>
+        <v>99999</v>
       </c>
       <c r="M235">
         <v>18</v>
@@ -13740,7 +13743,7 @@
         <v>10</v>
       </c>
       <c r="L236">
-        <v>1069.7588000000001</v>
+        <v>99999</v>
       </c>
       <c r="M236">
         <v>14</v>
@@ -13793,7 +13796,7 @@
         <v>10</v>
       </c>
       <c r="L237">
-        <v>1069.7588000000001</v>
+        <v>99999</v>
       </c>
       <c r="M237">
         <v>0</v>
@@ -13846,7 +13849,7 @@
         <v>10</v>
       </c>
       <c r="L238">
-        <v>1069.7588000000001</v>
+        <v>99999</v>
       </c>
       <c r="M238">
         <v>0</v>
@@ -13896,7 +13899,7 @@
         <v>6</v>
       </c>
       <c r="L239">
-        <v>1841.7820999999999</v>
+        <v>99999</v>
       </c>
       <c r="M239">
         <v>0</v>
@@ -13946,7 +13949,7 @@
         <v>10</v>
       </c>
       <c r="L240">
-        <v>1004.0559</v>
+        <v>99999</v>
       </c>
       <c r="M240">
         <v>805</v>
@@ -13996,7 +13999,7 @@
         <v>6</v>
       </c>
       <c r="L241">
-        <v>1847.5297</v>
+        <v>99999</v>
       </c>
       <c r="M241">
         <v>55</v>
@@ -14046,7 +14049,7 @@
         <v>10</v>
       </c>
       <c r="L242">
-        <v>959.10879999999997</v>
+        <v>99999</v>
       </c>
       <c r="M242">
         <v>225</v>
@@ -14096,7 +14099,7 @@
         <v>12</v>
       </c>
       <c r="L243">
-        <v>2346.4548</v>
+        <v>99999</v>
       </c>
       <c r="M243">
         <v>0</v>
@@ -14146,7 +14149,7 @@
         <v>12</v>
       </c>
       <c r="L244">
-        <v>2615.9733999999999</v>
+        <v>99999</v>
       </c>
       <c r="M244">
         <v>3</v>
@@ -14196,7 +14199,7 @@
         <v>10</v>
       </c>
       <c r="L245">
-        <v>1271.1398999999999</v>
+        <v>99999</v>
       </c>
       <c r="M245">
         <v>0</v>
@@ -14246,7 +14249,7 @@
         <v>15</v>
       </c>
       <c r="L246">
-        <v>1193.1205</v>
+        <v>99999</v>
       </c>
       <c r="M246">
         <v>1</v>
@@ -14296,7 +14299,7 @@
         <v>15</v>
       </c>
       <c r="L247">
-        <v>829.92</v>
+        <v>99999</v>
       </c>
       <c r="M247">
         <v>0</v>
@@ -14346,7 +14349,7 @@
         <v>15</v>
       </c>
       <c r="L248">
-        <v>875.68</v>
+        <v>99999</v>
       </c>
       <c r="M248">
         <v>0</v>
@@ -14396,7 +14399,7 @@
         <v>15</v>
       </c>
       <c r="L249">
-        <v>631.37630000000001</v>
+        <v>99999</v>
       </c>
       <c r="M249">
         <v>1</v>
@@ -14446,7 +14449,7 @@
         <v>15</v>
       </c>
       <c r="L250">
-        <v>874.33219999999994</v>
+        <v>99999</v>
       </c>
       <c r="M250">
         <v>25</v>
@@ -14496,7 +14499,7 @@
         <v>10</v>
       </c>
       <c r="L251">
-        <v>1004.0559</v>
+        <v>99999</v>
       </c>
       <c r="M251">
         <v>0</v>
@@ -14546,7 +14549,7 @@
         <v>6</v>
       </c>
       <c r="L252">
-        <v>1847.5297</v>
+        <v>99999</v>
       </c>
       <c r="M252">
         <v>0</v>
@@ -14596,7 +14599,7 @@
         <v>6</v>
       </c>
       <c r="L253">
-        <v>1923.8516999999999</v>
+        <v>99999</v>
       </c>
       <c r="M253">
         <v>231</v>
@@ -14646,7 +14649,7 @@
         <v>6</v>
       </c>
       <c r="L254">
-        <v>4217</v>
+        <v>99999</v>
       </c>
       <c r="M254">
         <v>0</v>
@@ -14696,7 +14699,7 @@
         <v>6</v>
       </c>
       <c r="L255">
-        <v>4413.1684999999998</v>
+        <v>99999</v>
       </c>
       <c r="M255">
         <v>0</v>
@@ -14746,7 +14749,7 @@
         <v>6</v>
       </c>
       <c r="L256">
-        <v>4413.1684999999998</v>
+        <v>99999</v>
       </c>
       <c r="M256">
         <v>0</v>
@@ -14796,7 +14799,7 @@
         <v>6</v>
       </c>
       <c r="L257">
-        <v>2545.0142000000001</v>
+        <v>99999</v>
       </c>
       <c r="M257">
         <v>5</v>
@@ -14846,7 +14849,7 @@
         <v>6</v>
       </c>
       <c r="L258">
-        <v>2697.2808</v>
+        <v>99999</v>
       </c>
       <c r="M258">
         <v>0</v>
@@ -14896,7 +14899,7 @@
         <v>6</v>
       </c>
       <c r="L259">
-        <v>2697.2808</v>
+        <v>99999</v>
       </c>
       <c r="M259">
         <v>0</v>
@@ -14946,7 +14949,7 @@
         <v>6</v>
       </c>
       <c r="L260">
-        <v>2601.2617</v>
+        <v>99999</v>
       </c>
       <c r="M260">
         <v>3</v>
@@ -14996,7 +14999,7 @@
         <v>6</v>
       </c>
       <c r="L261">
-        <v>2441.1864999999998</v>
+        <v>99999</v>
       </c>
       <c r="M261">
         <v>1</v>
@@ -15046,7 +15049,7 @@
         <v>6</v>
       </c>
       <c r="L262">
-        <v>2441.1864999999998</v>
+        <v>99999</v>
       </c>
       <c r="M262">
         <v>4</v>
@@ -15096,7 +15099,7 @@
         <v>6</v>
       </c>
       <c r="L263">
-        <v>2441.1864999999998</v>
+        <v>99999</v>
       </c>
       <c r="M263">
         <v>0</v>
@@ -15146,7 +15149,7 @@
         <v>6</v>
       </c>
       <c r="L264">
-        <v>2601.2617</v>
+        <v>99999</v>
       </c>
       <c r="M264">
         <v>0</v>
@@ -15196,7 +15199,7 @@
         <v>6</v>
       </c>
       <c r="L265">
-        <v>2601.2617</v>
+        <v>99999</v>
       </c>
       <c r="M265">
         <v>6</v>
@@ -15246,7 +15249,7 @@
         <v>6</v>
       </c>
       <c r="L266">
-        <v>2441.1864999999998</v>
+        <v>99999</v>
       </c>
       <c r="M266">
         <v>0</v>
@@ -15296,7 +15299,7 @@
         <v>6</v>
       </c>
       <c r="L267">
-        <v>2601.2617</v>
+        <v>99999</v>
       </c>
       <c r="M267">
         <v>9</v>
@@ -15346,7 +15349,7 @@
         <v>6</v>
       </c>
       <c r="L268">
-        <v>2601.2617</v>
+        <v>99999</v>
       </c>
       <c r="M268">
         <v>0</v>
@@ -15396,7 +15399,7 @@
         <v>6</v>
       </c>
       <c r="L269">
-        <v>3057</v>
+        <v>99999</v>
       </c>
       <c r="M269">
         <v>0</v>
@@ -15446,7 +15449,7 @@
         <v>6</v>
       </c>
       <c r="L270">
-        <v>3057</v>
+        <v>99999</v>
       </c>
       <c r="M270">
         <v>68</v>
@@ -15496,7 +15499,7 @@
         <v>6</v>
       </c>
       <c r="L271">
-        <v>3057</v>
+        <v>99999</v>
       </c>
       <c r="M271">
         <v>33</v>
@@ -15546,7 +15549,7 @@
         <v>6</v>
       </c>
       <c r="L272">
-        <v>3281.5963999999999</v>
+        <v>99999</v>
       </c>
       <c r="M272">
         <v>0</v>
@@ -15596,7 +15599,7 @@
         <v>6</v>
       </c>
       <c r="L273">
-        <v>3481.6875</v>
+        <v>99999</v>
       </c>
       <c r="M273">
         <v>15</v>
@@ -15646,7 +15649,7 @@
         <v>6</v>
       </c>
       <c r="L274">
-        <v>3481.6875</v>
+        <v>99999</v>
       </c>
       <c r="M274">
         <v>0</v>
@@ -15696,7 +15699,7 @@
         <v>6</v>
       </c>
       <c r="L275">
-        <v>3281.5963999999999</v>
+        <v>99999</v>
       </c>
       <c r="M275">
         <v>0</v>
@@ -15746,7 +15749,7 @@
         <v>6</v>
       </c>
       <c r="L276">
-        <v>3362</v>
+        <v>99999</v>
       </c>
       <c r="M276">
         <v>0</v>
@@ -15796,7 +15799,7 @@
         <v>6</v>
       </c>
       <c r="L277">
-        <v>4274.8984</v>
+        <v>99999</v>
       </c>
       <c r="M277">
         <v>7</v>
@@ -15846,7 +15849,7 @@
         <v>6</v>
       </c>
       <c r="L278">
-        <v>4274.8984</v>
+        <v>99999</v>
       </c>
       <c r="M278">
         <v>9</v>
@@ -15896,7 +15899,7 @@
         <v>6</v>
       </c>
       <c r="L279">
-        <v>6089.9170000000004</v>
+        <v>99999</v>
       </c>
       <c r="M279">
         <v>1</v>
@@ -15946,7 +15949,7 @@
         <v>6</v>
       </c>
       <c r="L280">
-        <v>6089.9170000000004</v>
+        <v>99999</v>
       </c>
       <c r="M280">
         <v>0</v>
@@ -15996,7 +15999,7 @@
         <v>6</v>
       </c>
       <c r="L281">
-        <v>8220.9599999999991</v>
+        <v>99999</v>
       </c>
       <c r="M281">
         <v>25</v>
@@ -16046,7 +16049,7 @@
         <v>6</v>
       </c>
       <c r="L282">
-        <v>8220.9599999999991</v>
+        <v>99999</v>
       </c>
       <c r="M282">
         <v>26</v>
@@ -16096,7 +16099,7 @@
         <v>6</v>
       </c>
       <c r="L283">
-        <v>5102.4809999999998</v>
+        <v>99999</v>
       </c>
       <c r="M283">
         <v>9</v>
@@ -16146,7 +16149,7 @@
         <v>6</v>
       </c>
       <c r="L284">
-        <v>5102.4809999999998</v>
+        <v>99999</v>
       </c>
       <c r="M284">
         <v>37</v>
@@ -16196,7 +16199,7 @@
         <v>6</v>
       </c>
       <c r="L285">
-        <v>7394.8975</v>
+        <v>99999</v>
       </c>
       <c r="M285">
         <v>8</v>
@@ -16246,7 +16249,7 @@
         <v>6</v>
       </c>
       <c r="L286">
-        <v>7177.4008999999996</v>
+        <v>99999</v>
       </c>
       <c r="M286">
         <v>31</v>
@@ -16296,7 +16299,7 @@
         <v>6</v>
       </c>
       <c r="L287">
-        <v>7177.4008999999996</v>
+        <v>99999</v>
       </c>
       <c r="M287">
         <v>7</v>
@@ -16346,7 +16349,7 @@
         <v>6</v>
       </c>
       <c r="L288">
-        <v>4545.2754000000004</v>
+        <v>99999</v>
       </c>
       <c r="M288">
         <v>19</v>
@@ -16396,7 +16399,7 @@
         <v>6</v>
       </c>
       <c r="L289">
-        <v>4545.2754000000004</v>
+        <v>99999</v>
       </c>
       <c r="M289">
         <v>15</v>
@@ -16446,7 +16449,7 @@
         <v>6</v>
       </c>
       <c r="L290">
-        <v>4545.2754000000004</v>
+        <v>99999</v>
       </c>
       <c r="M290">
         <v>7</v>
@@ -16496,7 +16499,7 @@
         <v>6</v>
       </c>
       <c r="L291">
-        <v>4545.2754000000004</v>
+        <v>99999</v>
       </c>
       <c r="M291">
         <v>0</v>
@@ -16546,7 +16549,7 @@
         <v>6</v>
       </c>
       <c r="L292">
-        <v>4077</v>
+        <v>99999</v>
       </c>
       <c r="M292">
         <v>0</v>
@@ -16596,7 +16599,7 @@
         <v>6</v>
       </c>
       <c r="L293">
-        <v>5712</v>
+        <v>99999</v>
       </c>
       <c r="M293">
         <v>0</v>
@@ -16646,7 +16649,7 @@
         <v>12</v>
       </c>
       <c r="L294">
-        <v>1780.8624</v>
+        <v>99999</v>
       </c>
       <c r="M294">
         <v>3</v>
@@ -16696,7 +16699,7 @@
         <v>12</v>
       </c>
       <c r="L295">
-        <v>2875</v>
+        <v>99999</v>
       </c>
       <c r="M295">
         <v>4</v>
@@ -16746,7 +16749,7 @@
         <v>6</v>
       </c>
       <c r="L296">
-        <v>5712</v>
+        <v>99999</v>
       </c>
       <c r="M296">
         <v>0</v>
@@ -16796,7 +16799,7 @@
         <v>6</v>
       </c>
       <c r="L297">
-        <v>5102.4809999999998</v>
+        <v>99999</v>
       </c>
       <c r="M297">
         <v>9</v>
@@ -16846,7 +16849,7 @@
         <v>6</v>
       </c>
       <c r="L298">
-        <v>6089.9102000000003</v>
+        <v>99999</v>
       </c>
       <c r="M298">
         <v>0</v>
@@ -16896,7 +16899,7 @@
         <v>6</v>
       </c>
       <c r="L299">
-        <v>5712</v>
+        <v>99999</v>
       </c>
       <c r="M299">
         <v>8</v>
@@ -16946,7 +16949,7 @@
         <v>6</v>
       </c>
       <c r="L300">
-        <v>8220.9599999999991</v>
+        <v>99999</v>
       </c>
       <c r="M300">
         <v>3</v>
@@ -16996,7 +16999,7 @@
         <v>6</v>
       </c>
       <c r="L301">
-        <v>3057</v>
+        <v>99999</v>
       </c>
       <c r="M301">
         <v>0</v>
@@ -17046,7 +17049,7 @@
         <v>1</v>
       </c>
       <c r="L302">
-        <v>13147.3945</v>
+        <v>99999</v>
       </c>
       <c r="M302">
         <v>6</v>
@@ -17096,7 +17099,7 @@
         <v>1</v>
       </c>
       <c r="L303">
-        <v>5302.5438999999997</v>
+        <v>99999</v>
       </c>
       <c r="M303">
         <v>1</v>
@@ -17146,7 +17149,7 @@
         <v>12</v>
       </c>
       <c r="L304">
-        <v>4090.3289</v>
+        <v>99999</v>
       </c>
       <c r="M304">
         <v>17</v>
@@ -17196,7 +17199,7 @@
         <v>12</v>
       </c>
       <c r="L305">
-        <v>2516.3092999999999</v>
+        <v>99999</v>
       </c>
       <c r="M305">
         <v>34</v>
@@ -17246,7 +17249,7 @@
         <v>12</v>
       </c>
       <c r="L306">
-        <v>1449.7825</v>
+        <v>99999</v>
       </c>
       <c r="M306">
         <v>20</v>
@@ -17296,7 +17299,7 @@
         <v>20</v>
       </c>
       <c r="L307">
-        <v>699.36659999999995</v>
+        <v>99999</v>
       </c>
       <c r="M307">
         <v>10</v>
@@ -17349,7 +17352,7 @@
         <v>20</v>
       </c>
       <c r="L308">
-        <v>699.36659999999995</v>
+        <v>99999</v>
       </c>
       <c r="M308">
         <v>0</v>
@@ -17402,7 +17405,7 @@
         <v>6</v>
       </c>
       <c r="L309">
-        <v>3124.8499000000002</v>
+        <v>99999</v>
       </c>
       <c r="M309">
         <v>0</v>
@@ -17455,7 +17458,7 @@
         <v>1</v>
       </c>
       <c r="L310">
-        <v>2968.2824999999998</v>
+        <v>99999</v>
       </c>
       <c r="M310">
         <v>1</v>
@@ -17505,7 +17508,7 @@
         <v>1</v>
       </c>
       <c r="L311">
-        <v>2968.2824999999998</v>
+        <v>99999</v>
       </c>
       <c r="M311">
         <v>1</v>
@@ -17555,7 +17558,7 @@
         <v>4</v>
       </c>
       <c r="L312">
-        <v>11586.6396</v>
+        <v>99999</v>
       </c>
       <c r="M312">
         <v>8</v>
@@ -17605,7 +17608,7 @@
         <v>4</v>
       </c>
       <c r="L313">
-        <v>11586.6396</v>
+        <v>99999</v>
       </c>
       <c r="M313">
         <v>8</v>
@@ -17655,7 +17658,7 @@
         <v>4</v>
       </c>
       <c r="L314">
-        <v>10333.6816</v>
+        <v>99999</v>
       </c>
       <c r="M314">
         <v>3</v>
@@ -17705,7 +17708,7 @@
         <v>4</v>
       </c>
       <c r="L315">
-        <v>10333.6816</v>
+        <v>99999</v>
       </c>
       <c r="M315">
         <v>3</v>
@@ -17755,7 +17758,7 @@
         <v>12</v>
       </c>
       <c r="L316">
-        <v>1025.729</v>
+        <v>99999</v>
       </c>
       <c r="M316">
         <v>2</v>
@@ -17805,7 +17808,7 @@
         <v>12</v>
       </c>
       <c r="L317">
-        <v>1025.729</v>
+        <v>99999</v>
       </c>
       <c r="M317">
         <v>0</v>
@@ -17855,7 +17858,7 @@
         <v>12</v>
       </c>
       <c r="L318">
-        <v>1411.7118</v>
+        <v>99999</v>
       </c>
       <c r="M318">
         <v>2</v>
@@ -17905,7 +17908,7 @@
         <v>12</v>
       </c>
       <c r="L319">
-        <v>1411.7118</v>
+        <v>99999</v>
       </c>
       <c r="M319">
         <v>2</v>
@@ -17955,7 +17958,7 @@
         <v>12</v>
       </c>
       <c r="L320">
-        <v>2327.1918999999998</v>
+        <v>99999</v>
       </c>
       <c r="M320">
         <v>0</v>
@@ -18005,7 +18008,7 @@
         <v>12</v>
       </c>
       <c r="L321">
-        <v>2327.1918999999998</v>
+        <v>99999</v>
       </c>
       <c r="M321">
         <v>0</v>
@@ -18055,7 +18058,7 @@
         <v>12</v>
       </c>
       <c r="L322">
-        <v>1131.0522000000001</v>
+        <v>99999</v>
       </c>
       <c r="M322">
         <v>0</v>
@@ -18105,7 +18108,7 @@
         <v>12</v>
       </c>
       <c r="L323">
-        <v>1131.0522000000001</v>
+        <v>99999</v>
       </c>
       <c r="M323">
         <v>0</v>
@@ -18155,7 +18158,7 @@
         <v>12</v>
       </c>
       <c r="L324">
-        <v>1131.0524</v>
+        <v>99999</v>
       </c>
       <c r="M324">
         <v>0</v>
@@ -18205,7 +18208,7 @@
         <v>12</v>
       </c>
       <c r="L325">
-        <v>1131.0524</v>
+        <v>99999</v>
       </c>
       <c r="M325">
         <v>0</v>
@@ -18255,7 +18258,7 @@
         <v>12</v>
       </c>
       <c r="L326">
-        <v>1131.0524</v>
+        <v>99999</v>
       </c>
       <c r="M326">
         <v>1</v>
@@ -18305,7 +18308,7 @@
         <v>12</v>
       </c>
       <c r="L327">
-        <v>1131.0524</v>
+        <v>99999</v>
       </c>
       <c r="M327">
         <v>1</v>
@@ -18355,7 +18358,7 @@
         <v>12</v>
       </c>
       <c r="L328">
-        <v>1445.3273999999999</v>
+        <v>99999</v>
       </c>
       <c r="M328">
         <v>0</v>
@@ -18405,7 +18408,7 @@
         <v>12</v>
       </c>
       <c r="L329">
-        <v>1445.3273999999999</v>
+        <v>99999</v>
       </c>
       <c r="M329">
         <v>0</v>
@@ -18455,7 +18458,7 @@
         <v>12</v>
       </c>
       <c r="L330">
-        <v>690.08939999999996</v>
+        <v>99999</v>
       </c>
       <c r="M330">
         <v>0</v>
@@ -18505,7 +18508,7 @@
         <v>12</v>
       </c>
       <c r="L331">
-        <v>690.08939999999996</v>
+        <v>99999</v>
       </c>
       <c r="M331">
         <v>0</v>
@@ -18555,7 +18558,7 @@
         <v>12</v>
       </c>
       <c r="L332">
-        <v>857.94420000000002</v>
+        <v>99999</v>
       </c>
       <c r="M332">
         <v>4</v>
@@ -18605,7 +18608,7 @@
         <v>12</v>
       </c>
       <c r="L333">
-        <v>857.94420000000002</v>
+        <v>99999</v>
       </c>
       <c r="M333">
         <v>4</v>
@@ -18655,7 +18658,7 @@
         <v>12</v>
       </c>
       <c r="L334">
-        <v>760.26859999999999</v>
+        <v>99999</v>
       </c>
       <c r="M334">
         <v>0</v>
@@ -18705,7 +18708,7 @@
         <v>12</v>
       </c>
       <c r="L335">
-        <v>760.26859999999999</v>
+        <v>99999</v>
       </c>
       <c r="M335">
         <v>0</v>
@@ -18755,7 +18758,7 @@
         <v>12</v>
       </c>
       <c r="L336">
-        <v>988.34829999999999</v>
+        <v>99999</v>
       </c>
       <c r="M336">
         <v>15</v>
@@ -18805,7 +18808,7 @@
         <v>12</v>
       </c>
       <c r="L337">
-        <v>988.34829999999999</v>
+        <v>99999</v>
       </c>
       <c r="M337">
         <v>15</v>
@@ -18855,7 +18858,7 @@
         <v>12</v>
       </c>
       <c r="L338">
-        <v>1981.4906000000001</v>
+        <v>99999</v>
       </c>
       <c r="M338">
         <v>8</v>
@@ -18905,7 +18908,7 @@
         <v>12</v>
       </c>
       <c r="L339">
-        <v>1981.4906000000001</v>
+        <v>99999</v>
       </c>
       <c r="M339">
         <v>7</v>
@@ -18955,7 +18958,7 @@
         <v>12</v>
       </c>
       <c r="L340">
-        <v>2476.7649000000001</v>
+        <v>99999</v>
       </c>
       <c r="M340">
         <v>8</v>
@@ -19005,7 +19008,7 @@
         <v>12</v>
       </c>
       <c r="L341">
-        <v>2476.7649000000001</v>
+        <v>99999</v>
       </c>
       <c r="M341">
         <v>8</v>
@@ -19055,7 +19058,7 @@
         <v>12</v>
       </c>
       <c r="L342">
-        <v>2476.7649000000001</v>
+        <v>99999</v>
       </c>
       <c r="M342">
         <v>9</v>
@@ -19105,7 +19108,7 @@
         <v>12</v>
       </c>
       <c r="L343">
-        <v>2476.7649000000001</v>
+        <v>99999</v>
       </c>
       <c r="M343">
         <v>9</v>
@@ -19155,7 +19158,7 @@
         <v>12</v>
       </c>
       <c r="L344">
-        <v>1131.0524</v>
+        <v>99999</v>
       </c>
       <c r="M344">
         <v>3</v>
@@ -19205,7 +19208,7 @@
         <v>12</v>
       </c>
       <c r="L345">
-        <v>1131.0524</v>
+        <v>99999</v>
       </c>
       <c r="M345">
         <v>0</v>
@@ -19255,7 +19258,7 @@
         <v>12</v>
       </c>
       <c r="L346">
-        <v>1131.0524</v>
+        <v>99999</v>
       </c>
       <c r="M346">
         <v>3</v>
@@ -19305,7 +19308,7 @@
         <v>12</v>
       </c>
       <c r="L347">
-        <v>1131.0524</v>
+        <v>99999</v>
       </c>
       <c r="M347">
         <v>3</v>
@@ -19355,7 +19358,7 @@
         <v>12</v>
       </c>
       <c r="L348">
-        <v>1445.3275000000001</v>
+        <v>99999</v>
       </c>
       <c r="M348">
         <v>1</v>
@@ -19405,7 +19408,7 @@
         <v>12</v>
       </c>
       <c r="L349">
-        <v>1445.3275000000001</v>
+        <v>99999</v>
       </c>
       <c r="M349">
         <v>2</v>
@@ -19455,7 +19458,7 @@
         <v>12</v>
       </c>
       <c r="L350">
-        <v>933.83969999999999</v>
+        <v>99999</v>
       </c>
       <c r="M350">
         <v>7</v>
@@ -19505,7 +19508,7 @@
         <v>12</v>
       </c>
       <c r="L351">
-        <v>933.83969999999999</v>
+        <v>99999</v>
       </c>
       <c r="M351">
         <v>6</v>
@@ -19555,7 +19558,7 @@
         <v>12</v>
       </c>
       <c r="L352">
-        <v>1194.4117000000001</v>
+        <v>99999</v>
       </c>
       <c r="M352">
         <v>0</v>
@@ -19605,7 +19608,7 @@
         <v>12</v>
       </c>
       <c r="L353">
-        <v>1194.4117000000001</v>
+        <v>99999</v>
       </c>
       <c r="M353">
         <v>0</v>
@@ -19655,7 +19658,7 @@
         <v>12</v>
       </c>
       <c r="L354">
-        <v>1040.3666000000001</v>
+        <v>99999</v>
       </c>
       <c r="M354">
         <v>0</v>
@@ -19705,7 +19708,7 @@
         <v>12</v>
       </c>
       <c r="L355">
-        <v>1040.3666000000001</v>
+        <v>99999</v>
       </c>
       <c r="M355">
         <v>0</v>
@@ -19755,7 +19758,7 @@
         <v>12</v>
       </c>
       <c r="L356">
-        <v>1414.8679</v>
+        <v>99999</v>
       </c>
       <c r="M356">
         <v>0</v>
@@ -19805,7 +19808,7 @@
         <v>12</v>
       </c>
       <c r="L357">
-        <v>1414.8679</v>
+        <v>99999</v>
       </c>
       <c r="M357">
         <v>0</v>
@@ -19855,7 +19858,7 @@
         <v>6</v>
       </c>
       <c r="L358">
-        <v>760.47149999999999</v>
+        <v>99999</v>
       </c>
       <c r="M358">
         <v>1</v>
@@ -19905,7 +19908,7 @@
         <v>6</v>
       </c>
       <c r="L359">
-        <v>760.47149999999999</v>
+        <v>99999</v>
       </c>
       <c r="M359">
         <v>0</v>
@@ -19955,7 +19958,7 @@
         <v>12</v>
       </c>
       <c r="L360">
-        <v>1411.712</v>
+        <v>99999</v>
       </c>
       <c r="M360">
         <v>2</v>
@@ -20005,7 +20008,7 @@
         <v>12</v>
       </c>
       <c r="L361">
-        <v>1411.712</v>
+        <v>99999</v>
       </c>
       <c r="M361">
         <v>0</v>
@@ -20055,7 +20058,7 @@
         <v>12</v>
       </c>
       <c r="L362">
-        <v>1411.712</v>
+        <v>99999</v>
       </c>
       <c r="M362">
         <v>4</v>
@@ -20105,7 +20108,7 @@
         <v>12</v>
       </c>
       <c r="L363">
-        <v>1411.712</v>
+        <v>99999</v>
       </c>
       <c r="M363">
         <v>3</v>
@@ -20155,7 +20158,7 @@
         <v>12</v>
       </c>
       <c r="L364">
-        <v>1960.1014</v>
+        <v>99999</v>
       </c>
       <c r="M364">
         <v>2</v>
@@ -20205,7 +20208,7 @@
         <v>12</v>
       </c>
       <c r="L365">
-        <v>1960.1014</v>
+        <v>99999</v>
       </c>
       <c r="M365">
         <v>1</v>
@@ -20255,7 +20258,7 @@
         <v>60</v>
       </c>
       <c r="L366">
-        <v>287.75639999999999</v>
+        <v>99999</v>
       </c>
       <c r="M366">
         <v>0</v>
@@ -20305,7 +20308,7 @@
         <v>60</v>
       </c>
       <c r="L367">
-        <v>601.53409999999997</v>
+        <v>99999</v>
       </c>
       <c r="M367">
         <v>0</v>
@@ -20355,7 +20358,7 @@
         <v>25</v>
       </c>
       <c r="L368">
-        <v>2630.8154</v>
+        <v>99999</v>
       </c>
       <c r="M368">
         <v>6</v>
@@ -20405,7 +20408,7 @@
         <v>60</v>
       </c>
       <c r="L369">
-        <v>350.28289999999998</v>
+        <v>99999</v>
       </c>
       <c r="M369">
         <v>7</v>
@@ -20455,7 +20458,7 @@
         <v>60</v>
       </c>
       <c r="L370">
-        <v>381.15379999999999</v>
+        <v>99999</v>
       </c>
       <c r="M370">
         <v>8</v>
@@ -20505,7 +20508,7 @@
         <v>60</v>
       </c>
       <c r="L371">
-        <v>274.37200000000001</v>
+        <v>99999</v>
       </c>
       <c r="M371">
         <v>2</v>
@@ -20555,7 +20558,7 @@
         <v>60</v>
       </c>
       <c r="L372">
-        <v>758.74839999999995</v>
+        <v>99999</v>
       </c>
       <c r="M372">
         <v>10</v>
@@ -20605,7 +20608,7 @@
         <v>60</v>
       </c>
       <c r="L373">
-        <v>577.024</v>
+        <v>99999</v>
       </c>
       <c r="M373">
         <v>0</v>
@@ -20655,7 +20658,7 @@
         <v>60</v>
       </c>
       <c r="L374">
-        <v>448.61849999999998</v>
+        <v>99999</v>
       </c>
       <c r="M374">
         <v>0</v>
@@ -20705,7 +20708,7 @@
         <v>60</v>
       </c>
       <c r="L375">
-        <v>305.41520000000003</v>
+        <v>99999</v>
       </c>
       <c r="M375">
         <v>6</v>
@@ -20755,7 +20758,7 @@
         <v>60</v>
       </c>
       <c r="L376">
-        <v>271.02089999999998</v>
+        <v>99999</v>
       </c>
       <c r="M376">
         <v>6</v>
@@ -20805,7 +20808,7 @@
         <v>40</v>
       </c>
       <c r="L377">
-        <v>420.70609999999999</v>
+        <v>99999</v>
       </c>
       <c r="M377">
         <v>10</v>
@@ -20855,7 +20858,7 @@
         <v>60</v>
       </c>
       <c r="L378">
-        <v>327.166</v>
+        <v>99999</v>
       </c>
       <c r="M378">
         <v>0</v>
@@ -20905,7 +20908,7 @@
         <v>50</v>
       </c>
       <c r="L379">
-        <v>81.743600000000001</v>
+        <v>99999</v>
       </c>
       <c r="M379">
         <v>0</v>
@@ -20955,7 +20958,7 @@
         <v>12</v>
       </c>
       <c r="L380">
-        <v>663.178</v>
+        <v>99999</v>
       </c>
       <c r="M380">
         <v>6</v>
@@ -21005,7 +21008,7 @@
         <v>60</v>
       </c>
       <c r="L381">
-        <v>370.45409999999998</v>
+        <v>99999</v>
       </c>
       <c r="M381">
         <v>14</v>
@@ -21055,7 +21058,7 @@
         <v>24</v>
       </c>
       <c r="L382">
-        <v>570.50289999999995</v>
+        <v>99999</v>
       </c>
       <c r="M382">
         <v>15</v>
@@ -21105,7 +21108,7 @@
         <v>60</v>
       </c>
       <c r="L383">
-        <v>286.7251</v>
+        <v>99999</v>
       </c>
       <c r="M383">
         <v>6</v>
@@ -21155,7 +21158,7 @@
         <v>12</v>
       </c>
       <c r="L384">
-        <v>1596.5615</v>
+        <v>99999</v>
       </c>
       <c r="M384">
         <v>13</v>
@@ -21205,7 +21208,7 @@
         <v>28</v>
       </c>
       <c r="L385">
-        <v>874.50760000000002</v>
+        <v>99999</v>
       </c>
       <c r="M385">
         <v>0</v>
@@ -21255,7 +21258,7 @@
         <v>18</v>
       </c>
       <c r="L386">
-        <v>613.84289999999999</v>
+        <v>99999</v>
       </c>
       <c r="M386">
         <v>0</v>
@@ -21305,7 +21308,7 @@
         <v>4</v>
       </c>
       <c r="L387">
-        <v>7121.5684000000001</v>
+        <v>99999</v>
       </c>
       <c r="M387">
         <v>1</v>
@@ -21355,7 +21358,7 @@
         <v>18</v>
       </c>
       <c r="L388">
-        <v>636.726</v>
+        <v>99999</v>
       </c>
       <c r="M388">
         <v>0</v>
@@ -21405,7 +21408,7 @@
         <v>12</v>
       </c>
       <c r="L389">
-        <v>1380.9825000000001</v>
+        <v>99999</v>
       </c>
       <c r="M389">
         <v>3</v>
@@ -21455,7 +21458,7 @@
         <v>12</v>
       </c>
       <c r="L390">
-        <v>1010.7366</v>
+        <v>99999</v>
       </c>
       <c r="M390">
         <v>0</v>
@@ -21505,7 +21508,7 @@
         <v>12</v>
       </c>
       <c r="L391">
-        <v>954.44290000000001</v>
+        <v>99999</v>
       </c>
       <c r="M391">
         <v>3</v>
@@ -21555,7 +21558,7 @@
         <v>12</v>
       </c>
       <c r="L392">
-        <v>906.72280000000001</v>
+        <v>99999</v>
       </c>
       <c r="M392">
         <v>3</v>
@@ -21605,7 +21608,7 @@
         <v>12</v>
       </c>
       <c r="L393">
-        <v>1325.4614999999999</v>
+        <v>99999</v>
       </c>
       <c r="M393">
         <v>7</v>
@@ -21655,7 +21658,7 @@
         <v>12</v>
       </c>
       <c r="L394">
-        <v>675.76189999999997</v>
+        <v>99999</v>
       </c>
       <c r="M394">
         <v>4</v>
@@ -21705,7 +21708,7 @@
         <v>12</v>
       </c>
       <c r="L395">
-        <v>1503.8697999999999</v>
+        <v>99999</v>
       </c>
       <c r="M395">
         <v>1</v>
@@ -21755,7 +21758,7 @@
         <v>12</v>
       </c>
       <c r="L396">
-        <v>1655.4640999999999</v>
+        <v>99999</v>
       </c>
       <c r="M396">
         <v>9</v>
@@ -21805,7 +21808,7 @@
         <v>12</v>
       </c>
       <c r="L397">
-        <v>1123.9269999999999</v>
+        <v>99999</v>
       </c>
       <c r="M397">
         <v>1</v>
@@ -21855,7 +21858,7 @@
         <v>12</v>
       </c>
       <c r="L398">
-        <v>2884.6289000000002</v>
+        <v>99999</v>
       </c>
       <c r="M398">
         <v>7</v>
@@ -21905,7 +21908,7 @@
         <v>28</v>
       </c>
       <c r="L399">
-        <v>1058.2320999999999</v>
+        <v>99999</v>
       </c>
       <c r="M399">
         <v>3</v>
@@ -21955,7 +21958,7 @@
         <v>12</v>
       </c>
       <c r="L400">
-        <v>844.70460000000003</v>
+        <v>99999</v>
       </c>
       <c r="M400">
         <v>0</v>
@@ -22005,7 +22008,7 @@
         <v>12</v>
       </c>
       <c r="L401">
-        <v>844.70460000000003</v>
+        <v>99999</v>
       </c>
       <c r="M401">
         <v>0</v>
@@ -22055,7 +22058,7 @@
         <v>4</v>
       </c>
       <c r="L402">
-        <v>5874.6602000000003</v>
+        <v>99999</v>
       </c>
       <c r="M402">
         <v>10</v>
@@ -22105,7 +22108,7 @@
         <v>14</v>
       </c>
       <c r="L403">
-        <v>949.70479999999998</v>
+        <v>99999</v>
       </c>
       <c r="M403">
         <v>233</v>
@@ -22158,7 +22161,7 @@
         <v>14</v>
       </c>
       <c r="L404">
-        <v>949.70479999999998</v>
+        <v>99999</v>
       </c>
       <c r="M404">
         <v>0</v>
@@ -22211,7 +22214,7 @@
         <v>60</v>
       </c>
       <c r="L405">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M405">
         <v>6</v>
@@ -22261,7 +22264,7 @@
         <v>60</v>
       </c>
       <c r="L406">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M406">
         <v>5</v>
@@ -22311,7 +22314,7 @@
         <v>60</v>
       </c>
       <c r="L407">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M407">
         <v>45</v>
@@ -22361,7 +22364,7 @@
         <v>60</v>
       </c>
       <c r="L408">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M408">
         <v>37</v>
@@ -22411,7 +22414,7 @@
         <v>108</v>
       </c>
       <c r="L409">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M409">
         <v>7</v>
@@ -22461,7 +22464,7 @@
         <v>108</v>
       </c>
       <c r="L410">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M410">
         <v>5</v>
@@ -22511,7 +22514,7 @@
         <v>18</v>
       </c>
       <c r="L411">
-        <v>1742.62</v>
+        <v>99999</v>
       </c>
       <c r="M411">
         <v>0</v>
@@ -22561,7 +22564,7 @@
         <v>18</v>
       </c>
       <c r="L412">
-        <v>1742.62</v>
+        <v>99999</v>
       </c>
       <c r="M412">
         <v>0</v>
@@ -22611,7 +22614,7 @@
         <v>76</v>
       </c>
       <c r="L413">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M413">
         <v>74</v>
@@ -22661,7 +22664,7 @@
         <v>76</v>
       </c>
       <c r="L414">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M414">
         <v>62</v>
@@ -22711,7 +22714,7 @@
         <v>120</v>
       </c>
       <c r="L415">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M415">
         <v>8</v>
@@ -22761,7 +22764,7 @@
         <v>120</v>
       </c>
       <c r="L416">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M416">
         <v>18</v>
@@ -22811,7 +22814,7 @@
         <v>36</v>
       </c>
       <c r="L417">
-        <v>1113.3399999999999</v>
+        <v>99999</v>
       </c>
       <c r="M417">
         <v>26</v>
@@ -22861,7 +22864,7 @@
         <v>36</v>
       </c>
       <c r="L418">
-        <v>1113.3399999999999</v>
+        <v>99999</v>
       </c>
       <c r="M418">
         <v>18</v>
@@ -22911,7 +22914,7 @@
         <v>20</v>
       </c>
       <c r="L419">
-        <v>2371.8998999999999</v>
+        <v>99999</v>
       </c>
       <c r="M419">
         <v>28</v>
@@ -22961,7 +22964,7 @@
         <v>20</v>
       </c>
       <c r="L420">
-        <v>2371.8998999999999</v>
+        <v>99999</v>
       </c>
       <c r="M420">
         <v>38</v>
@@ -23011,7 +23014,7 @@
         <v>20</v>
       </c>
       <c r="L421">
-        <v>2371.8998999999999</v>
+        <v>99999</v>
       </c>
       <c r="M421">
         <v>54</v>
@@ -23061,7 +23064,7 @@
         <v>20</v>
       </c>
       <c r="L422">
-        <v>2371.8998999999999</v>
+        <v>99999</v>
       </c>
       <c r="M422">
         <v>38</v>
@@ -23111,7 +23114,7 @@
         <v>21</v>
       </c>
       <c r="L423">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M423">
         <v>20</v>
@@ -23161,7 +23164,7 @@
         <v>21</v>
       </c>
       <c r="L424">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M424">
         <v>27</v>
@@ -23211,7 +23214,7 @@
         <v>36</v>
       </c>
       <c r="L425">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M425">
         <v>105</v>
@@ -23261,7 +23264,7 @@
         <v>36</v>
       </c>
       <c r="L426">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M426">
         <v>136</v>
@@ -23311,7 +23314,7 @@
         <v>16</v>
       </c>
       <c r="L427">
-        <v>1694.21</v>
+        <v>99999</v>
       </c>
       <c r="M427">
         <v>28</v>
@@ -23361,7 +23364,7 @@
         <v>16</v>
       </c>
       <c r="L428">
-        <v>1694.21</v>
+        <v>99999</v>
       </c>
       <c r="M428">
         <v>33</v>
@@ -23411,7 +23414,7 @@
         <v>36</v>
       </c>
       <c r="L429">
-        <v>1113.3399999999999</v>
+        <v>99999</v>
       </c>
       <c r="M429">
         <v>20</v>
@@ -23461,7 +23464,7 @@
         <v>36</v>
       </c>
       <c r="L430">
-        <v>1113.3399999999999</v>
+        <v>99999</v>
       </c>
       <c r="M430">
         <v>30</v>
@@ -23511,7 +23514,7 @@
         <v>36</v>
       </c>
       <c r="L431">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M431">
         <v>28</v>
@@ -23561,7 +23564,7 @@
         <v>36</v>
       </c>
       <c r="L432">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M432">
         <v>23</v>
@@ -23611,7 +23614,7 @@
         <v>21</v>
       </c>
       <c r="L433">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M433">
         <v>7</v>
@@ -23661,7 +23664,7 @@
         <v>21</v>
       </c>
       <c r="L434">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M434">
         <v>6</v>
@@ -23711,7 +23714,7 @@
         <v>75</v>
       </c>
       <c r="L435">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M435">
         <v>266</v>
@@ -23764,7 +23767,7 @@
         <v>75</v>
       </c>
       <c r="L436">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M436">
         <v>0</v>
@@ -23817,7 +23820,7 @@
         <v>75</v>
       </c>
       <c r="L437">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M437">
         <v>247</v>
@@ -23867,7 +23870,7 @@
         <v>75</v>
       </c>
       <c r="L438">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M438">
         <v>202</v>
@@ -23917,7 +23920,7 @@
         <v>18</v>
       </c>
       <c r="L439">
-        <v>2468.71</v>
+        <v>99999</v>
       </c>
       <c r="M439">
         <v>249</v>
@@ -23967,7 +23970,7 @@
         <v>18</v>
       </c>
       <c r="L440">
-        <v>2468.71</v>
+        <v>99999</v>
       </c>
       <c r="M440">
         <v>253</v>
@@ -24017,7 +24020,7 @@
         <v>18</v>
       </c>
       <c r="L441">
-        <v>1064.9399000000001</v>
+        <v>99999</v>
       </c>
       <c r="M441">
         <v>0</v>
@@ -24067,7 +24070,7 @@
         <v>18</v>
       </c>
       <c r="L442">
-        <v>1064.9399000000001</v>
+        <v>99999</v>
       </c>
       <c r="M442">
         <v>0</v>
@@ -24117,7 +24120,7 @@
         <v>18</v>
       </c>
       <c r="L443">
-        <v>1742.62</v>
+        <v>99999</v>
       </c>
       <c r="M443">
         <v>0</v>
@@ -24167,7 +24170,7 @@
         <v>18</v>
       </c>
       <c r="L444">
-        <v>1742.62</v>
+        <v>99999</v>
       </c>
       <c r="M444">
         <v>0</v>
@@ -24217,7 +24220,7 @@
         <v>21</v>
       </c>
       <c r="L445">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M445">
         <v>9</v>
@@ -24267,7 +24270,7 @@
         <v>21</v>
       </c>
       <c r="L446">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M446">
         <v>8</v>
@@ -24317,7 +24320,7 @@
         <v>36</v>
       </c>
       <c r="L447">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M447">
         <v>24</v>
@@ -24367,7 +24370,7 @@
         <v>36</v>
       </c>
       <c r="L448">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M448">
         <v>16</v>
@@ -24417,7 +24420,7 @@
         <v>60</v>
       </c>
       <c r="L449">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M449">
         <v>4</v>
@@ -24467,7 +24470,7 @@
         <v>60</v>
       </c>
       <c r="L450">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M450">
         <v>0</v>
@@ -24517,7 +24520,7 @@
         <v>72</v>
       </c>
       <c r="L451">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M451">
         <v>5</v>
@@ -24567,7 +24570,7 @@
         <v>72</v>
       </c>
       <c r="L452">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M452">
         <v>9</v>
@@ -24617,7 +24620,7 @@
         <v>72</v>
       </c>
       <c r="L453">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M453">
         <v>5</v>
@@ -24667,7 +24670,7 @@
         <v>72</v>
       </c>
       <c r="L454">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M454">
         <v>4</v>
@@ -24717,7 +24720,7 @@
         <v>68</v>
       </c>
       <c r="L455">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M455">
         <v>505</v>
@@ -24770,7 +24773,7 @@
         <v>68</v>
       </c>
       <c r="L456">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M456">
         <v>0</v>
@@ -24823,7 +24826,7 @@
         <v>68</v>
       </c>
       <c r="L457">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M457">
         <v>475</v>
@@ -24876,7 +24879,7 @@
         <v>68</v>
       </c>
       <c r="L458">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M458">
         <v>0</v>
@@ -24929,7 +24932,7 @@
         <v>68</v>
       </c>
       <c r="L459">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M459">
         <v>473</v>
@@ -24979,7 +24982,7 @@
         <v>68</v>
       </c>
       <c r="L460">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M460">
         <v>397</v>
@@ -25029,7 +25032,7 @@
         <v>70</v>
       </c>
       <c r="L461">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M461">
         <v>219</v>
@@ -25079,7 +25082,7 @@
         <v>70</v>
       </c>
       <c r="L462">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M462">
         <v>188</v>
@@ -25129,7 +25132,7 @@
         <v>70</v>
       </c>
       <c r="L463">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M463">
         <v>1018</v>
@@ -25182,7 +25185,7 @@
         <v>70</v>
       </c>
       <c r="L464">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M464">
         <v>0</v>
@@ -25235,7 +25238,7 @@
         <v>70</v>
       </c>
       <c r="L465">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M465">
         <v>974</v>
@@ -25288,7 +25291,7 @@
         <v>70</v>
       </c>
       <c r="L466">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M466">
         <v>0</v>
@@ -25341,7 +25344,7 @@
         <v>70</v>
       </c>
       <c r="L467">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M467">
         <v>974</v>
@@ -25391,7 +25394,7 @@
         <v>70</v>
       </c>
       <c r="L468">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M468">
         <v>874</v>
@@ -25441,7 +25444,7 @@
         <v>58</v>
       </c>
       <c r="L469">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M469">
         <v>0</v>
@@ -25491,7 +25494,7 @@
         <v>58</v>
       </c>
       <c r="L470">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M470">
         <v>0</v>
@@ -25541,7 +25544,7 @@
         <v>72</v>
       </c>
       <c r="L471">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M471">
         <v>3</v>
@@ -25591,7 +25594,7 @@
         <v>72</v>
       </c>
       <c r="L472">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M472">
         <v>2</v>
@@ -25641,7 +25644,7 @@
         <v>28</v>
       </c>
       <c r="L473">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M473">
         <v>90</v>
@@ -25694,7 +25697,7 @@
         <v>28</v>
       </c>
       <c r="L474">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M474">
         <v>0</v>
@@ -25747,7 +25750,7 @@
         <v>28</v>
       </c>
       <c r="L475">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M475">
         <v>82</v>
@@ -25800,7 +25803,7 @@
         <v>28</v>
       </c>
       <c r="L476">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M476">
         <v>0</v>
@@ -25853,7 +25856,7 @@
         <v>28</v>
       </c>
       <c r="L477">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M477">
         <v>82</v>
@@ -25903,7 +25906,7 @@
         <v>28</v>
       </c>
       <c r="L478">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M478">
         <v>91</v>
@@ -25953,7 +25956,7 @@
         <v>19</v>
       </c>
       <c r="L479">
-        <v>2468.71</v>
+        <v>99999</v>
       </c>
       <c r="M479">
         <v>22</v>
@@ -26003,7 +26006,7 @@
         <v>19</v>
       </c>
       <c r="L480">
-        <v>2468.71</v>
+        <v>99999</v>
       </c>
       <c r="M480">
         <v>27</v>
@@ -26053,7 +26056,7 @@
         <v>6</v>
       </c>
       <c r="L481">
-        <v>4262.6899000000003</v>
+        <v>99999</v>
       </c>
       <c r="M481">
         <v>0</v>
@@ -26103,7 +26106,7 @@
         <v>6</v>
       </c>
       <c r="L482">
-        <v>4262.6899000000003</v>
+        <v>99999</v>
       </c>
       <c r="M482">
         <v>0</v>
@@ -26153,7 +26156,7 @@
         <v>21</v>
       </c>
       <c r="L483">
-        <v>1549</v>
+        <v>99999</v>
       </c>
       <c r="M483">
         <v>0</v>
@@ -26203,7 +26206,7 @@
         <v>21</v>
       </c>
       <c r="L484">
-        <v>1549</v>
+        <v>99999</v>
       </c>
       <c r="M484">
         <v>0</v>
@@ -26253,7 +26256,7 @@
         <v>6</v>
       </c>
       <c r="L485">
-        <v>4262.6899000000003</v>
+        <v>99999</v>
       </c>
       <c r="M485">
         <v>0</v>
@@ -26303,7 +26306,7 @@
         <v>6</v>
       </c>
       <c r="L486">
-        <v>4262.6899000000003</v>
+        <v>99999</v>
       </c>
       <c r="M486">
         <v>0</v>
@@ -26353,7 +26356,7 @@
         <v>21</v>
       </c>
       <c r="L487">
-        <v>1549</v>
+        <v>99999</v>
       </c>
       <c r="M487">
         <v>0</v>
@@ -26403,7 +26406,7 @@
         <v>21</v>
       </c>
       <c r="L488">
-        <v>1549</v>
+        <v>99999</v>
       </c>
       <c r="M488">
         <v>0</v>
@@ -26453,7 +26456,7 @@
         <v>19</v>
       </c>
       <c r="L489">
-        <v>1791.03</v>
+        <v>99999</v>
       </c>
       <c r="M489">
         <v>34</v>
@@ -26503,7 +26506,7 @@
         <v>19</v>
       </c>
       <c r="L490">
-        <v>1791.03</v>
+        <v>99999</v>
       </c>
       <c r="M490">
         <v>52</v>
@@ -26553,7 +26556,7 @@
         <v>28</v>
       </c>
       <c r="L491">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M491">
         <v>0</v>
@@ -26603,7 +26606,7 @@
         <v>28</v>
       </c>
       <c r="L492">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M492">
         <v>0</v>
@@ -26653,7 +26656,7 @@
         <v>19</v>
       </c>
       <c r="L493">
-        <v>2468.71</v>
+        <v>99999</v>
       </c>
       <c r="M493">
         <v>637</v>
@@ -26706,7 +26709,7 @@
         <v>19</v>
       </c>
       <c r="L494">
-        <v>2468.71</v>
+        <v>99999</v>
       </c>
       <c r="M494">
         <v>0</v>
@@ -26759,7 +26762,7 @@
         <v>19</v>
       </c>
       <c r="L495">
-        <v>2468.71</v>
+        <v>99999</v>
       </c>
       <c r="M495">
         <v>637</v>
@@ -26809,7 +26812,7 @@
         <v>19</v>
       </c>
       <c r="L496">
-        <v>2468.71</v>
+        <v>99999</v>
       </c>
       <c r="M496">
         <v>631</v>
@@ -26859,7 +26862,7 @@
         <v>14</v>
       </c>
       <c r="L497">
-        <v>3727.27</v>
+        <v>99999</v>
       </c>
       <c r="M497">
         <v>83</v>
@@ -26909,7 +26912,7 @@
         <v>14</v>
       </c>
       <c r="L498">
-        <v>3727.27</v>
+        <v>99999</v>
       </c>
       <c r="M498">
         <v>86</v>
@@ -26959,7 +26962,7 @@
         <v>26</v>
       </c>
       <c r="L499">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M499">
         <v>2130</v>
@@ -27012,7 +27015,7 @@
         <v>26</v>
       </c>
       <c r="L500">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M500">
         <v>0</v>
@@ -27065,7 +27068,7 @@
         <v>26</v>
       </c>
       <c r="L501">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M501">
         <v>1967</v>
@@ -27118,7 +27121,7 @@
         <v>26</v>
       </c>
       <c r="L502">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M502">
         <v>0</v>
@@ -27171,7 +27174,7 @@
         <v>26</v>
       </c>
       <c r="L503">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M503">
         <v>1967</v>
@@ -27221,7 +27224,7 @@
         <v>26</v>
       </c>
       <c r="L504">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M504">
         <v>1721</v>
@@ -27271,7 +27274,7 @@
         <v>25</v>
       </c>
       <c r="L505">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M505">
         <v>1221</v>
@@ -27324,7 +27327,7 @@
         <v>25</v>
       </c>
       <c r="L506">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M506">
         <v>0</v>
@@ -27377,7 +27380,7 @@
         <v>25</v>
       </c>
       <c r="L507">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M507">
         <v>1112</v>
@@ -27430,7 +27433,7 @@
         <v>25</v>
       </c>
       <c r="L508">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M508">
         <v>0</v>
@@ -27483,7 +27486,7 @@
         <v>25</v>
       </c>
       <c r="L509">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M509">
         <v>1112</v>
@@ -27533,7 +27536,7 @@
         <v>25</v>
       </c>
       <c r="L510">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M510">
         <v>1220</v>
@@ -27583,7 +27586,7 @@
         <v>19</v>
       </c>
       <c r="L511">
-        <v>1791.03</v>
+        <v>99999</v>
       </c>
       <c r="M511">
         <v>15</v>
@@ -27633,7 +27636,7 @@
         <v>19</v>
       </c>
       <c r="L512">
-        <v>1791.03</v>
+        <v>99999</v>
       </c>
       <c r="M512">
         <v>10</v>
@@ -27683,7 +27686,7 @@
         <v>14</v>
       </c>
       <c r="L513">
-        <v>3081.46</v>
+        <v>99999</v>
       </c>
       <c r="M513">
         <v>5</v>
@@ -27733,7 +27736,7 @@
         <v>14</v>
       </c>
       <c r="L514">
-        <v>3081.46</v>
+        <v>99999</v>
       </c>
       <c r="M514">
         <v>2</v>
@@ -27783,7 +27786,7 @@
         <v>14</v>
       </c>
       <c r="L515">
-        <v>3001.1799000000001</v>
+        <v>99999</v>
       </c>
       <c r="M515">
         <v>0</v>
@@ -27833,7 +27836,7 @@
         <v>14</v>
       </c>
       <c r="L516">
-        <v>3001.1799000000001</v>
+        <v>99999</v>
       </c>
       <c r="M516">
         <v>0</v>
@@ -27883,7 +27886,7 @@
         <v>9</v>
       </c>
       <c r="L517">
-        <v>4598.5801000000001</v>
+        <v>99999</v>
       </c>
       <c r="M517">
         <v>41</v>
@@ -27933,7 +27936,7 @@
         <v>9</v>
       </c>
       <c r="L518">
-        <v>4598.5801000000001</v>
+        <v>99999</v>
       </c>
       <c r="M518">
         <v>56</v>
@@ -27983,7 +27986,7 @@
         <v>27</v>
       </c>
       <c r="L519">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M519">
         <v>675</v>
@@ -28036,7 +28039,7 @@
         <v>27</v>
       </c>
       <c r="L520">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M520">
         <v>0</v>
@@ -28089,7 +28092,7 @@
         <v>27</v>
       </c>
       <c r="L521">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M521">
         <v>611</v>
@@ -28139,7 +28142,7 @@
         <v>27</v>
       </c>
       <c r="L522">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M522">
         <v>648</v>
@@ -28189,7 +28192,7 @@
         <v>18</v>
       </c>
       <c r="L523">
-        <v>2468.71</v>
+        <v>99999</v>
       </c>
       <c r="M523">
         <v>126</v>
@@ -28239,7 +28242,7 @@
         <v>18</v>
       </c>
       <c r="L524">
-        <v>2468.71</v>
+        <v>99999</v>
       </c>
       <c r="M524">
         <v>141</v>
@@ -28289,7 +28292,7 @@
         <v>12</v>
       </c>
       <c r="L525">
-        <v>3630.46</v>
+        <v>99999</v>
       </c>
       <c r="M525">
         <v>26</v>
@@ -28339,7 +28342,7 @@
         <v>12</v>
       </c>
       <c r="L526">
-        <v>3630.46</v>
+        <v>99999</v>
       </c>
       <c r="M526">
         <v>24</v>
@@ -28389,7 +28392,7 @@
         <v>24</v>
       </c>
       <c r="L527">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M527">
         <v>566</v>
@@ -28442,7 +28445,7 @@
         <v>24</v>
       </c>
       <c r="L528">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M528">
         <v>0</v>
@@ -28495,7 +28498,7 @@
         <v>24</v>
       </c>
       <c r="L529">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M529">
         <v>513</v>
@@ -28545,7 +28548,7 @@
         <v>24</v>
       </c>
       <c r="L530">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M530">
         <v>517</v>
@@ -28595,7 +28598,7 @@
         <v>60</v>
       </c>
       <c r="L531">
-        <v>1151.1199999999999</v>
+        <v>99999</v>
       </c>
       <c r="M531">
         <v>4</v>
@@ -28645,7 +28648,7 @@
         <v>60</v>
       </c>
       <c r="L532">
-        <v>1151.1199999999999</v>
+        <v>99999</v>
       </c>
       <c r="M532">
         <v>3</v>
@@ -28695,7 +28698,7 @@
         <v>24</v>
       </c>
       <c r="L533">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M533">
         <v>160</v>
@@ -28745,7 +28748,7 @@
         <v>24</v>
       </c>
       <c r="L534">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M534">
         <v>148</v>
@@ -28795,7 +28798,7 @@
         <v>66</v>
       </c>
       <c r="L535">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M535">
         <v>31</v>
@@ -28845,7 +28848,7 @@
         <v>66</v>
       </c>
       <c r="L536">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M536">
         <v>26</v>
@@ -28895,7 +28898,7 @@
         <v>40</v>
       </c>
       <c r="L537">
-        <v>1151.1199999999999</v>
+        <v>99999</v>
       </c>
       <c r="M537">
         <v>5</v>
@@ -28945,7 +28948,7 @@
         <v>40</v>
       </c>
       <c r="L538">
-        <v>1151.1199999999999</v>
+        <v>99999</v>
       </c>
       <c r="M538">
         <v>3</v>
@@ -28995,7 +28998,7 @@
         <v>40</v>
       </c>
       <c r="L539">
-        <v>1151.1199999999999</v>
+        <v>99999</v>
       </c>
       <c r="M539">
         <v>3</v>
@@ -29045,7 +29048,7 @@
         <v>40</v>
       </c>
       <c r="L540">
-        <v>1151.1199999999999</v>
+        <v>99999</v>
       </c>
       <c r="M540">
         <v>1</v>
@@ -29095,7 +29098,7 @@
         <v>17</v>
       </c>
       <c r="L541">
-        <v>3001.1799000000001</v>
+        <v>99999</v>
       </c>
       <c r="M541">
         <v>0</v>
@@ -29145,7 +29148,7 @@
         <v>17</v>
       </c>
       <c r="L542">
-        <v>3001.1799000000001</v>
+        <v>99999</v>
       </c>
       <c r="M542">
         <v>0</v>
@@ -29195,7 +29198,7 @@
         <v>40</v>
       </c>
       <c r="L543">
-        <v>1519.48</v>
+        <v>99999</v>
       </c>
       <c r="M543">
         <v>7</v>
@@ -29245,7 +29248,7 @@
         <v>40</v>
       </c>
       <c r="L544">
-        <v>1519.48</v>
+        <v>99999</v>
       </c>
       <c r="M544">
         <v>5</v>
@@ -29295,7 +29298,7 @@
         <v>64</v>
       </c>
       <c r="L545">
-        <v>966.94</v>
+        <v>99999</v>
       </c>
       <c r="M545">
         <v>4</v>
@@ -29345,7 +29348,7 @@
         <v>64</v>
       </c>
       <c r="L546">
-        <v>966.94</v>
+        <v>99999</v>
       </c>
       <c r="M546">
         <v>3</v>
@@ -29395,7 +29398,7 @@
         <v>10</v>
       </c>
       <c r="L547">
-        <v>2978.75</v>
+        <v>99999</v>
       </c>
       <c r="M547">
         <v>21</v>
@@ -29445,7 +29448,7 @@
         <v>10</v>
       </c>
       <c r="L548">
-        <v>2978.75</v>
+        <v>99999</v>
       </c>
       <c r="M548">
         <v>18</v>
@@ -29495,7 +29498,7 @@
         <v>14</v>
       </c>
       <c r="L549">
-        <v>3081.46</v>
+        <v>99999</v>
       </c>
       <c r="M549">
         <v>25</v>
@@ -29545,7 +29548,7 @@
         <v>14</v>
       </c>
       <c r="L550">
-        <v>3081.46</v>
+        <v>99999</v>
       </c>
       <c r="M550">
         <v>20</v>
@@ -29595,7 +29598,7 @@
         <v>29</v>
       </c>
       <c r="L551">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M551">
         <v>127</v>
@@ -29648,7 +29651,7 @@
         <v>29</v>
       </c>
       <c r="L552">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M552">
         <v>0</v>
@@ -29701,7 +29704,7 @@
         <v>29</v>
       </c>
       <c r="L553">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M553">
         <v>116</v>
@@ -29751,7 +29754,7 @@
         <v>29</v>
       </c>
       <c r="L554">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M554">
         <v>88</v>
@@ -29801,7 +29804,7 @@
         <v>30</v>
       </c>
       <c r="L555">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M555">
         <v>379</v>
@@ -29854,7 +29857,7 @@
         <v>30</v>
       </c>
       <c r="L556">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M556">
         <v>0</v>
@@ -29907,7 +29910,7 @@
         <v>30</v>
       </c>
       <c r="L557">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M557">
         <v>373</v>
@@ -29957,7 +29960,7 @@
         <v>30</v>
       </c>
       <c r="L558">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M558">
         <v>320</v>
@@ -30007,7 +30010,7 @@
         <v>30</v>
       </c>
       <c r="L559">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M559">
         <v>525</v>
@@ -30060,7 +30063,7 @@
         <v>30</v>
       </c>
       <c r="L560">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M560">
         <v>0</v>
@@ -30113,7 +30116,7 @@
         <v>30</v>
       </c>
       <c r="L561">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M561">
         <v>484</v>
@@ -30163,7 +30166,7 @@
         <v>30</v>
       </c>
       <c r="L562">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M562">
         <v>471</v>
@@ -30213,7 +30216,7 @@
         <v>112</v>
       </c>
       <c r="L563">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M563">
         <v>33</v>
@@ -30263,7 +30266,7 @@
         <v>112</v>
       </c>
       <c r="L564">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M564">
         <v>53</v>
@@ -30313,7 +30316,7 @@
         <v>112</v>
       </c>
       <c r="L565">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M565">
         <v>74</v>
@@ -30363,7 +30366,7 @@
         <v>112</v>
       </c>
       <c r="L566">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M566">
         <v>89</v>
@@ -30413,7 +30416,7 @@
         <v>64</v>
       </c>
       <c r="L567">
-        <v>966.94</v>
+        <v>99999</v>
       </c>
       <c r="M567">
         <v>17</v>
@@ -30463,7 +30466,7 @@
         <v>64</v>
       </c>
       <c r="L568">
-        <v>966.94</v>
+        <v>99999</v>
       </c>
       <c r="M568">
         <v>21</v>
@@ -30513,7 +30516,7 @@
         <v>40</v>
       </c>
       <c r="L569">
-        <v>1519.48</v>
+        <v>99999</v>
       </c>
       <c r="M569">
         <v>0</v>
@@ -30563,7 +30566,7 @@
         <v>40</v>
       </c>
       <c r="L570">
-        <v>1519.48</v>
+        <v>99999</v>
       </c>
       <c r="M570">
         <v>0</v>
@@ -30613,7 +30616,7 @@
         <v>88</v>
       </c>
       <c r="L571">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M571">
         <v>0</v>
@@ -30663,7 +30666,7 @@
         <v>88</v>
       </c>
       <c r="L572">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M572">
         <v>0</v>
@@ -30713,7 +30716,7 @@
         <v>38</v>
       </c>
       <c r="L573">
-        <v>1289.26</v>
+        <v>99999</v>
       </c>
       <c r="M573">
         <v>267</v>
@@ -30763,7 +30766,7 @@
         <v>38</v>
       </c>
       <c r="L574">
-        <v>1289.26</v>
+        <v>99999</v>
       </c>
       <c r="M574">
         <v>247</v>
@@ -30813,7 +30816,7 @@
         <v>110</v>
       </c>
       <c r="L575">
-        <v>796.93</v>
+        <v>99999</v>
       </c>
       <c r="M575">
         <v>94</v>
@@ -30866,7 +30869,7 @@
         <v>110</v>
       </c>
       <c r="L576">
-        <v>796.93</v>
+        <v>99999</v>
       </c>
       <c r="M576">
         <v>0</v>
@@ -30919,7 +30922,7 @@
         <v>110</v>
       </c>
       <c r="L577">
-        <v>796.93</v>
+        <v>99999</v>
       </c>
       <c r="M577">
         <v>87</v>
@@ -30972,7 +30975,7 @@
         <v>110</v>
       </c>
       <c r="L578">
-        <v>796.93</v>
+        <v>99999</v>
       </c>
       <c r="M578">
         <v>0</v>
@@ -31025,7 +31028,7 @@
         <v>110</v>
       </c>
       <c r="L579">
-        <v>796.93</v>
+        <v>99999</v>
       </c>
       <c r="M579">
         <v>82</v>
@@ -31075,7 +31078,7 @@
         <v>110</v>
       </c>
       <c r="L580">
-        <v>796.93</v>
+        <v>99999</v>
       </c>
       <c r="M580">
         <v>69</v>
@@ -31125,7 +31128,7 @@
         <v>88</v>
       </c>
       <c r="L581">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M581">
         <v>49</v>
@@ -31175,7 +31178,7 @@
         <v>88</v>
       </c>
       <c r="L582">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M582">
         <v>48</v>
@@ -31225,7 +31228,7 @@
         <v>25</v>
       </c>
       <c r="L583">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M583">
         <v>63</v>
@@ -31278,7 +31281,7 @@
         <v>25</v>
       </c>
       <c r="L584">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M584">
         <v>0</v>
@@ -31331,7 +31334,7 @@
         <v>25</v>
       </c>
       <c r="L585">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M585">
         <v>55</v>
@@ -31384,7 +31387,7 @@
         <v>25</v>
       </c>
       <c r="L586">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M586">
         <v>0</v>
@@ -31437,7 +31440,7 @@
         <v>25</v>
       </c>
       <c r="L587">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M587">
         <v>55</v>
@@ -31487,7 +31490,7 @@
         <v>25</v>
       </c>
       <c r="L588">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M588">
         <v>78</v>
@@ -31537,7 +31540,7 @@
         <v>22</v>
       </c>
       <c r="L589">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M589">
         <v>150</v>
@@ -31590,7 +31593,7 @@
         <v>22</v>
       </c>
       <c r="L590">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M590">
         <v>0</v>
@@ -31643,7 +31646,7 @@
         <v>22</v>
       </c>
       <c r="L591">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M591">
         <v>127</v>
@@ -31696,7 +31699,7 @@
         <v>22</v>
       </c>
       <c r="L592">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M592">
         <v>0</v>
@@ -31749,7 +31752,7 @@
         <v>22</v>
       </c>
       <c r="L593">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M593">
         <v>127</v>
@@ -31799,7 +31802,7 @@
         <v>22</v>
       </c>
       <c r="L594">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M594">
         <v>207</v>
@@ -31849,7 +31852,7 @@
         <v>9</v>
       </c>
       <c r="L595">
-        <v>5033.0600999999997</v>
+        <v>99999</v>
       </c>
       <c r="M595">
         <v>351</v>
@@ -31899,7 +31902,7 @@
         <v>9</v>
       </c>
       <c r="L596">
-        <v>5033.0600999999997</v>
+        <v>99999</v>
       </c>
       <c r="M596">
         <v>537</v>
@@ -31949,7 +31952,7 @@
         <v>22</v>
       </c>
       <c r="L597">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M597">
         <v>44</v>
@@ -32002,7 +32005,7 @@
         <v>22</v>
       </c>
       <c r="L598">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M598">
         <v>0</v>
@@ -32055,7 +32058,7 @@
         <v>22</v>
       </c>
       <c r="L599">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M599">
         <v>36</v>
@@ -32105,7 +32108,7 @@
         <v>22</v>
       </c>
       <c r="L600">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M600">
         <v>53</v>
@@ -32155,7 +32158,7 @@
         <v>9</v>
       </c>
       <c r="L601">
-        <v>5033.0600999999997</v>
+        <v>99999</v>
       </c>
       <c r="M601">
         <v>25</v>
@@ -32205,7 +32208,7 @@
         <v>9</v>
       </c>
       <c r="L602">
-        <v>5033.0600999999997</v>
+        <v>99999</v>
       </c>
       <c r="M602">
         <v>10</v>
@@ -32255,7 +32258,7 @@
         <v>25</v>
       </c>
       <c r="L603">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M603">
         <v>51</v>
@@ -32308,7 +32311,7 @@
         <v>25</v>
       </c>
       <c r="L604">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M604">
         <v>0</v>
@@ -32361,7 +32364,7 @@
         <v>25</v>
       </c>
       <c r="L605">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M605">
         <v>45</v>
@@ -32414,7 +32417,7 @@
         <v>25</v>
       </c>
       <c r="L606">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M606">
         <v>0</v>
@@ -32467,7 +32470,7 @@
         <v>25</v>
       </c>
       <c r="L607">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M607">
         <v>45</v>
@@ -32517,7 +32520,7 @@
         <v>25</v>
       </c>
       <c r="L608">
-        <v>1210.1500000000001</v>
+        <v>99999</v>
       </c>
       <c r="M608">
         <v>35</v>
@@ -32567,7 +32570,7 @@
         <v>100</v>
       </c>
       <c r="L609">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M609">
         <v>1</v>
@@ -32617,7 +32620,7 @@
         <v>100</v>
       </c>
       <c r="L610">
-        <v>487.01</v>
+        <v>99999</v>
       </c>
       <c r="M610">
         <v>1</v>
@@ -32667,7 +32670,7 @@
         <v>25</v>
       </c>
       <c r="L611">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M611">
         <v>0</v>
@@ -32717,7 +32720,7 @@
         <v>25</v>
       </c>
       <c r="L612">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M612">
         <v>0</v>
@@ -32767,7 +32770,7 @@
         <v>72</v>
       </c>
       <c r="L613">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M613">
         <v>0</v>
@@ -32817,7 +32820,7 @@
         <v>72</v>
       </c>
       <c r="L614">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M614">
         <v>0</v>
@@ -32867,7 +32870,7 @@
         <v>25</v>
       </c>
       <c r="L615">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M615">
         <v>53</v>
@@ -32917,7 +32920,7 @@
         <v>25</v>
       </c>
       <c r="L616">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M616">
         <v>38</v>
@@ -32967,7 +32970,7 @@
         <v>38</v>
       </c>
       <c r="L617">
-        <v>1289.26</v>
+        <v>99999</v>
       </c>
       <c r="M617">
         <v>107</v>
@@ -33020,7 +33023,7 @@
         <v>38</v>
       </c>
       <c r="L618">
-        <v>1289.26</v>
+        <v>99999</v>
       </c>
       <c r="M618">
         <v>0</v>
@@ -33073,7 +33076,7 @@
         <v>38</v>
       </c>
       <c r="L619">
-        <v>1289.26</v>
+        <v>99999</v>
       </c>
       <c r="M619">
         <v>107</v>
@@ -33123,7 +33126,7 @@
         <v>38</v>
       </c>
       <c r="L620">
-        <v>1289.26</v>
+        <v>99999</v>
       </c>
       <c r="M620">
         <v>82</v>
@@ -33173,7 +33176,7 @@
         <v>110</v>
       </c>
       <c r="L621">
-        <v>796.93</v>
+        <v>99999</v>
       </c>
       <c r="M621">
         <v>28</v>
@@ -33226,7 +33229,7 @@
         <v>110</v>
       </c>
       <c r="L622">
-        <v>796.93</v>
+        <v>99999</v>
       </c>
       <c r="M622">
         <v>0</v>
@@ -33279,7 +33282,7 @@
         <v>110</v>
       </c>
       <c r="L623">
-        <v>796.93</v>
+        <v>99999</v>
       </c>
       <c r="M623">
         <v>26</v>
@@ -33329,7 +33332,7 @@
         <v>110</v>
       </c>
       <c r="L624">
-        <v>796.93</v>
+        <v>99999</v>
       </c>
       <c r="M624">
         <v>21</v>
@@ -33379,7 +33382,7 @@
         <v>25</v>
       </c>
       <c r="L625">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M625">
         <v>120</v>
@@ -33429,7 +33432,7 @@
         <v>25</v>
       </c>
       <c r="L626">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M626">
         <v>90</v>
@@ -33479,7 +33482,7 @@
         <v>25</v>
       </c>
       <c r="L627">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M627">
         <v>142</v>
@@ -33529,7 +33532,7 @@
         <v>25</v>
       </c>
       <c r="L628">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M628">
         <v>139</v>
@@ -33579,7 +33582,7 @@
         <v>25</v>
       </c>
       <c r="L629">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M629">
         <v>427</v>
@@ -33629,7 +33632,7 @@
         <v>25</v>
       </c>
       <c r="L630">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M630">
         <v>374</v>
@@ -33679,7 +33682,7 @@
         <v>18</v>
       </c>
       <c r="L631">
-        <v>2468.71</v>
+        <v>99999</v>
       </c>
       <c r="M631">
         <v>396</v>
@@ -33729,7 +33732,7 @@
         <v>18</v>
       </c>
       <c r="L632">
-        <v>2468.71</v>
+        <v>99999</v>
       </c>
       <c r="M632">
         <v>448</v>
@@ -33779,7 +33782,7 @@
         <v>13</v>
       </c>
       <c r="L633">
-        <v>3727.27</v>
+        <v>99999</v>
       </c>
       <c r="M633">
         <v>54</v>
@@ -33832,7 +33835,7 @@
         <v>13</v>
       </c>
       <c r="L634">
-        <v>3727.27</v>
+        <v>99999</v>
       </c>
       <c r="M634">
         <v>0</v>
@@ -33885,7 +33888,7 @@
         <v>13</v>
       </c>
       <c r="L635">
-        <v>3727.27</v>
+        <v>99999</v>
       </c>
       <c r="M635">
         <v>33</v>
@@ -33935,7 +33938,7 @@
         <v>13</v>
       </c>
       <c r="L636">
-        <v>3727.27</v>
+        <v>99999</v>
       </c>
       <c r="M636">
         <v>32</v>
@@ -33985,7 +33988,7 @@
         <v>25</v>
       </c>
       <c r="L637">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M637">
         <v>418</v>
@@ -34038,7 +34041,7 @@
         <v>25</v>
       </c>
       <c r="L638">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M638">
         <v>0</v>
@@ -34091,7 +34094,7 @@
         <v>25</v>
       </c>
       <c r="L639">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M639">
         <v>391</v>
@@ -34141,7 +34144,7 @@
         <v>25</v>
       </c>
       <c r="L640">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M640">
         <v>344</v>
@@ -34191,7 +34194,7 @@
         <v>10</v>
       </c>
       <c r="L641">
-        <v>2922.0801000000001</v>
+        <v>99999</v>
       </c>
       <c r="M641">
         <v>0</v>
@@ -34241,7 +34244,7 @@
         <v>10</v>
       </c>
       <c r="L642">
-        <v>2922.0801000000001</v>
+        <v>99999</v>
       </c>
       <c r="M642">
         <v>0</v>
@@ -34291,7 +34294,7 @@
         <v>10</v>
       </c>
       <c r="L643">
-        <v>2922.0801000000001</v>
+        <v>99999</v>
       </c>
       <c r="M643">
         <v>11</v>
@@ -34341,7 +34344,7 @@
         <v>10</v>
       </c>
       <c r="L644">
-        <v>2922.0801000000001</v>
+        <v>99999</v>
       </c>
       <c r="M644">
         <v>1</v>
@@ -34391,7 +34394,7 @@
         <v>36</v>
       </c>
       <c r="L645">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M645">
         <v>30</v>
@@ -34441,7 +34444,7 @@
         <v>36</v>
       </c>
       <c r="L646">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M646">
         <v>23</v>
@@ -34491,7 +34494,7 @@
         <v>12</v>
       </c>
       <c r="L647">
-        <v>1742.62</v>
+        <v>99999</v>
       </c>
       <c r="M647">
         <v>20</v>
@@ -34541,7 +34544,7 @@
         <v>12</v>
       </c>
       <c r="L648">
-        <v>1742.62</v>
+        <v>99999</v>
       </c>
       <c r="M648">
         <v>24</v>
@@ -34591,7 +34594,7 @@
         <v>12</v>
       </c>
       <c r="L649">
-        <v>1742.62</v>
+        <v>99999</v>
       </c>
       <c r="M649">
         <v>20</v>
@@ -34641,7 +34644,7 @@
         <v>12</v>
       </c>
       <c r="L650">
-        <v>1742.62</v>
+        <v>99999</v>
       </c>
       <c r="M650">
         <v>15</v>
@@ -34691,7 +34694,7 @@
         <v>20</v>
       </c>
       <c r="L651">
-        <v>1064.9399000000001</v>
+        <v>99999</v>
       </c>
       <c r="M651">
         <v>3</v>
@@ -34741,7 +34744,7 @@
         <v>20</v>
       </c>
       <c r="L652">
-        <v>1064.9399000000001</v>
+        <v>99999</v>
       </c>
       <c r="M652">
         <v>0</v>
@@ -34791,7 +34794,7 @@
         <v>10</v>
       </c>
       <c r="L653">
-        <v>1742.62</v>
+        <v>99999</v>
       </c>
       <c r="M653">
         <v>44</v>
@@ -34841,7 +34844,7 @@
         <v>10</v>
       </c>
       <c r="L654">
-        <v>1742.62</v>
+        <v>99999</v>
       </c>
       <c r="M654">
         <v>53</v>
@@ -34891,7 +34894,7 @@
         <v>20</v>
       </c>
       <c r="L655">
-        <v>1064.9399000000001</v>
+        <v>99999</v>
       </c>
       <c r="M655">
         <v>52</v>
@@ -34941,7 +34944,7 @@
         <v>20</v>
       </c>
       <c r="L656">
-        <v>1064.9399000000001</v>
+        <v>99999</v>
       </c>
       <c r="M656">
         <v>90</v>
@@ -34991,7 +34994,7 @@
         <v>15</v>
       </c>
       <c r="L657">
-        <v>3049.5900999999999</v>
+        <v>99999</v>
       </c>
       <c r="M657">
         <v>9</v>
@@ -35041,7 +35044,7 @@
         <v>15</v>
       </c>
       <c r="L658">
-        <v>3049.5900999999999</v>
+        <v>99999</v>
       </c>
       <c r="M658">
         <v>35</v>
@@ -35091,7 +35094,7 @@
         <v>24</v>
       </c>
       <c r="L659">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M659">
         <v>159</v>
@@ -35144,7 +35147,7 @@
         <v>24</v>
       </c>
       <c r="L660">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M660">
         <v>0</v>
@@ -35197,7 +35200,7 @@
         <v>24</v>
       </c>
       <c r="L661">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M661">
         <v>147</v>
@@ -35247,7 +35250,7 @@
         <v>24</v>
       </c>
       <c r="L662">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M662">
         <v>152</v>
@@ -35297,7 +35300,7 @@
         <v>66</v>
       </c>
       <c r="L663">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M663">
         <v>33</v>
@@ -35347,7 +35350,7 @@
         <v>66</v>
       </c>
       <c r="L664">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M664">
         <v>31</v>
@@ -35397,7 +35400,7 @@
         <v>19</v>
       </c>
       <c r="L665">
-        <v>2468.71</v>
+        <v>99999</v>
       </c>
       <c r="M665">
         <v>23</v>
@@ -35447,7 +35450,7 @@
         <v>19</v>
       </c>
       <c r="L666">
-        <v>2468.71</v>
+        <v>99999</v>
       </c>
       <c r="M666">
         <v>49</v>
@@ -35497,7 +35500,7 @@
         <v>26</v>
       </c>
       <c r="L667">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M667">
         <v>93</v>
@@ -35550,7 +35553,7 @@
         <v>26</v>
       </c>
       <c r="L668">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M668">
         <v>0</v>
@@ -35603,7 +35606,7 @@
         <v>26</v>
       </c>
       <c r="L669">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M669">
         <v>84</v>
@@ -35653,7 +35656,7 @@
         <v>26</v>
       </c>
       <c r="L670">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M670">
         <v>104</v>
@@ -35703,7 +35706,7 @@
         <v>29</v>
       </c>
       <c r="L671">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M671">
         <v>337</v>
@@ -35753,7 +35756,7 @@
         <v>29</v>
       </c>
       <c r="L672">
-        <v>1611.5699</v>
+        <v>99999</v>
       </c>
       <c r="M672">
         <v>299</v>
@@ -35803,7 +35806,7 @@
         <v>88</v>
       </c>
       <c r="L673">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M673">
         <v>138</v>
@@ -35853,7 +35856,7 @@
         <v>88</v>
       </c>
       <c r="L674">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M674">
         <v>134</v>
@@ -35906,7 +35909,7 @@
         <v>88</v>
       </c>
       <c r="L675">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M675">
         <v>1</v>
@@ -35959,7 +35962,7 @@
         <v>88</v>
       </c>
       <c r="L676">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M676">
         <v>112</v>
@@ -35976,28 +35979,28 @@
     </row>
     <row r="677" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A677" s="1">
-        <v>46175</v>
+        <v>46185</v>
       </c>
       <c r="B677">
-        <v>300066500</v>
+        <v>300066262</v>
       </c>
       <c r="C677" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D677">
-        <v>0</v>
+        <v>-2200</v>
       </c>
       <c r="E677">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F677">
         <v>0</v>
       </c>
       <c r="G677" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H677" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I677">
         <v>0</v>
@@ -36006,72 +36009,78 @@
         <v>20</v>
       </c>
       <c r="K677">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="L677">
-        <v>9297.5195000000003</v>
+        <v>99999</v>
       </c>
       <c r="M677">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="N677">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="O677">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="P677">
-        <v>5</v>
+        <v>44</v>
+      </c>
+      <c r="Q677" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="678" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A678" s="1">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="B678">
-        <v>300066500</v>
+        <v>300066262</v>
       </c>
       <c r="C678" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D678">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E678">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F678">
         <v>0</v>
       </c>
       <c r="G678" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H678" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I678">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J678" t="s">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="K678">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="L678">
-        <v>9297.5195000000003</v>
+        <v>99999</v>
       </c>
       <c r="M678">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="N678">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="O678">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="P678">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="Q678" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="679" spans="1:17" x14ac:dyDescent="0.25">
@@ -36079,19 +36088,19 @@
         <v>46175</v>
       </c>
       <c r="B679">
-        <v>300066580</v>
+        <v>300066500</v>
       </c>
       <c r="C679" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D679">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="E679">
         <v>0</v>
       </c>
       <c r="F679">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="G679" t="s">
         <v>40</v>
@@ -36106,22 +36115,22 @@
         <v>20</v>
       </c>
       <c r="K679">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="L679">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M679">
-        <v>492</v>
+        <v>3</v>
       </c>
       <c r="N679">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="O679">
-        <v>492</v>
+        <v>3</v>
       </c>
       <c r="P679">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="680" spans="1:17" x14ac:dyDescent="0.25">
@@ -36129,19 +36138,19 @@
         <v>46182</v>
       </c>
       <c r="B680">
-        <v>300066580</v>
+        <v>300066500</v>
       </c>
       <c r="C680" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D680">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="E680">
         <v>0</v>
       </c>
       <c r="F680">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="G680" t="s">
         <v>40</v>
@@ -36156,133 +36165,127 @@
         <v>20</v>
       </c>
       <c r="K680">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="L680">
-        <v>1427.39</v>
+        <v>99999</v>
       </c>
       <c r="M680">
-        <v>453</v>
+        <v>3</v>
       </c>
       <c r="N680">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O680">
-        <v>452</v>
+        <v>3</v>
       </c>
       <c r="P680">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="681" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A681" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B681">
-        <v>300066581</v>
+        <v>300066580</v>
       </c>
       <c r="C681" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D681">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E681">
         <v>0</v>
       </c>
       <c r="F681">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="G681" t="s">
+        <v>40</v>
+      </c>
+      <c r="H681" t="s">
+        <v>41</v>
+      </c>
+      <c r="I681">
+        <v>0</v>
+      </c>
+      <c r="J681" t="s">
+        <v>20</v>
+      </c>
+      <c r="K681">
+        <v>25</v>
+      </c>
+      <c r="L681">
+        <v>99999</v>
+      </c>
+      <c r="M681">
+        <v>492</v>
+      </c>
+      <c r="N681">
         <v>23</v>
       </c>
-      <c r="H681" t="s">
-        <v>123</v>
-      </c>
-      <c r="I681">
-        <v>0</v>
-      </c>
-      <c r="J681" t="s">
-        <v>20</v>
-      </c>
-      <c r="K681">
-        <v>72</v>
-      </c>
-      <c r="L681">
-        <v>929.75</v>
-      </c>
-      <c r="M681">
-        <v>31</v>
-      </c>
-      <c r="N681">
-        <v>20</v>
-      </c>
       <c r="O681">
-        <v>31</v>
+        <v>492</v>
       </c>
       <c r="P681">
-        <v>16</v>
-      </c>
-      <c r="Q681" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
     </row>
     <row r="682" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A682" s="1">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="B682">
-        <v>300066581</v>
+        <v>300066580</v>
       </c>
       <c r="C682" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D682">
-        <v>4</v>
+        <v>-19</v>
       </c>
       <c r="E682">
         <v>0</v>
       </c>
       <c r="F682">
-        <v>4</v>
+        <v>-19</v>
       </c>
       <c r="G682" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H682" t="s">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="I682">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J682" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="K682">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="L682">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M682">
-        <v>0</v>
+        <v>453</v>
       </c>
       <c r="N682">
         <v>2</v>
       </c>
       <c r="O682">
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="P682">
-        <v>6</v>
-      </c>
-      <c r="Q682" t="s">
-        <v>124</v>
+        <v>8</v>
       </c>
     </row>
     <row r="683" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A683" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B683">
         <v>300066581</v>
@@ -36291,19 +36294,19 @@
         <v>219</v>
       </c>
       <c r="D683">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="E683">
         <v>0</v>
       </c>
       <c r="F683">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="G683" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H683" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="I683">
         <v>0</v>
@@ -36315,24 +36318,27 @@
         <v>72</v>
       </c>
       <c r="L683">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M683">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N683">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="O683">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P683">
-        <v>40</v>
+        <v>16</v>
+      </c>
+      <c r="Q683" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="684" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A684" s="1">
-        <v>46182</v>
+        <v>46174</v>
       </c>
       <c r="B684">
         <v>300066581</v>
@@ -36341,43 +36347,46 @@
         <v>219</v>
       </c>
       <c r="D684">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E684">
         <v>0</v>
       </c>
       <c r="F684">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G684" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H684" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="I684">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J684" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="K684">
         <v>72</v>
       </c>
       <c r="L684">
-        <v>929.75</v>
+        <v>99999</v>
       </c>
       <c r="M684">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="N684">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O684">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="P684">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="Q684" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="685" spans="1:17" x14ac:dyDescent="0.25">
@@ -36385,19 +36394,19 @@
         <v>46175</v>
       </c>
       <c r="B685">
-        <v>300066598</v>
+        <v>300066581</v>
       </c>
       <c r="C685" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D685">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E685">
         <v>0</v>
       </c>
       <c r="F685">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G685" t="s">
         <v>40</v>
@@ -36412,22 +36421,22 @@
         <v>20</v>
       </c>
       <c r="K685">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="L685">
-        <v>9297.5195000000003</v>
+        <v>99999</v>
       </c>
       <c r="M685">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="N685">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="O685">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="P685">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="686" spans="1:17" x14ac:dyDescent="0.25">
@@ -36435,19 +36444,19 @@
         <v>46182</v>
       </c>
       <c r="B686">
-        <v>300066598</v>
+        <v>300066581</v>
       </c>
       <c r="C686" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D686">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E686">
         <v>0</v>
       </c>
       <c r="F686">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G686" t="s">
         <v>40</v>
@@ -36462,71 +36471,171 @@
         <v>20</v>
       </c>
       <c r="K686">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="L686">
-        <v>9297.5195000000003</v>
+        <v>99999</v>
       </c>
       <c r="M686">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="N686">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O686">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="P686">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="687" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A687" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B687">
+        <v>300066598</v>
+      </c>
+      <c r="C687" t="s">
+        <v>220</v>
+      </c>
+      <c r="D687">
+        <v>2</v>
+      </c>
+      <c r="E687">
+        <v>0</v>
+      </c>
+      <c r="F687">
+        <v>2</v>
+      </c>
+      <c r="G687" t="s">
+        <v>40</v>
+      </c>
+      <c r="H687" t="s">
+        <v>41</v>
+      </c>
+      <c r="I687">
+        <v>0</v>
+      </c>
+      <c r="J687" t="s">
+        <v>20</v>
+      </c>
+      <c r="K687">
+        <v>6</v>
+      </c>
+      <c r="L687">
+        <v>99999</v>
+      </c>
+      <c r="M687">
+        <v>10</v>
+      </c>
+      <c r="N687">
+        <v>2</v>
+      </c>
+      <c r="O687">
+        <v>10</v>
+      </c>
+      <c r="P687">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="688" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A688" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B688">
+        <v>300066598</v>
+      </c>
+      <c r="C688" t="s">
+        <v>220</v>
+      </c>
+      <c r="D688">
+        <v>0</v>
+      </c>
+      <c r="E688">
+        <v>0</v>
+      </c>
+      <c r="F688">
+        <v>0</v>
+      </c>
+      <c r="G688" t="s">
+        <v>40</v>
+      </c>
+      <c r="H688" t="s">
+        <v>41</v>
+      </c>
+      <c r="I688">
+        <v>0</v>
+      </c>
+      <c r="J688" t="s">
+        <v>20</v>
+      </c>
+      <c r="K688">
+        <v>6</v>
+      </c>
+      <c r="L688">
+        <v>99999</v>
+      </c>
+      <c r="M688">
+        <v>3</v>
+      </c>
+      <c r="N688">
+        <v>3</v>
+      </c>
+      <c r="O688">
+        <v>3</v>
+      </c>
+      <c r="P688">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="689" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A689" s="1">
         <v>46183</v>
       </c>
-      <c r="B687">
+      <c r="B689">
         <v>33594</v>
       </c>
-      <c r="C687" t="s">
+      <c r="C689" t="s">
         <v>513</v>
       </c>
-      <c r="D687">
+      <c r="D689">
         <v>-4</v>
       </c>
-      <c r="E687">
-        <v>0</v>
-      </c>
-      <c r="F687">
+      <c r="E689">
+        <v>0</v>
+      </c>
+      <c r="F689">
         <v>-4</v>
       </c>
-      <c r="G687" t="s">
-        <v>40</v>
-      </c>
-      <c r="H687" t="s">
-        <v>41</v>
-      </c>
-      <c r="I687">
-        <v>0</v>
-      </c>
-      <c r="J687" t="s">
-        <v>20</v>
-      </c>
-      <c r="K687">
+      <c r="G689" t="s">
+        <v>40</v>
+      </c>
+      <c r="H689" t="s">
+        <v>41</v>
+      </c>
+      <c r="I689">
+        <v>0</v>
+      </c>
+      <c r="J689" t="s">
+        <v>20</v>
+      </c>
+      <c r="K689">
         <v>15</v>
       </c>
-      <c r="L687">
-        <v>1033.6348</v>
-      </c>
-      <c r="M687">
-        <v>0</v>
-      </c>
-      <c r="N687">
+      <c r="L689">
+        <v>99999</v>
+      </c>
+      <c r="M689">
+        <v>0</v>
+      </c>
+      <c r="N689">
         <v>7</v>
       </c>
-      <c r="O687">
-        <v>0</v>
-      </c>
-      <c r="P687">
+      <c r="O689">
+        <v>0</v>
+      </c>
+      <c r="P689">
         <v>3</v>
       </c>
     </row>

--- a/data/movimientos.xlsx
+++ b/data/movimientos.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6673FF6-7E52-4F12-BF76-9D296470977E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCCD757-AEB2-404B-9080-CEEBF655825F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{99072C7C-E32F-4A2F-800E-3105C8F1D176}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$Q$112</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="148">
   <si>
     <t>stockmov_fecha</t>
   </si>
@@ -85,6 +88,399 @@
   </si>
   <si>
     <t>stockmov_comprobante</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Pepas Terepin Fr Roj 18x260g</t>
+  </si>
+  <si>
+    <t>TRA</t>
+  </si>
+  <si>
+    <t>consumo</t>
+  </si>
+  <si>
+    <t>STX000100000541</t>
+  </si>
+  <si>
+    <t>CONSUMO INTERNO</t>
+  </si>
+  <si>
+    <t>Pep Comun 40gx60 Pi</t>
+  </si>
+  <si>
+    <t>CON</t>
+  </si>
+  <si>
+    <t>Ajuste por conteo fisico</t>
+  </si>
+  <si>
+    <t>Pep Rueditas 40gx60 Pi</t>
+  </si>
+  <si>
+    <t>Cheetos 23grx108</t>
+  </si>
+  <si>
+    <t>Quaker Avena Extra Fina 18x470g</t>
+  </si>
+  <si>
+    <t>Lays Clasicas 20grx76</t>
+  </si>
+  <si>
+    <t>3dmegaqueso23gx120</t>
+  </si>
+  <si>
+    <t>Pehuamar Paliqueso 90gx36</t>
+  </si>
+  <si>
+    <t>Twistos Minit Queso 155gx20</t>
+  </si>
+  <si>
+    <t>Twistos Minit Jamon 155gx20</t>
+  </si>
+  <si>
+    <t>Pep Rueditas 120grx21</t>
+  </si>
+  <si>
+    <t>Pep Rueditas 74grx36</t>
+  </si>
+  <si>
+    <t>Pehuamar Maicitos 125gx16</t>
+  </si>
+  <si>
+    <t>Pehuamar Palisal 90gx36</t>
+  </si>
+  <si>
+    <t>Pep Comun 84grx36</t>
+  </si>
+  <si>
+    <t>Pep Comun 120grx21</t>
+  </si>
+  <si>
+    <t>3d Queso 43gx75x1</t>
+  </si>
+  <si>
+    <t>3d Queso 143gx18x1</t>
+  </si>
+  <si>
+    <t>Quaker Avena Instant 18x280g Arg</t>
+  </si>
+  <si>
+    <t>Quaker Avena Tradic 18x550g Arg</t>
+  </si>
+  <si>
+    <t>Pep Ramitas Queso 120gx21</t>
+  </si>
+  <si>
+    <t>Pep Ramitas Queso 84gx36</t>
+  </si>
+  <si>
+    <t>Pep Ramitas Queso 40gx60</t>
+  </si>
+  <si>
+    <t>Lays Qso Y Cebolla 34gx72</t>
+  </si>
+  <si>
+    <t>Lays Jamon Serrano 34gx72</t>
+  </si>
+  <si>
+    <t>Lays Clasicas 40gx68x1</t>
+  </si>
+  <si>
+    <t>Cheetos Queso 43gx70x1</t>
+  </si>
+  <si>
+    <t>Doritos Queso 40gx70x1</t>
+  </si>
+  <si>
+    <t>Doritos Queso 40gx58x1 Ch</t>
+  </si>
+  <si>
+    <t>Lays Ondas Fh 30gx72</t>
+  </si>
+  <si>
+    <t>Lays Ondas Fh 70gx28</t>
+  </si>
+  <si>
+    <t>Lays Jamon Serrano 122gx19</t>
+  </si>
+  <si>
+    <t>Pehuamar Palisal 620gx6x1</t>
+  </si>
+  <si>
+    <t>Pehuamar Palisal 165gx21x1</t>
+  </si>
+  <si>
+    <t>Pehuamar Paliqueso 620gx6x1</t>
+  </si>
+  <si>
+    <t>Pehuamar Paliqueso 165gx21x1</t>
+  </si>
+  <si>
+    <t>Pehuamar Papa Acana 135gx19</t>
+  </si>
+  <si>
+    <t>Lays Ketchup 77gx28x1</t>
+  </si>
+  <si>
+    <t>Doritos Queso 129gx19</t>
+  </si>
+  <si>
+    <t>Doritos Queso 200gx14</t>
+  </si>
+  <si>
+    <t>Doritos Queso 77gx26</t>
+  </si>
+  <si>
+    <t>Lays Clasicas 85gx25x1</t>
+  </si>
+  <si>
+    <t>Pehuamar Papa Lisa 135gx19x1</t>
+  </si>
+  <si>
+    <t>Pehuamar Papa Lisa 230gx14x1</t>
+  </si>
+  <si>
+    <t>Tostitos 200gx14</t>
+  </si>
+  <si>
+    <t>Lays Clasicas 330gx9</t>
+  </si>
+  <si>
+    <t>3d Queso 85gx27x1</t>
+  </si>
+  <si>
+    <t>Cheetos Queso 140gx18x1</t>
+  </si>
+  <si>
+    <t>Cheetos Queso 229gx12x1</t>
+  </si>
+  <si>
+    <t>Cheetos Queso 85gx24x1</t>
+  </si>
+  <si>
+    <t>Maniax Sal Y Limon 95gx60x1</t>
+  </si>
+  <si>
+    <t>Cheetos Queso Crema 85gx24</t>
+  </si>
+  <si>
+    <t>Cheetos Queso Crema 43gx66</t>
+  </si>
+  <si>
+    <t>Maniax Japones Sal 95gx40x1</t>
+  </si>
+  <si>
+    <t>Maniax Japones Jamon 95gx40x1</t>
+  </si>
+  <si>
+    <t>Mani Pelado 320gx17x1</t>
+  </si>
+  <si>
+    <t>Mani Pelado 135gx40x1</t>
+  </si>
+  <si>
+    <t>Mani Sal Con Piel 75gx64x1</t>
+  </si>
+  <si>
+    <t>Pehuamar Maicitos 265gx10x1</t>
+  </si>
+  <si>
+    <t>Pehuamar Acanalada 230gx14x1</t>
+  </si>
+  <si>
+    <t>Doritos Sweet Chili Mb 74gx29x1</t>
+  </si>
+  <si>
+    <t>Twistos Minit Queso 95gx30x1</t>
+  </si>
+  <si>
+    <t>Twistos Minit Queso 40gx112x1</t>
+  </si>
+  <si>
+    <t>Twistos Minit Jamon 40gx112x1</t>
+  </si>
+  <si>
+    <t>Mani Sal Pelado 75gx64x1</t>
+  </si>
+  <si>
+    <t>Mani Con Piel 135gx40x1</t>
+  </si>
+  <si>
+    <t>Doritos Sweet Chili Sb 35gx88x1</t>
+  </si>
+  <si>
+    <t>Doritos Dinamita Fh 82gx38x1</t>
+  </si>
+  <si>
+    <t>Doritos Dinamita Fh 45gx110x1</t>
+  </si>
+  <si>
+    <t>Doritos Queso 20gx88x1</t>
+  </si>
+  <si>
+    <t>Pehuamar Acan Matambrito 80x25x1</t>
+  </si>
+  <si>
+    <t>Pehua Papa Acana 90gx22 Rm</t>
+  </si>
+  <si>
+    <t>Pehua Papa Lisa 90gx22 Rm</t>
+  </si>
+  <si>
+    <t>Pehuamar Papa Lisa 450gx9 Rm</t>
+  </si>
+  <si>
+    <t>Pehuamar Acan Chimichurri 80x25x1</t>
+  </si>
+  <si>
+    <t>Mani Tubular 40grs</t>
+  </si>
+  <si>
+    <t>Lays Panceta 77gx25x1</t>
+  </si>
+  <si>
+    <t>Lays Panceta 34gx72x1</t>
+  </si>
+  <si>
+    <t>Lays Barbacoa 77gx25x1</t>
+  </si>
+  <si>
+    <t>Dinamita Extra Flamin Hot 82g</t>
+  </si>
+  <si>
+    <t>Dinamita Extra Flamin Hot 45g</t>
+  </si>
+  <si>
+    <t>Lays Provoleta 77gx25x1</t>
+  </si>
+  <si>
+    <t>Lays Ketchup 77gx25x1</t>
+  </si>
+  <si>
+    <t>Lays Jamon Serrano 77gx25x1</t>
+  </si>
+  <si>
+    <t>Lays Clasicas 134gx18x1</t>
+  </si>
+  <si>
+    <t>Lays Clasicas 230gx13x1</t>
+  </si>
+  <si>
+    <t>Lays Queso Y Cebolla 77gx25x1</t>
+  </si>
+  <si>
+    <t>Lays Clasica 20gx6x10 Tir</t>
+  </si>
+  <si>
+    <t>Doritos Queso 20gx6x10 Tir</t>
+  </si>
+  <si>
+    <t>Pep Rueditas Flamin Hot 71g</t>
+  </si>
+  <si>
+    <t>Quaker Avena Ext Fina 470gx12 Arg</t>
+  </si>
+  <si>
+    <t>Quaker Avena Tradic 550gx12 Arg</t>
+  </si>
+  <si>
+    <t>Quaker Avena Tradic 280gx20 Arg</t>
+  </si>
+  <si>
+    <t>Quaker Avena Inst 500gx10 Arg</t>
+  </si>
+  <si>
+    <t>Quaker Avena Inst 280gx20 Arg</t>
+  </si>
+  <si>
+    <t>Tostitos Rounded Sal 260 Gramos</t>
+  </si>
+  <si>
+    <t>Cheetos Ondulados Ketchup 80gx24</t>
+  </si>
+  <si>
+    <t>Cheetos Ondulados Ketchup 40gx66</t>
+  </si>
+  <si>
+    <t>Tostitos Rounded Sal 160 Gramos</t>
+  </si>
+  <si>
+    <t>Tostitos Rounded Sal 100 Gramos</t>
+  </si>
+  <si>
+    <t>Doritos Pizza 74x29x1</t>
+  </si>
+  <si>
+    <t>Doritos Pizza 35x88x1</t>
+  </si>
+  <si>
+    <t>Lays Clasica 40gx6x10 Tir</t>
+  </si>
+  <si>
+    <t>Lays Acan Asado 77gx25x1</t>
+  </si>
+  <si>
+    <t>Lays Acan Asado 34gx72x1 Mnd</t>
+  </si>
+  <si>
+    <t>vencido innovacion</t>
+  </si>
+  <si>
+    <t>STX000100000542</t>
+  </si>
+  <si>
+    <t>Vencido deposito</t>
+  </si>
+  <si>
+    <t>Doritos Queso 40gx6x10 Tir</t>
+  </si>
+  <si>
+    <t>Pehuamar Papa Lisa 420gx9x1 Rm</t>
+  </si>
+  <si>
+    <t>Pehuamar Acanalada 420x9x1 Rm</t>
+  </si>
+  <si>
+    <t>Alf Mantecol rell pasta Mantecol 24x40g</t>
+  </si>
+  <si>
+    <t>MAN</t>
+  </si>
+  <si>
+    <t>merma</t>
+  </si>
+  <si>
+    <t>STX000100000546</t>
+  </si>
+  <si>
+    <t>Tokke Choco C/lecheyMani  Cuarte X40x120</t>
+  </si>
+  <si>
+    <t>ingreso pyp</t>
+  </si>
+  <si>
+    <t>STX000100000543</t>
+  </si>
+  <si>
+    <t>Alfajor Mantecol Triple 20x60g</t>
+  </si>
+  <si>
+    <t>mal conteo</t>
+  </si>
+  <si>
+    <t>STX000100000545</t>
+  </si>
+  <si>
+    <t>Twistos Minit Jamon 95gx30x1</t>
+  </si>
+  <si>
+    <t>Pehuamar Acanalada 450x9 Rm</t>
+  </si>
+  <si>
+    <t>STX000100000544</t>
   </si>
 </sst>
 </file>
@@ -437,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5D248C6-4721-43B8-8122-45E55855FA17}">
-  <dimension ref="A1:Q915"/>
+  <dimension ref="A1:Q912"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -494,384 +890,6057 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B2">
+        <v>2644</v>
+      </c>
+      <c r="C2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2">
+        <v>-2</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>-2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2">
+        <v>24</v>
+      </c>
+      <c r="L2">
+        <v>463.5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B3">
+        <v>11300013</v>
+      </c>
+      <c r="C3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3">
+        <v>200</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3">
+        <v>40</v>
+      </c>
+      <c r="L3">
+        <v>2375</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>5</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B4">
+        <v>11302646</v>
+      </c>
+      <c r="C4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4">
+        <v>-25</v>
+      </c>
+      <c r="E4">
+        <v>-1</v>
+      </c>
+      <c r="F4">
+        <v>-5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4">
+        <v>20</v>
+      </c>
+      <c r="L4">
+        <v>726.6</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B5">
+        <v>22900004</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5">
+        <v>-20</v>
+      </c>
+      <c r="E5">
+        <v>-1</v>
+      </c>
+      <c r="F5">
+        <v>-2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>736.40949999999998</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
+      <c r="A6" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B6">
+        <v>22900004</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6">
+        <v>18</v>
+      </c>
+      <c r="L6">
+        <v>736.40949999999998</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
+      <c r="A7" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B7">
+        <v>300033488</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>59</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>59</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7">
+        <v>60</v>
+      </c>
+      <c r="L7">
+        <v>531.29</v>
+      </c>
+      <c r="M7">
+        <v>9</v>
+      </c>
+      <c r="N7">
+        <v>48</v>
+      </c>
+      <c r="O7">
+        <v>10</v>
+      </c>
+      <c r="P7">
+        <v>47</v>
+      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
+      <c r="A8" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B8">
+        <v>300033489</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8">
+        <v>60</v>
+      </c>
+      <c r="L8">
+        <v>531.29</v>
+      </c>
+      <c r="M8">
+        <v>37</v>
+      </c>
+      <c r="N8">
+        <v>42</v>
+      </c>
+      <c r="O8">
+        <v>37</v>
+      </c>
+      <c r="P8">
+        <v>50</v>
+      </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
+      <c r="A9" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B9">
+        <v>300050336</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9">
+        <v>108</v>
+      </c>
+      <c r="L9">
+        <v>531.29</v>
+      </c>
+      <c r="M9">
+        <v>9</v>
+      </c>
+      <c r="N9">
+        <v>107</v>
+      </c>
+      <c r="O9">
+        <v>10</v>
+      </c>
+      <c r="P9">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
+      <c r="A10" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B10">
+        <v>300051958</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10">
+        <v>18</v>
+      </c>
+      <c r="L10">
+        <v>1815.23</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
+      <c r="A11" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B11">
+        <v>300051988</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11">
+        <v>17</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11">
+        <v>76</v>
+      </c>
+      <c r="L11">
+        <v>531.29</v>
+      </c>
+      <c r="M11">
+        <v>71</v>
+      </c>
+      <c r="N11">
+        <v>56</v>
+      </c>
+      <c r="O11">
+        <v>71</v>
+      </c>
+      <c r="P11">
+        <v>73</v>
+      </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
+      <c r="A12" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B12">
+        <v>300052023</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>12</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12">
+        <v>120</v>
+      </c>
+      <c r="L12">
+        <v>531.29</v>
+      </c>
+      <c r="M12">
+        <v>24</v>
+      </c>
+      <c r="N12">
+        <v>115</v>
+      </c>
+      <c r="O12">
+        <v>25</v>
+      </c>
+      <c r="P12">
+        <v>7</v>
+      </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+      <c r="A13" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B13">
+        <v>300052656</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13">
+        <v>-145</v>
+      </c>
+      <c r="E13">
+        <v>-4</v>
+      </c>
+      <c r="F13">
+        <v>-1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13">
+        <v>36</v>
+      </c>
+      <c r="L13">
+        <v>1161.75</v>
+      </c>
+      <c r="M13">
+        <v>44</v>
+      </c>
+      <c r="N13">
+        <v>35</v>
+      </c>
+      <c r="O13">
+        <v>40</v>
+      </c>
+      <c r="P13">
+        <v>34</v>
+      </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B14">
+        <v>300052694</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14">
+        <v>-11</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>-11</v>
+      </c>
+      <c r="G14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14">
+        <v>20</v>
+      </c>
+      <c r="L14">
+        <v>2517.1201000000001</v>
+      </c>
+      <c r="M14">
+        <v>30</v>
+      </c>
+      <c r="N14">
+        <v>5</v>
+      </c>
+      <c r="O14">
+        <v>29</v>
+      </c>
+      <c r="P14">
+        <v>14</v>
+      </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
+      <c r="A15" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B15">
+        <v>300052697</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15">
+        <v>68</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <v>8</v>
+      </c>
+      <c r="G15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15">
+        <v>20</v>
+      </c>
+      <c r="L15">
+        <v>2517.1201000000001</v>
+      </c>
+      <c r="M15">
+        <v>36</v>
+      </c>
+      <c r="N15">
+        <v>8</v>
+      </c>
+      <c r="O15">
+        <v>39</v>
+      </c>
+      <c r="P15">
+        <v>16</v>
+      </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="1"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="1"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="1"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="1"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="1"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="1"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="1"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="1"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="1"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="1"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="1"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="1"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="1"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="1"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="1"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="1"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="1"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="1"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="1"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="1"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="1"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="1"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="1"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="1"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="1"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="1"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="1"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="1"/>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="1"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="1"/>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="1"/>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="1"/>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="1"/>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="1"/>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="1"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="1"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="1"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="1"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="1"/>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="1"/>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="1"/>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="1"/>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="1"/>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="1"/>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="1"/>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="1"/>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="1"/>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="1"/>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="1"/>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="1"/>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="1"/>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="1"/>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="1"/>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="1"/>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="1"/>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="1"/>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="1"/>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="1"/>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="1"/>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="1"/>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B16">
+        <v>300052756</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16">
+        <v>-9</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>-9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16">
+        <v>21</v>
+      </c>
+      <c r="L16">
+        <v>1611.5699</v>
+      </c>
+      <c r="M16">
+        <v>20</v>
+      </c>
+      <c r="N16">
+        <v>10</v>
+      </c>
+      <c r="O16">
+        <v>20</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B17">
+        <v>300052757</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>16</v>
+      </c>
+      <c r="G17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17">
+        <v>36</v>
+      </c>
+      <c r="L17">
+        <v>929.75</v>
+      </c>
+      <c r="M17">
+        <v>131</v>
+      </c>
+      <c r="N17">
+        <v>17</v>
+      </c>
+      <c r="O17">
+        <v>131</v>
+      </c>
+      <c r="P17">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B18">
+        <v>300052758</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18">
+        <v>-17</v>
+      </c>
+      <c r="E18">
+        <v>-1</v>
+      </c>
+      <c r="F18">
+        <v>-1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18">
+        <v>16</v>
+      </c>
+      <c r="L18">
+        <v>1791.03</v>
+      </c>
+      <c r="M18">
+        <v>15</v>
+      </c>
+      <c r="N18">
+        <v>9</v>
+      </c>
+      <c r="O18">
+        <v>14</v>
+      </c>
+      <c r="P18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B19">
+        <v>300052790</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>6</v>
+      </c>
+      <c r="G19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19">
+        <v>36</v>
+      </c>
+      <c r="L19">
+        <v>1161.75</v>
+      </c>
+      <c r="M19">
+        <v>2</v>
+      </c>
+      <c r="N19">
+        <v>24</v>
+      </c>
+      <c r="O19">
+        <v>2</v>
+      </c>
+      <c r="P19">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B20">
+        <v>300052820</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20">
+        <v>35</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>35</v>
+      </c>
+      <c r="G20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20">
+        <v>36</v>
+      </c>
+      <c r="L20">
+        <v>929.75</v>
+      </c>
+      <c r="M20">
+        <v>15</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>16</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B21">
+        <v>300052821</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21">
+        <v>-9</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>-9</v>
+      </c>
+      <c r="G21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21">
+        <v>21</v>
+      </c>
+      <c r="L21">
+        <v>1611.5699</v>
+      </c>
+      <c r="M21">
+        <v>4</v>
+      </c>
+      <c r="N21">
+        <v>5</v>
+      </c>
+      <c r="O21">
+        <v>3</v>
+      </c>
+      <c r="P21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B22">
+        <v>300058395</v>
+      </c>
+      <c r="C22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22">
+        <v>16</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>16</v>
+      </c>
+      <c r="G22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22">
+        <v>75</v>
+      </c>
+      <c r="L22">
+        <v>929.75</v>
+      </c>
+      <c r="M22">
+        <v>281</v>
+      </c>
+      <c r="N22">
+        <v>37</v>
+      </c>
+      <c r="O22">
+        <v>281</v>
+      </c>
+      <c r="P22">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B23">
+        <v>300058397</v>
+      </c>
+      <c r="C23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23">
+        <v>18</v>
+      </c>
+      <c r="L23">
+        <v>2662.3400999999999</v>
+      </c>
+      <c r="M23">
+        <v>299</v>
+      </c>
+      <c r="N23">
+        <v>7</v>
+      </c>
+      <c r="O23">
+        <v>299</v>
+      </c>
+      <c r="P23">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B24">
+        <v>300058444</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24">
+        <v>18</v>
+      </c>
+      <c r="L24">
+        <v>1113.3399999999999</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B25">
+        <v>300058446</v>
+      </c>
+      <c r="C25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" t="s">
+        <v>25</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25">
+        <v>18</v>
+      </c>
+      <c r="L25">
+        <v>1815.23</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B26">
+        <v>300058720</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26">
+        <v>17</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>17</v>
+      </c>
+      <c r="G26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26">
+        <v>21</v>
+      </c>
+      <c r="L26">
+        <v>1611.5699</v>
+      </c>
+      <c r="M26">
+        <v>7</v>
+      </c>
+      <c r="N26">
+        <v>14</v>
+      </c>
+      <c r="O26">
+        <v>8</v>
+      </c>
+      <c r="P26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B27">
+        <v>300058721</v>
+      </c>
+      <c r="C27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27">
+        <v>-31</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>-31</v>
+      </c>
+      <c r="G27" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" t="s">
+        <v>25</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27">
+        <v>36</v>
+      </c>
+      <c r="L27">
+        <v>929.75</v>
+      </c>
+      <c r="M27">
+        <v>11</v>
+      </c>
+      <c r="N27">
+        <v>9</v>
+      </c>
+      <c r="O27">
+        <v>10</v>
+      </c>
+      <c r="P27">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B28">
+        <v>300058740</v>
+      </c>
+      <c r="C28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28">
+        <v>-11</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>-11</v>
+      </c>
+      <c r="G28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28">
+        <v>60</v>
+      </c>
+      <c r="L28">
+        <v>531.29</v>
+      </c>
+      <c r="M28">
+        <v>5</v>
+      </c>
+      <c r="N28">
+        <v>28</v>
+      </c>
+      <c r="O28">
+        <v>5</v>
+      </c>
+      <c r="P28">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B29">
+        <v>300059430</v>
+      </c>
+      <c r="C29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29">
+        <v>6</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>6</v>
+      </c>
+      <c r="G29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29">
+        <v>72</v>
+      </c>
+      <c r="L29">
+        <v>929.75</v>
+      </c>
+      <c r="M29">
+        <v>5</v>
+      </c>
+      <c r="N29">
+        <v>29</v>
+      </c>
+      <c r="O29">
+        <v>5</v>
+      </c>
+      <c r="P29">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B30">
+        <v>300059431</v>
+      </c>
+      <c r="C30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30">
+        <v>11</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>11</v>
+      </c>
+      <c r="G30" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" t="s">
+        <v>25</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30">
+        <v>72</v>
+      </c>
+      <c r="L30">
+        <v>929.75</v>
+      </c>
+      <c r="M30">
+        <v>5</v>
+      </c>
+      <c r="N30">
+        <v>44</v>
+      </c>
+      <c r="O30">
+        <v>5</v>
+      </c>
+      <c r="P30">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B31">
+        <v>300059432</v>
+      </c>
+      <c r="C31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31">
+        <v>10</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>10</v>
+      </c>
+      <c r="G31" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" t="s">
+        <v>25</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31">
+        <v>68</v>
+      </c>
+      <c r="L31">
+        <v>929.75</v>
+      </c>
+      <c r="M31">
+        <v>493</v>
+      </c>
+      <c r="N31">
+        <v>35</v>
+      </c>
+      <c r="O31">
+        <v>493</v>
+      </c>
+      <c r="P31">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B32">
+        <v>300059433</v>
+      </c>
+      <c r="C32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32">
+        <v>37</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>37</v>
+      </c>
+      <c r="G32" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" t="s">
+        <v>25</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32">
+        <v>70</v>
+      </c>
+      <c r="L32">
+        <v>929.75</v>
+      </c>
+      <c r="M32">
+        <v>194</v>
+      </c>
+      <c r="N32">
+        <v>59</v>
+      </c>
+      <c r="O32">
+        <v>195</v>
+      </c>
+      <c r="P32">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B33">
+        <v>300059545</v>
+      </c>
+      <c r="C33" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33">
+        <v>53</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>53</v>
+      </c>
+      <c r="G33" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" t="s">
+        <v>25</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33">
+        <v>70</v>
+      </c>
+      <c r="L33">
+        <v>929.75</v>
+      </c>
+      <c r="M33">
+        <v>719</v>
+      </c>
+      <c r="N33">
+        <v>2</v>
+      </c>
+      <c r="O33">
+        <v>719</v>
+      </c>
+      <c r="P33">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B34">
+        <v>300059547</v>
+      </c>
+      <c r="C34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" t="s">
+        <v>25</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34">
+        <v>58</v>
+      </c>
+      <c r="L34">
+        <v>929.75</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B35">
+        <v>300059801</v>
+      </c>
+      <c r="C35" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" t="s">
+        <v>25</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35">
+        <v>72</v>
+      </c>
+      <c r="L35">
+        <v>929.75</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B36">
+        <v>300059811</v>
+      </c>
+      <c r="C36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36">
+        <v>15</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" t="s">
+        <v>25</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36">
+        <v>28</v>
+      </c>
+      <c r="L36">
+        <v>1611.5699</v>
+      </c>
+      <c r="M36">
+        <v>81</v>
+      </c>
+      <c r="N36">
+        <v>25</v>
+      </c>
+      <c r="O36">
+        <v>82</v>
+      </c>
+      <c r="P36">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B37">
+        <v>300060080</v>
+      </c>
+      <c r="C37" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" t="s">
+        <v>25</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37">
+        <v>19</v>
+      </c>
+      <c r="L37">
+        <v>2662.3400999999999</v>
+      </c>
+      <c r="M37">
+        <v>11</v>
+      </c>
+      <c r="N37">
+        <v>16</v>
+      </c>
+      <c r="O37">
+        <v>11</v>
+      </c>
+      <c r="P37">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B38">
+        <v>300060091</v>
+      </c>
+      <c r="C38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" t="s">
+        <v>25</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38">
+        <v>6</v>
+      </c>
+      <c r="L38">
+        <v>4365.4102000000003</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B39">
+        <v>300060092</v>
+      </c>
+      <c r="C39" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39">
+        <v>-6</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>-6</v>
+      </c>
+      <c r="G39" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" t="s">
+        <v>25</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39">
+        <v>21</v>
+      </c>
+      <c r="L39">
+        <v>1597.4</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>16</v>
+      </c>
+      <c r="O39">
+        <v>1</v>
+      </c>
+      <c r="P39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B40">
+        <v>300060093</v>
+      </c>
+      <c r="C40" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" t="s">
+        <v>25</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40">
+        <v>6</v>
+      </c>
+      <c r="L40">
+        <v>4365.4102000000003</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B41">
+        <v>300060094</v>
+      </c>
+      <c r="C41" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" t="s">
+        <v>25</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41">
+        <v>21</v>
+      </c>
+      <c r="L41">
+        <v>1597.4</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B42">
+        <v>300060097</v>
+      </c>
+      <c r="C42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42">
+        <v>-3</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>-3</v>
+      </c>
+      <c r="G42" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" t="s">
+        <v>25</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42">
+        <v>19</v>
+      </c>
+      <c r="L42">
+        <v>1839.4301</v>
+      </c>
+      <c r="M42">
+        <v>28</v>
+      </c>
+      <c r="N42">
+        <v>11</v>
+      </c>
+      <c r="O42">
+        <v>28</v>
+      </c>
+      <c r="P42">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B43">
+        <v>300060099</v>
+      </c>
+      <c r="C43" t="s">
+        <v>61</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" t="s">
+        <v>25</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43">
+        <v>28</v>
+      </c>
+      <c r="L43">
+        <v>1427.39</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B44">
+        <v>300060190</v>
+      </c>
+      <c r="C44" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44">
+        <v>-613</v>
+      </c>
+      <c r="E44">
+        <v>-32</v>
+      </c>
+      <c r="F44">
+        <v>-5</v>
+      </c>
+      <c r="G44" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" t="s">
+        <v>25</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44">
+        <v>19</v>
+      </c>
+      <c r="L44">
+        <v>2662.3400999999999</v>
+      </c>
+      <c r="M44">
+        <v>966</v>
+      </c>
+      <c r="N44">
+        <v>9</v>
+      </c>
+      <c r="O44">
+        <v>934</v>
+      </c>
+      <c r="P44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B45">
+        <v>300060191</v>
+      </c>
+      <c r="C45" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45">
+        <v>495</v>
+      </c>
+      <c r="E45">
+        <v>35</v>
+      </c>
+      <c r="F45">
+        <v>5</v>
+      </c>
+      <c r="G45" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" t="s">
+        <v>25</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45">
+        <v>14</v>
+      </c>
+      <c r="L45">
+        <v>3872.49</v>
+      </c>
+      <c r="M45">
+        <v>112</v>
+      </c>
+      <c r="N45">
+        <v>11</v>
+      </c>
+      <c r="O45">
+        <v>148</v>
+      </c>
+      <c r="P45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B46">
+        <v>300060192</v>
+      </c>
+      <c r="C46" t="s">
+        <v>64</v>
+      </c>
+      <c r="D46">
+        <v>18</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>24</v>
+      </c>
+      <c r="H46" t="s">
+        <v>25</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46">
+        <v>26</v>
+      </c>
+      <c r="L46">
+        <v>1611.5699</v>
+      </c>
+      <c r="M46">
+        <v>1787</v>
+      </c>
+      <c r="N46">
+        <v>11</v>
+      </c>
+      <c r="O46">
+        <v>1788</v>
+      </c>
+      <c r="P46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B47">
+        <v>300060195</v>
+      </c>
+      <c r="C47" t="s">
+        <v>65</v>
+      </c>
+      <c r="D47">
+        <v>-7</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>-7</v>
+      </c>
+      <c r="G47" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" t="s">
+        <v>25</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47">
+        <v>25</v>
+      </c>
+      <c r="L47">
+        <v>1611.5699</v>
+      </c>
+      <c r="M47">
+        <v>1450</v>
+      </c>
+      <c r="N47">
+        <v>11</v>
+      </c>
+      <c r="O47">
+        <v>1450</v>
+      </c>
+      <c r="P47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B48">
+        <v>300060196</v>
+      </c>
+      <c r="C48" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48">
+        <v>11</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>11</v>
+      </c>
+      <c r="G48" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" t="s">
+        <v>25</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48" t="s">
+        <v>17</v>
+      </c>
+      <c r="K48">
+        <v>19</v>
+      </c>
+      <c r="L48">
+        <v>1839.4301</v>
+      </c>
+      <c r="M48">
+        <v>17</v>
+      </c>
+      <c r="N48">
+        <v>1</v>
+      </c>
+      <c r="O48">
+        <v>17</v>
+      </c>
+      <c r="P48">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B49">
+        <v>300060197</v>
+      </c>
+      <c r="C49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" t="s">
+        <v>25</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49">
+        <v>14</v>
+      </c>
+      <c r="L49">
+        <v>3184.1799000000001</v>
+      </c>
+      <c r="M49">
+        <v>4</v>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
+      <c r="O49">
+        <v>4</v>
+      </c>
+      <c r="P49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B50">
+        <v>300060200</v>
+      </c>
+      <c r="C50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50" t="s">
+        <v>24</v>
+      </c>
+      <c r="H50" t="s">
+        <v>25</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50">
+        <v>14</v>
+      </c>
+      <c r="L50">
+        <v>3001.1799000000001</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B51">
+        <v>300060231</v>
+      </c>
+      <c r="C51" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51">
+        <v>-6</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>-6</v>
+      </c>
+      <c r="G51" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" t="s">
+        <v>25</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51">
+        <v>9</v>
+      </c>
+      <c r="L51">
+        <v>4598.5801000000001</v>
+      </c>
+      <c r="M51">
+        <v>73</v>
+      </c>
+      <c r="N51">
+        <v>4</v>
+      </c>
+      <c r="O51">
+        <v>72</v>
+      </c>
+      <c r="P51">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B52">
+        <v>300060661</v>
+      </c>
+      <c r="C52" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52">
+        <v>-16</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>-16</v>
+      </c>
+      <c r="G52" t="s">
+        <v>24</v>
+      </c>
+      <c r="H52" t="s">
+        <v>25</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52">
+        <v>27</v>
+      </c>
+      <c r="L52">
+        <v>1611.5699</v>
+      </c>
+      <c r="M52">
+        <v>865</v>
+      </c>
+      <c r="N52">
+        <v>5</v>
+      </c>
+      <c r="O52">
+        <v>864</v>
+      </c>
+      <c r="P52">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B53">
+        <v>300060662</v>
+      </c>
+      <c r="C53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D53">
+        <v>-11</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>-11</v>
+      </c>
+      <c r="G53" t="s">
+        <v>24</v>
+      </c>
+      <c r="H53" t="s">
+        <v>25</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53" t="s">
+        <v>17</v>
+      </c>
+      <c r="K53">
+        <v>18</v>
+      </c>
+      <c r="L53">
+        <v>2662.3400999999999</v>
+      </c>
+      <c r="M53">
+        <v>213</v>
+      </c>
+      <c r="N53">
+        <v>2</v>
+      </c>
+      <c r="O53">
+        <v>212</v>
+      </c>
+      <c r="P53">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B54">
+        <v>300060663</v>
+      </c>
+      <c r="C54" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54" t="s">
+        <v>24</v>
+      </c>
+      <c r="H54" t="s">
+        <v>25</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K54">
+        <v>12</v>
+      </c>
+      <c r="L54">
+        <v>3775.6799000000001</v>
+      </c>
+      <c r="M54">
+        <v>13</v>
+      </c>
+      <c r="N54">
+        <v>6</v>
+      </c>
+      <c r="O54">
+        <v>13</v>
+      </c>
+      <c r="P54">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B55">
+        <v>300060664</v>
+      </c>
+      <c r="C55" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55">
+        <v>67</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="F55">
+        <v>19</v>
+      </c>
+      <c r="G55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H55" t="s">
+        <v>25</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55" t="s">
+        <v>17</v>
+      </c>
+      <c r="K55">
+        <v>24</v>
+      </c>
+      <c r="L55">
+        <v>1611.5699</v>
+      </c>
+      <c r="M55">
+        <v>706</v>
+      </c>
+      <c r="N55">
+        <v>15</v>
+      </c>
+      <c r="O55">
+        <v>709</v>
+      </c>
+      <c r="P55">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B56">
+        <v>300060869</v>
+      </c>
+      <c r="C56" t="s">
+        <v>74</v>
+      </c>
+      <c r="D56">
+        <v>-5</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>-5</v>
+      </c>
+      <c r="G56" t="s">
+        <v>24</v>
+      </c>
+      <c r="H56" t="s">
+        <v>25</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56" t="s">
+        <v>17</v>
+      </c>
+      <c r="K56">
+        <v>60</v>
+      </c>
+      <c r="L56">
+        <v>1151.1199999999999</v>
+      </c>
+      <c r="M56">
+        <v>4</v>
+      </c>
+      <c r="N56">
+        <v>20</v>
+      </c>
+      <c r="O56">
+        <v>4</v>
+      </c>
+      <c r="P56">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B57">
+        <v>300061010</v>
+      </c>
+      <c r="C57" t="s">
+        <v>75</v>
+      </c>
+      <c r="D57">
+        <v>68</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="F57">
+        <v>20</v>
+      </c>
+      <c r="G57" t="s">
+        <v>24</v>
+      </c>
+      <c r="H57" t="s">
+        <v>25</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57" t="s">
+        <v>17</v>
+      </c>
+      <c r="K57">
+        <v>24</v>
+      </c>
+      <c r="L57">
+        <v>1611.5699</v>
+      </c>
+      <c r="M57">
+        <v>162</v>
+      </c>
+      <c r="N57">
+        <v>4</v>
+      </c>
+      <c r="O57">
+        <v>165</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B58">
+        <v>300061011</v>
+      </c>
+      <c r="C58" t="s">
+        <v>76</v>
+      </c>
+      <c r="D58">
+        <v>-4</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>-4</v>
+      </c>
+      <c r="G58" t="s">
+        <v>24</v>
+      </c>
+      <c r="H58" t="s">
+        <v>25</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58" t="s">
+        <v>17</v>
+      </c>
+      <c r="K58">
+        <v>66</v>
+      </c>
+      <c r="L58">
+        <v>929.75</v>
+      </c>
+      <c r="M58">
+        <v>30</v>
+      </c>
+      <c r="N58">
+        <v>52</v>
+      </c>
+      <c r="O58">
+        <v>30</v>
+      </c>
+      <c r="P58">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B59">
+        <v>300061020</v>
+      </c>
+      <c r="C59" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59" t="s">
+        <v>24</v>
+      </c>
+      <c r="H59" t="s">
+        <v>25</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59" t="s">
+        <v>17</v>
+      </c>
+      <c r="K59">
+        <v>40</v>
+      </c>
+      <c r="L59">
+        <v>1151.1199999999999</v>
+      </c>
+      <c r="M59">
+        <v>4</v>
+      </c>
+      <c r="N59">
+        <v>8</v>
+      </c>
+      <c r="O59">
+        <v>4</v>
+      </c>
+      <c r="P59">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B60">
+        <v>300061021</v>
+      </c>
+      <c r="C60" t="s">
+        <v>78</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60" t="s">
+        <v>24</v>
+      </c>
+      <c r="H60" t="s">
+        <v>25</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60" t="s">
+        <v>17</v>
+      </c>
+      <c r="K60">
+        <v>40</v>
+      </c>
+      <c r="L60">
+        <v>1151.1199999999999</v>
+      </c>
+      <c r="M60">
+        <v>8</v>
+      </c>
+      <c r="N60">
+        <v>18</v>
+      </c>
+      <c r="O60">
+        <v>8</v>
+      </c>
+      <c r="P60">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B61">
+        <v>300061022</v>
+      </c>
+      <c r="C61" t="s">
+        <v>79</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61" t="s">
+        <v>24</v>
+      </c>
+      <c r="H61" t="s">
+        <v>25</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61" t="s">
+        <v>17</v>
+      </c>
+      <c r="K61">
+        <v>17</v>
+      </c>
+      <c r="L61">
+        <v>3146.3998999999999</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B62">
+        <v>300061023</v>
+      </c>
+      <c r="C62" t="s">
+        <v>80</v>
+      </c>
+      <c r="D62">
+        <v>12</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>12</v>
+      </c>
+      <c r="G62" t="s">
+        <v>24</v>
+      </c>
+      <c r="H62" t="s">
+        <v>25</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62" t="s">
+        <v>17</v>
+      </c>
+      <c r="K62">
+        <v>40</v>
+      </c>
+      <c r="L62">
+        <v>1519.48</v>
+      </c>
+      <c r="M62">
+        <v>2</v>
+      </c>
+      <c r="N62">
+        <v>16</v>
+      </c>
+      <c r="O62">
+        <v>2</v>
+      </c>
+      <c r="P62">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B63">
+        <v>300061030</v>
+      </c>
+      <c r="C63" t="s">
+        <v>81</v>
+      </c>
+      <c r="D63">
+        <v>-52</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>-52</v>
+      </c>
+      <c r="G63" t="s">
+        <v>24</v>
+      </c>
+      <c r="H63" t="s">
+        <v>25</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63" t="s">
+        <v>17</v>
+      </c>
+      <c r="K63">
+        <v>64</v>
+      </c>
+      <c r="L63">
+        <v>1012.99</v>
+      </c>
+      <c r="M63">
+        <v>8</v>
+      </c>
+      <c r="N63">
+        <v>23</v>
+      </c>
+      <c r="O63">
+        <v>7</v>
+      </c>
+      <c r="P63">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B64">
+        <v>300062972</v>
+      </c>
+      <c r="C64" t="s">
+        <v>82</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64" t="s">
+        <v>24</v>
+      </c>
+      <c r="H64" t="s">
+        <v>25</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64" t="s">
+        <v>17</v>
+      </c>
+      <c r="K64">
+        <v>10</v>
+      </c>
+      <c r="L64">
+        <v>3184.1799000000001</v>
+      </c>
+      <c r="M64">
+        <v>17</v>
+      </c>
+      <c r="N64">
+        <v>6</v>
+      </c>
+      <c r="O64">
+        <v>17</v>
+      </c>
+      <c r="P64">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B65">
+        <v>300062973</v>
+      </c>
+      <c r="C65" t="s">
+        <v>83</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
+        <v>24</v>
+      </c>
+      <c r="H65" t="s">
+        <v>25</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K65">
+        <v>14</v>
+      </c>
+      <c r="L65">
+        <v>3184.1799000000001</v>
+      </c>
+      <c r="M65">
+        <v>9</v>
+      </c>
+      <c r="N65">
+        <v>5</v>
+      </c>
+      <c r="O65">
+        <v>9</v>
+      </c>
+      <c r="P65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B66">
+        <v>300063015</v>
+      </c>
+      <c r="C66" t="s">
+        <v>84</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66" t="s">
+        <v>24</v>
+      </c>
+      <c r="H66" t="s">
+        <v>25</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66" t="s">
+        <v>17</v>
+      </c>
+      <c r="K66">
+        <v>29</v>
+      </c>
+      <c r="L66">
+        <v>1611.5699</v>
+      </c>
+      <c r="M66">
+        <v>77</v>
+      </c>
+      <c r="N66">
+        <v>22</v>
+      </c>
+      <c r="O66">
+        <v>77</v>
+      </c>
+      <c r="P66">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B67">
+        <v>300063097</v>
+      </c>
+      <c r="C67" t="s">
+        <v>85</v>
+      </c>
+      <c r="D67">
+        <v>62</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67" t="s">
+        <v>24</v>
+      </c>
+      <c r="H67" t="s">
+        <v>25</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K67">
+        <v>30</v>
+      </c>
+      <c r="L67">
+        <v>1657.62</v>
+      </c>
+      <c r="M67">
+        <v>341</v>
+      </c>
+      <c r="N67">
+        <v>3</v>
+      </c>
+      <c r="O67">
+        <v>343</v>
+      </c>
+      <c r="P67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B68">
+        <v>300063097</v>
+      </c>
+      <c r="C68" t="s">
+        <v>85</v>
+      </c>
+      <c r="D68">
+        <v>-130</v>
+      </c>
+      <c r="E68">
+        <v>-4</v>
+      </c>
+      <c r="F68">
+        <v>-10</v>
+      </c>
+      <c r="G68" t="s">
+        <v>136</v>
+      </c>
+      <c r="H68" t="s">
+        <v>143</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68" t="s">
+        <v>17</v>
+      </c>
+      <c r="K68">
+        <v>30</v>
+      </c>
+      <c r="L68">
+        <v>1657.62</v>
+      </c>
+      <c r="M68">
+        <v>343</v>
+      </c>
+      <c r="N68">
+        <v>5</v>
+      </c>
+      <c r="O68">
+        <v>338</v>
+      </c>
+      <c r="P68">
+        <v>25</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B69">
+        <v>300063098</v>
+      </c>
+      <c r="C69" t="s">
+        <v>145</v>
+      </c>
+      <c r="D69">
+        <v>135</v>
+      </c>
+      <c r="E69">
+        <v>4</v>
+      </c>
+      <c r="F69">
+        <v>15</v>
+      </c>
+      <c r="G69" t="s">
+        <v>24</v>
+      </c>
+      <c r="H69" t="s">
+        <v>25</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69" t="s">
+        <v>17</v>
+      </c>
+      <c r="K69">
+        <v>30</v>
+      </c>
+      <c r="L69">
+        <v>1657.62</v>
+      </c>
+      <c r="M69">
+        <v>435</v>
+      </c>
+      <c r="N69">
+        <v>9</v>
+      </c>
+      <c r="O69">
+        <v>439</v>
+      </c>
+      <c r="P69">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B70">
+        <v>300063263</v>
+      </c>
+      <c r="C70" t="s">
+        <v>86</v>
+      </c>
+      <c r="D70">
+        <v>9</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>9</v>
+      </c>
+      <c r="G70" t="s">
+        <v>24</v>
+      </c>
+      <c r="H70" t="s">
+        <v>25</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70" t="s">
+        <v>17</v>
+      </c>
+      <c r="K70">
+        <v>112</v>
+      </c>
+      <c r="L70">
+        <v>974.03</v>
+      </c>
+      <c r="M70">
+        <v>63</v>
+      </c>
+      <c r="N70">
+        <v>33</v>
+      </c>
+      <c r="O70">
+        <v>63</v>
+      </c>
+      <c r="P70">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B71">
+        <v>300063264</v>
+      </c>
+      <c r="C71" t="s">
+        <v>87</v>
+      </c>
+      <c r="D71">
+        <v>7</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>7</v>
+      </c>
+      <c r="G71" t="s">
+        <v>24</v>
+      </c>
+      <c r="H71" t="s">
+        <v>25</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71" t="s">
+        <v>17</v>
+      </c>
+      <c r="K71">
+        <v>112</v>
+      </c>
+      <c r="L71">
+        <v>974.03</v>
+      </c>
+      <c r="M71">
+        <v>112</v>
+      </c>
+      <c r="N71">
+        <v>54</v>
+      </c>
+      <c r="O71">
+        <v>112</v>
+      </c>
+      <c r="P71">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B72">
+        <v>300063271</v>
+      </c>
+      <c r="C72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D72">
+        <v>-32</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>-32</v>
+      </c>
+      <c r="G72" t="s">
+        <v>24</v>
+      </c>
+      <c r="H72" t="s">
+        <v>25</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72" t="s">
+        <v>17</v>
+      </c>
+      <c r="K72">
+        <v>64</v>
+      </c>
+      <c r="L72">
+        <v>1012.99</v>
+      </c>
+      <c r="M72">
+        <v>13</v>
+      </c>
+      <c r="N72">
+        <v>12</v>
+      </c>
+      <c r="O72">
+        <v>12</v>
+      </c>
+      <c r="P72">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B73">
+        <v>300063273</v>
+      </c>
+      <c r="C73" t="s">
+        <v>89</v>
+      </c>
+      <c r="D73">
+        <v>58</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+      <c r="F73">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>24</v>
+      </c>
+      <c r="H73" t="s">
+        <v>25</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73" t="s">
+        <v>17</v>
+      </c>
+      <c r="K73">
+        <v>40</v>
+      </c>
+      <c r="L73">
+        <v>1519.48</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>1</v>
+      </c>
+      <c r="P73">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B74">
+        <v>300063283</v>
+      </c>
+      <c r="C74" t="s">
+        <v>90</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74" t="s">
+        <v>24</v>
+      </c>
+      <c r="H74" t="s">
+        <v>25</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74" t="s">
+        <v>17</v>
+      </c>
+      <c r="K74">
+        <v>88</v>
+      </c>
+      <c r="L74">
+        <v>929.75</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B75">
+        <v>300064054</v>
+      </c>
+      <c r="C75" t="s">
+        <v>91</v>
+      </c>
+      <c r="D75">
+        <v>12</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>12</v>
+      </c>
+      <c r="G75" t="s">
+        <v>24</v>
+      </c>
+      <c r="H75" t="s">
+        <v>25</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75" t="s">
+        <v>17</v>
+      </c>
+      <c r="K75">
+        <v>38</v>
+      </c>
+      <c r="L75">
+        <v>1381.35</v>
+      </c>
+      <c r="M75">
+        <v>221</v>
+      </c>
+      <c r="N75">
+        <v>11</v>
+      </c>
+      <c r="O75">
+        <v>221</v>
+      </c>
+      <c r="P75">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B76">
+        <v>300064055</v>
+      </c>
+      <c r="C76" t="s">
+        <v>92</v>
+      </c>
+      <c r="D76">
+        <v>-23</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>-23</v>
+      </c>
+      <c r="G76" t="s">
+        <v>24</v>
+      </c>
+      <c r="H76" t="s">
+        <v>25</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76" t="s">
+        <v>17</v>
+      </c>
+      <c r="K76">
+        <v>110</v>
+      </c>
+      <c r="L76">
+        <v>885.48</v>
+      </c>
+      <c r="M76">
+        <v>48</v>
+      </c>
+      <c r="N76">
+        <v>58</v>
+      </c>
+      <c r="O76">
+        <v>48</v>
+      </c>
+      <c r="P76">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B77">
+        <v>300064193</v>
+      </c>
+      <c r="C77" t="s">
+        <v>93</v>
+      </c>
+      <c r="D77">
+        <v>2</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>2</v>
+      </c>
+      <c r="G77" t="s">
+        <v>24</v>
+      </c>
+      <c r="H77" t="s">
+        <v>25</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77" t="s">
+        <v>17</v>
+      </c>
+      <c r="K77">
+        <v>88</v>
+      </c>
+      <c r="L77">
+        <v>531.29</v>
+      </c>
+      <c r="M77">
+        <v>73</v>
+      </c>
+      <c r="N77">
+        <v>27</v>
+      </c>
+      <c r="O77">
+        <v>73</v>
+      </c>
+      <c r="P77">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B78">
+        <v>300064478</v>
+      </c>
+      <c r="C78" t="s">
+        <v>94</v>
+      </c>
+      <c r="D78">
+        <v>-15</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>-15</v>
+      </c>
+      <c r="G78" t="s">
+        <v>24</v>
+      </c>
+      <c r="H78" t="s">
+        <v>25</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78" t="s">
+        <v>17</v>
+      </c>
+      <c r="K78">
+        <v>25</v>
+      </c>
+      <c r="L78">
+        <v>1210.1500000000001</v>
+      </c>
+      <c r="M78">
+        <v>50</v>
+      </c>
+      <c r="N78">
+        <v>19</v>
+      </c>
+      <c r="O78">
+        <v>50</v>
+      </c>
+      <c r="P78">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B79">
+        <v>300064630</v>
+      </c>
+      <c r="C79" t="s">
+        <v>95</v>
+      </c>
+      <c r="D79">
+        <v>-18</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>-18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>24</v>
+      </c>
+      <c r="H79" t="s">
+        <v>25</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79" t="s">
+        <v>17</v>
+      </c>
+      <c r="K79">
+        <v>22</v>
+      </c>
+      <c r="L79">
+        <v>1210.1500000000001</v>
+      </c>
+      <c r="M79">
+        <v>233</v>
+      </c>
+      <c r="N79">
+        <v>21</v>
+      </c>
+      <c r="O79">
+        <v>233</v>
+      </c>
+      <c r="P79">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B80">
+        <v>300064640</v>
+      </c>
+      <c r="C80" t="s">
+        <v>146</v>
+      </c>
+      <c r="D80">
+        <v>69</v>
+      </c>
+      <c r="E80">
+        <v>7</v>
+      </c>
+      <c r="F80">
+        <v>6</v>
+      </c>
+      <c r="G80" t="s">
+        <v>24</v>
+      </c>
+      <c r="H80" t="s">
+        <v>25</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80" t="s">
+        <v>17</v>
+      </c>
+      <c r="K80">
+        <v>9</v>
+      </c>
+      <c r="L80">
+        <v>5084.4198999999999</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>7</v>
+      </c>
+      <c r="P80">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B81">
+        <v>300064640</v>
+      </c>
+      <c r="C81" t="s">
+        <v>146</v>
+      </c>
+      <c r="D81">
+        <v>-69</v>
+      </c>
+      <c r="E81">
+        <v>-7</v>
+      </c>
+      <c r="F81">
+        <v>-6</v>
+      </c>
+      <c r="G81" t="s">
+        <v>136</v>
+      </c>
+      <c r="H81" t="s">
+        <v>143</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81" t="s">
+        <v>17</v>
+      </c>
+      <c r="K81">
+        <v>9</v>
+      </c>
+      <c r="L81">
+        <v>5084.4198999999999</v>
+      </c>
+      <c r="M81">
+        <v>7</v>
+      </c>
+      <c r="N81">
+        <v>6</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B82">
+        <v>300064641</v>
+      </c>
+      <c r="C82" t="s">
+        <v>96</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82" t="s">
+        <v>24</v>
+      </c>
+      <c r="H82" t="s">
+        <v>25</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82" t="s">
+        <v>17</v>
+      </c>
+      <c r="K82">
+        <v>22</v>
+      </c>
+      <c r="L82">
+        <v>1210.1500000000001</v>
+      </c>
+      <c r="M82">
+        <v>61</v>
+      </c>
+      <c r="N82">
+        <v>5</v>
+      </c>
+      <c r="O82">
+        <v>61</v>
+      </c>
+      <c r="P82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B83">
+        <v>300064740</v>
+      </c>
+      <c r="C83" t="s">
+        <v>97</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83" t="s">
+        <v>24</v>
+      </c>
+      <c r="H83" t="s">
+        <v>25</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83" t="s">
+        <v>17</v>
+      </c>
+      <c r="K83">
+        <v>9</v>
+      </c>
+      <c r="L83">
+        <v>5084.4198999999999</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B84">
+        <v>300064830</v>
+      </c>
+      <c r="C84" t="s">
+        <v>98</v>
+      </c>
+      <c r="D84">
+        <v>5</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>5</v>
+      </c>
+      <c r="G84" t="s">
+        <v>24</v>
+      </c>
+      <c r="H84" t="s">
+        <v>25</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84" t="s">
+        <v>17</v>
+      </c>
+      <c r="K84">
+        <v>25</v>
+      </c>
+      <c r="L84">
+        <v>1210.1500000000001</v>
+      </c>
+      <c r="M84">
+        <v>53</v>
+      </c>
+      <c r="N84">
+        <v>10</v>
+      </c>
+      <c r="O84">
+        <v>53</v>
+      </c>
+      <c r="P84">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B85">
+        <v>300064854</v>
+      </c>
+      <c r="C85" t="s">
+        <v>99</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85" t="s">
+        <v>24</v>
+      </c>
+      <c r="H85" t="s">
+        <v>25</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85" t="s">
+        <v>17</v>
+      </c>
+      <c r="K85">
+        <v>100</v>
+      </c>
+      <c r="L85">
+        <v>531.29</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>21</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B86">
+        <v>300064885</v>
+      </c>
+      <c r="C86" t="s">
+        <v>100</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86" t="s">
+        <v>24</v>
+      </c>
+      <c r="H86" t="s">
+        <v>25</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86" t="s">
+        <v>17</v>
+      </c>
+      <c r="K86">
+        <v>25</v>
+      </c>
+      <c r="L86">
+        <v>1611.5699</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B87">
+        <v>300064886</v>
+      </c>
+      <c r="C87" t="s">
+        <v>101</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87" t="s">
+        <v>24</v>
+      </c>
+      <c r="H87" t="s">
+        <v>25</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87" t="s">
+        <v>17</v>
+      </c>
+      <c r="K87">
+        <v>72</v>
+      </c>
+      <c r="L87">
+        <v>929.75</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B88">
+        <v>300064887</v>
+      </c>
+      <c r="C88" t="s">
+        <v>102</v>
+      </c>
+      <c r="D88">
+        <v>78</v>
+      </c>
+      <c r="E88">
+        <v>3</v>
+      </c>
+      <c r="F88">
+        <v>3</v>
+      </c>
+      <c r="G88" t="s">
+        <v>24</v>
+      </c>
+      <c r="H88" t="s">
+        <v>25</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88" t="s">
+        <v>17</v>
+      </c>
+      <c r="K88">
+        <v>25</v>
+      </c>
+      <c r="L88">
+        <v>1611.5699</v>
+      </c>
+      <c r="M88">
+        <v>36</v>
+      </c>
+      <c r="N88">
+        <v>23</v>
+      </c>
+      <c r="O88">
+        <v>40</v>
+      </c>
+      <c r="P88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B89">
+        <v>300064914</v>
+      </c>
+      <c r="C89" t="s">
+        <v>103</v>
+      </c>
+      <c r="D89">
+        <v>20</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>20</v>
+      </c>
+      <c r="G89" t="s">
+        <v>24</v>
+      </c>
+      <c r="H89" t="s">
+        <v>25</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89" t="s">
+        <v>17</v>
+      </c>
+      <c r="K89">
+        <v>38</v>
+      </c>
+      <c r="L89">
+        <v>1381.35</v>
+      </c>
+      <c r="M89">
+        <v>124</v>
+      </c>
+      <c r="N89">
+        <v>26</v>
+      </c>
+      <c r="O89">
+        <v>125</v>
+      </c>
+      <c r="P89">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B90">
+        <v>300064915</v>
+      </c>
+      <c r="C90" t="s">
+        <v>104</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90" t="s">
+        <v>24</v>
+      </c>
+      <c r="H90" t="s">
+        <v>25</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90" t="s">
+        <v>17</v>
+      </c>
+      <c r="K90">
+        <v>110</v>
+      </c>
+      <c r="L90">
+        <v>885.48</v>
+      </c>
+      <c r="M90">
+        <v>22</v>
+      </c>
+      <c r="N90">
+        <v>63</v>
+      </c>
+      <c r="O90">
+        <v>22</v>
+      </c>
+      <c r="P90">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B91">
+        <v>300065284</v>
+      </c>
+      <c r="C91" t="s">
+        <v>105</v>
+      </c>
+      <c r="D91">
+        <v>-12</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>-12</v>
+      </c>
+      <c r="G91" t="s">
+        <v>24</v>
+      </c>
+      <c r="H91" t="s">
+        <v>25</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91" t="s">
+        <v>17</v>
+      </c>
+      <c r="K91">
+        <v>25</v>
+      </c>
+      <c r="L91">
+        <v>1611.5699</v>
+      </c>
+      <c r="M91">
+        <v>64</v>
+      </c>
+      <c r="N91">
+        <v>21</v>
+      </c>
+      <c r="O91">
+        <v>64</v>
+      </c>
+      <c r="P91">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B92">
+        <v>300065285</v>
+      </c>
+      <c r="C92" t="s">
+        <v>106</v>
+      </c>
+      <c r="D92">
+        <v>15</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>15</v>
+      </c>
+      <c r="G92" t="s">
+        <v>24</v>
+      </c>
+      <c r="H92" t="s">
+        <v>25</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92" t="s">
+        <v>17</v>
+      </c>
+      <c r="K92">
+        <v>25</v>
+      </c>
+      <c r="L92">
+        <v>1611.5699</v>
+      </c>
+      <c r="M92">
+        <v>118</v>
+      </c>
+      <c r="N92">
+        <v>13</v>
+      </c>
+      <c r="O92">
+        <v>119</v>
+      </c>
+      <c r="P92">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B93">
+        <v>300065286</v>
+      </c>
+      <c r="C93" t="s">
+        <v>107</v>
+      </c>
+      <c r="D93">
+        <v>2</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>2</v>
+      </c>
+      <c r="G93" t="s">
+        <v>24</v>
+      </c>
+      <c r="H93" t="s">
+        <v>25</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93" t="s">
+        <v>17</v>
+      </c>
+      <c r="K93">
+        <v>25</v>
+      </c>
+      <c r="L93">
+        <v>1611.5699</v>
+      </c>
+      <c r="M93">
+        <v>346</v>
+      </c>
+      <c r="N93">
+        <v>15</v>
+      </c>
+      <c r="O93">
+        <v>346</v>
+      </c>
+      <c r="P93">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B94">
+        <v>300065287</v>
+      </c>
+      <c r="C94" t="s">
+        <v>108</v>
+      </c>
+      <c r="D94">
+        <v>-25</v>
+      </c>
+      <c r="E94">
+        <v>-1</v>
+      </c>
+      <c r="F94">
+        <v>-7</v>
+      </c>
+      <c r="G94" t="s">
+        <v>24</v>
+      </c>
+      <c r="H94" t="s">
+        <v>25</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94" t="s">
+        <v>17</v>
+      </c>
+      <c r="K94">
+        <v>18</v>
+      </c>
+      <c r="L94">
+        <v>2662.3400999999999</v>
+      </c>
+      <c r="M94">
+        <v>338</v>
+      </c>
+      <c r="N94">
+        <v>14</v>
+      </c>
+      <c r="O94">
+        <v>337</v>
+      </c>
+      <c r="P94">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B95">
+        <v>300065313</v>
+      </c>
+      <c r="C95" t="s">
+        <v>109</v>
+      </c>
+      <c r="D95">
+        <v>8</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>8</v>
+      </c>
+      <c r="G95" t="s">
+        <v>24</v>
+      </c>
+      <c r="H95" t="s">
+        <v>25</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95" t="s">
+        <v>17</v>
+      </c>
+      <c r="K95">
+        <v>13</v>
+      </c>
+      <c r="L95">
+        <v>3872.49</v>
+      </c>
+      <c r="M95">
+        <v>85</v>
+      </c>
+      <c r="N95">
+        <v>2</v>
+      </c>
+      <c r="O95">
+        <v>85</v>
+      </c>
+      <c r="P95">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B96">
+        <v>300065361</v>
+      </c>
+      <c r="C96" t="s">
+        <v>110</v>
+      </c>
+      <c r="D96">
+        <v>-10</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>-10</v>
+      </c>
+      <c r="G96" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" t="s">
+        <v>25</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96" t="s">
+        <v>17</v>
+      </c>
+      <c r="K96">
+        <v>25</v>
+      </c>
+      <c r="L96">
+        <v>1611.5699</v>
+      </c>
+      <c r="M96">
+        <v>321</v>
+      </c>
+      <c r="N96">
+        <v>21</v>
+      </c>
+      <c r="O96">
+        <v>321</v>
+      </c>
+      <c r="P96">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B97">
+        <v>300065476</v>
+      </c>
+      <c r="C97" t="s">
+        <v>111</v>
+      </c>
+      <c r="D97">
+        <v>-10</v>
+      </c>
+      <c r="E97">
+        <v>-1</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97" t="s">
+        <v>24</v>
+      </c>
+      <c r="H97" t="s">
+        <v>25</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97" t="s">
+        <v>17</v>
+      </c>
+      <c r="K97">
+        <v>10</v>
+      </c>
+      <c r="L97">
+        <v>3187.72</v>
+      </c>
+      <c r="M97">
+        <v>15</v>
+      </c>
+      <c r="N97">
+        <v>4</v>
+      </c>
+      <c r="O97">
+        <v>14</v>
+      </c>
+      <c r="P97">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B98">
+        <v>300065477</v>
+      </c>
+      <c r="C98" t="s">
+        <v>112</v>
+      </c>
+      <c r="D98">
+        <v>-2</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>-2</v>
+      </c>
+      <c r="G98" t="s">
+        <v>24</v>
+      </c>
+      <c r="H98" t="s">
+        <v>25</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98" t="s">
+        <v>17</v>
+      </c>
+      <c r="K98">
+        <v>10</v>
+      </c>
+      <c r="L98">
+        <v>3187.72</v>
+      </c>
+      <c r="M98">
+        <v>10</v>
+      </c>
+      <c r="N98">
+        <v>8</v>
+      </c>
+      <c r="O98">
+        <v>10</v>
+      </c>
+      <c r="P98">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B99">
+        <v>300065501</v>
+      </c>
+      <c r="C99" t="s">
+        <v>113</v>
+      </c>
+      <c r="D99">
+        <v>-108</v>
+      </c>
+      <c r="E99">
+        <v>-3</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99" t="s">
+        <v>24</v>
+      </c>
+      <c r="H99" t="s">
+        <v>25</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99" t="s">
+        <v>17</v>
+      </c>
+      <c r="K99">
+        <v>36</v>
+      </c>
+      <c r="L99">
+        <v>929.75</v>
+      </c>
+      <c r="M99">
+        <v>25</v>
+      </c>
+      <c r="N99">
+        <v>26</v>
+      </c>
+      <c r="O99">
+        <v>22</v>
+      </c>
+      <c r="P99">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B100">
+        <v>300065572</v>
+      </c>
+      <c r="C100" t="s">
+        <v>114</v>
+      </c>
+      <c r="D100">
+        <v>-71</v>
+      </c>
+      <c r="E100">
+        <v>-5</v>
+      </c>
+      <c r="F100">
+        <v>-11</v>
+      </c>
+      <c r="G100" t="s">
+        <v>24</v>
+      </c>
+      <c r="H100" t="s">
+        <v>25</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100" t="s">
+        <v>17</v>
+      </c>
+      <c r="K100">
+        <v>12</v>
+      </c>
+      <c r="L100">
+        <v>1815.23</v>
+      </c>
+      <c r="M100">
+        <v>30</v>
+      </c>
+      <c r="N100">
+        <v>4</v>
+      </c>
+      <c r="O100">
+        <v>24</v>
+      </c>
+      <c r="P100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B101">
+        <v>300065610</v>
+      </c>
+      <c r="C101" t="s">
+        <v>115</v>
+      </c>
+      <c r="D101">
+        <v>2</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>2</v>
+      </c>
+      <c r="G101" t="s">
+        <v>24</v>
+      </c>
+      <c r="H101" t="s">
+        <v>25</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101" t="s">
+        <v>17</v>
+      </c>
+      <c r="K101">
+        <v>12</v>
+      </c>
+      <c r="L101">
+        <v>1815.23</v>
+      </c>
+      <c r="M101">
+        <v>16</v>
+      </c>
+      <c r="N101">
+        <v>10</v>
+      </c>
+      <c r="O101">
+        <v>17</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B102">
+        <v>300065611</v>
+      </c>
+      <c r="C102" t="s">
+        <v>116</v>
+      </c>
+      <c r="D102">
+        <v>-33</v>
+      </c>
+      <c r="E102">
+        <v>-1</v>
+      </c>
+      <c r="F102">
+        <v>-13</v>
+      </c>
+      <c r="G102" t="s">
+        <v>24</v>
+      </c>
+      <c r="H102" t="s">
+        <v>25</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102" t="s">
+        <v>17</v>
+      </c>
+      <c r="K102">
+        <v>20</v>
+      </c>
+      <c r="L102">
+        <v>1113.3399999999999</v>
+      </c>
+      <c r="M102">
+        <v>38</v>
+      </c>
+      <c r="N102">
+        <v>9</v>
+      </c>
+      <c r="O102">
+        <v>36</v>
+      </c>
+      <c r="P102">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B103">
+        <v>300065612</v>
+      </c>
+      <c r="C103" t="s">
+        <v>117</v>
+      </c>
+      <c r="D103">
+        <v>7</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>7</v>
+      </c>
+      <c r="G103" t="s">
+        <v>24</v>
+      </c>
+      <c r="H103" t="s">
+        <v>25</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103" t="s">
+        <v>17</v>
+      </c>
+      <c r="K103">
+        <v>10</v>
+      </c>
+      <c r="L103">
+        <v>1815.23</v>
+      </c>
+      <c r="M103">
+        <v>60</v>
+      </c>
+      <c r="N103">
+        <v>4</v>
+      </c>
+      <c r="O103">
+        <v>61</v>
+      </c>
+      <c r="P103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B104">
+        <v>300065613</v>
+      </c>
+      <c r="C104" t="s">
+        <v>118</v>
+      </c>
+      <c r="D104">
+        <v>-13</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>-13</v>
+      </c>
+      <c r="G104" t="s">
+        <v>24</v>
+      </c>
+      <c r="H104" t="s">
+        <v>25</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104" t="s">
+        <v>17</v>
+      </c>
+      <c r="K104">
+        <v>20</v>
+      </c>
+      <c r="L104">
+        <v>1113.3399999999999</v>
+      </c>
+      <c r="M104">
+        <v>80</v>
+      </c>
+      <c r="N104">
+        <v>17</v>
+      </c>
+      <c r="O104">
+        <v>80</v>
+      </c>
+      <c r="P104">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B105">
+        <v>300065792</v>
+      </c>
+      <c r="C105" t="s">
+        <v>119</v>
+      </c>
+      <c r="D105">
+        <v>-17</v>
+      </c>
+      <c r="E105">
+        <v>-1</v>
+      </c>
+      <c r="F105">
+        <v>-2</v>
+      </c>
+      <c r="G105" t="s">
+        <v>24</v>
+      </c>
+      <c r="H105" t="s">
+        <v>25</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105" t="s">
+        <v>17</v>
+      </c>
+      <c r="K105">
+        <v>15</v>
+      </c>
+      <c r="L105">
+        <v>3146.3998999999999</v>
+      </c>
+      <c r="M105">
+        <v>14</v>
+      </c>
+      <c r="N105">
+        <v>14</v>
+      </c>
+      <c r="O105">
+        <v>13</v>
+      </c>
+      <c r="P105">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B106">
+        <v>300065825</v>
+      </c>
+      <c r="C106" t="s">
+        <v>120</v>
+      </c>
+      <c r="D106">
+        <v>-9</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>-9</v>
+      </c>
+      <c r="G106" t="s">
+        <v>24</v>
+      </c>
+      <c r="H106" t="s">
+        <v>25</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106" t="s">
+        <v>17</v>
+      </c>
+      <c r="K106">
+        <v>24</v>
+      </c>
+      <c r="L106">
+        <v>1611.5699</v>
+      </c>
+      <c r="M106">
+        <v>115</v>
+      </c>
+      <c r="N106">
+        <v>11</v>
+      </c>
+      <c r="O106">
+        <v>115</v>
+      </c>
+      <c r="P106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B107">
+        <v>300065826</v>
+      </c>
+      <c r="C107" t="s">
+        <v>121</v>
+      </c>
+      <c r="D107">
+        <v>15</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>15</v>
+      </c>
+      <c r="G107" t="s">
+        <v>24</v>
+      </c>
+      <c r="H107" t="s">
+        <v>25</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107" t="s">
+        <v>17</v>
+      </c>
+      <c r="K107">
+        <v>66</v>
+      </c>
+      <c r="L107">
+        <v>929.75</v>
+      </c>
+      <c r="M107">
+        <v>23</v>
+      </c>
+      <c r="N107">
+        <v>57</v>
+      </c>
+      <c r="O107">
+        <v>24</v>
+      </c>
+      <c r="P107">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B108">
+        <v>300065827</v>
+      </c>
+      <c r="C108" t="s">
+        <v>122</v>
+      </c>
+      <c r="D108">
+        <v>9</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>9</v>
+      </c>
+      <c r="G108" t="s">
+        <v>24</v>
+      </c>
+      <c r="H108" t="s">
+        <v>25</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108" t="s">
+        <v>17</v>
+      </c>
+      <c r="K108">
+        <v>19</v>
+      </c>
+      <c r="L108">
+        <v>2662.3400999999999</v>
+      </c>
+      <c r="M108">
+        <v>29</v>
+      </c>
+      <c r="N108">
+        <v>2</v>
+      </c>
+      <c r="O108">
+        <v>29</v>
+      </c>
+      <c r="P108">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B109">
+        <v>300065828</v>
+      </c>
+      <c r="C109" t="s">
+        <v>123</v>
+      </c>
+      <c r="D109">
+        <v>17</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>17</v>
+      </c>
+      <c r="G109" t="s">
+        <v>24</v>
+      </c>
+      <c r="H109" t="s">
+        <v>25</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109" t="s">
+        <v>17</v>
+      </c>
+      <c r="K109">
+        <v>26</v>
+      </c>
+      <c r="L109">
+        <v>1611.5699</v>
+      </c>
+      <c r="M109">
+        <v>57</v>
+      </c>
+      <c r="N109">
+        <v>9</v>
+      </c>
+      <c r="O109">
+        <v>58</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B110">
+        <v>300066261</v>
+      </c>
+      <c r="C110" t="s">
+        <v>124</v>
+      </c>
+      <c r="D110">
+        <v>14</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>14</v>
+      </c>
+      <c r="G110" t="s">
+        <v>24</v>
+      </c>
+      <c r="H110" t="s">
+        <v>25</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110" t="s">
+        <v>17</v>
+      </c>
+      <c r="K110">
+        <v>29</v>
+      </c>
+      <c r="L110">
+        <v>1611.5699</v>
+      </c>
+      <c r="M110">
+        <v>295</v>
+      </c>
+      <c r="N110">
+        <v>16</v>
+      </c>
+      <c r="O110">
+        <v>296</v>
+      </c>
+      <c r="P110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B111">
+        <v>300066262</v>
+      </c>
+      <c r="C111" t="s">
+        <v>125</v>
+      </c>
+      <c r="D111">
+        <v>4</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>4</v>
+      </c>
+      <c r="G111" t="s">
+        <v>24</v>
+      </c>
+      <c r="H111" t="s">
+        <v>25</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111" t="s">
+        <v>17</v>
+      </c>
+      <c r="K111">
+        <v>88</v>
+      </c>
+      <c r="L111">
+        <v>929.75</v>
+      </c>
+      <c r="M111">
+        <v>8</v>
+      </c>
+      <c r="N111">
+        <v>4</v>
+      </c>
+      <c r="O111">
+        <v>8</v>
+      </c>
+      <c r="P111">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B112">
+        <v>300066500</v>
+      </c>
+      <c r="C112" t="s">
+        <v>126</v>
+      </c>
+      <c r="D112">
+        <v>8</v>
+      </c>
+      <c r="E112">
+        <v>1</v>
+      </c>
+      <c r="F112">
+        <v>2</v>
+      </c>
+      <c r="G112" t="s">
+        <v>24</v>
+      </c>
+      <c r="H112" t="s">
+        <v>25</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112" t="s">
+        <v>17</v>
+      </c>
+      <c r="K112">
+        <v>6</v>
+      </c>
+      <c r="L112">
+        <v>9297.5195000000003</v>
+      </c>
+      <c r="M112">
+        <v>10</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>11</v>
+      </c>
+      <c r="P112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B113">
+        <v>300066580</v>
+      </c>
+      <c r="C113" t="s">
+        <v>127</v>
+      </c>
+      <c r="D113">
+        <v>-14</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>-14</v>
+      </c>
+      <c r="G113" t="s">
+        <v>24</v>
+      </c>
+      <c r="H113" t="s">
+        <v>25</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113" t="s">
+        <v>17</v>
+      </c>
+      <c r="K113">
+        <v>25</v>
+      </c>
+      <c r="L113">
+        <v>1611.5699</v>
+      </c>
+      <c r="M113">
+        <v>278</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>277</v>
+      </c>
+      <c r="P113">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B114">
+        <v>300066581</v>
+      </c>
+      <c r="C114" t="s">
+        <v>128</v>
+      </c>
+      <c r="D114">
+        <v>-1230</v>
+      </c>
+      <c r="E114">
+        <v>-17</v>
+      </c>
+      <c r="F114">
+        <v>-6</v>
+      </c>
+      <c r="G114" t="s">
+        <v>19</v>
+      </c>
+      <c r="H114" t="s">
+        <v>129</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114" t="s">
+        <v>17</v>
+      </c>
+      <c r="K114">
+        <v>72</v>
+      </c>
+      <c r="L114">
+        <v>929.75</v>
+      </c>
+      <c r="M114">
+        <v>22</v>
+      </c>
+      <c r="N114">
+        <v>18</v>
+      </c>
+      <c r="O114">
+        <v>5</v>
+      </c>
+      <c r="P114">
+        <v>12</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B115">
+        <v>300066581</v>
+      </c>
+      <c r="C115" t="s">
+        <v>128</v>
+      </c>
+      <c r="D115">
+        <v>1230</v>
+      </c>
+      <c r="E115">
+        <v>17</v>
+      </c>
+      <c r="F115">
+        <v>6</v>
+      </c>
+      <c r="G115" t="s">
+        <v>19</v>
+      </c>
+      <c r="H115" t="s">
+        <v>129</v>
+      </c>
+      <c r="I115">
+        <v>3</v>
+      </c>
+      <c r="J115" t="s">
+        <v>131</v>
+      </c>
+      <c r="K115">
+        <v>72</v>
+      </c>
+      <c r="L115">
+        <v>929.75</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>17</v>
+      </c>
+      <c r="P115">
+        <v>6</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B116">
+        <v>300066581</v>
+      </c>
+      <c r="C116" t="s">
+        <v>128</v>
+      </c>
+      <c r="D116">
+        <v>-55</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>-55</v>
+      </c>
+      <c r="G116" t="s">
+        <v>24</v>
+      </c>
+      <c r="H116" t="s">
+        <v>25</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116" t="s">
+        <v>17</v>
+      </c>
+      <c r="K116">
+        <v>72</v>
+      </c>
+      <c r="L116">
+        <v>929.75</v>
+      </c>
+      <c r="M116">
+        <v>4</v>
+      </c>
+      <c r="N116">
+        <v>61</v>
+      </c>
+      <c r="O116">
+        <v>4</v>
+      </c>
+      <c r="P116">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B117">
+        <v>300066581</v>
+      </c>
+      <c r="C117" t="s">
+        <v>128</v>
+      </c>
+      <c r="D117">
+        <v>-144</v>
+      </c>
+      <c r="E117">
+        <v>-2</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117" t="s">
+        <v>19</v>
+      </c>
+      <c r="H117" t="s">
+        <v>129</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117" t="s">
+        <v>17</v>
+      </c>
+      <c r="K117">
+        <v>72</v>
+      </c>
+      <c r="L117">
+        <v>929.75</v>
+      </c>
+      <c r="M117">
+        <v>4</v>
+      </c>
+      <c r="N117">
+        <v>6</v>
+      </c>
+      <c r="O117">
+        <v>2</v>
+      </c>
+      <c r="P117">
+        <v>6</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B118">
+        <v>300066581</v>
+      </c>
+      <c r="C118" t="s">
+        <v>128</v>
+      </c>
+      <c r="D118">
+        <v>144</v>
+      </c>
+      <c r="E118">
+        <v>2</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118" t="s">
+        <v>19</v>
+      </c>
+      <c r="H118" t="s">
+        <v>129</v>
+      </c>
+      <c r="I118">
+        <v>3</v>
+      </c>
+      <c r="J118" t="s">
+        <v>131</v>
+      </c>
+      <c r="K118">
+        <v>72</v>
+      </c>
+      <c r="L118">
+        <v>929.75</v>
+      </c>
+      <c r="M118">
+        <v>17</v>
+      </c>
+      <c r="N118">
+        <v>6</v>
+      </c>
+      <c r="O118">
+        <v>19</v>
+      </c>
+      <c r="P118">
+        <v>6</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B119">
+        <v>300066598</v>
+      </c>
+      <c r="C119" t="s">
+        <v>132</v>
+      </c>
+      <c r="D119">
+        <v>3</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>3</v>
+      </c>
+      <c r="G119" t="s">
+        <v>24</v>
+      </c>
+      <c r="H119" t="s">
+        <v>25</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119" t="s">
+        <v>17</v>
+      </c>
+      <c r="K119">
+        <v>6</v>
+      </c>
+      <c r="L119">
+        <v>9297.5195000000003</v>
+      </c>
+      <c r="M119">
+        <v>6</v>
+      </c>
+      <c r="N119">
+        <v>1</v>
+      </c>
+      <c r="O119">
+        <v>6</v>
+      </c>
+      <c r="P119">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B120">
+        <v>300066790</v>
+      </c>
+      <c r="C120" t="s">
+        <v>133</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120" t="s">
+        <v>24</v>
+      </c>
+      <c r="H120" t="s">
+        <v>25</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120" t="s">
+        <v>17</v>
+      </c>
+      <c r="K120">
+        <v>9</v>
+      </c>
+      <c r="L120">
+        <v>5084.4198999999999</v>
+      </c>
+      <c r="M120">
+        <v>35</v>
+      </c>
+      <c r="N120">
+        <v>6</v>
+      </c>
+      <c r="O120">
+        <v>35</v>
+      </c>
+      <c r="P120">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B121">
+        <v>300066791</v>
+      </c>
+      <c r="C121" t="s">
+        <v>134</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121" t="s">
+        <v>24</v>
+      </c>
+      <c r="H121" t="s">
+        <v>25</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121" t="s">
+        <v>17</v>
+      </c>
+      <c r="K121">
+        <v>9</v>
+      </c>
+      <c r="L121">
+        <v>5084.4198999999999</v>
+      </c>
+      <c r="M121">
+        <v>901</v>
+      </c>
+      <c r="N121">
+        <v>1</v>
+      </c>
+      <c r="O121">
+        <v>901</v>
+      </c>
+      <c r="P121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
@@ -3226,16 +9295,12 @@
     <row r="912" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A912" s="1"/>
     </row>
-    <row r="913" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A913" s="1"/>
-    </row>
-    <row r="914" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A914" s="1"/>
-    </row>
-    <row r="915" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A915" s="1"/>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:Q112" xr:uid="{D5D248C6-4721-43B8-8122-45E55855FA17}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q112">
+      <sortCondition ref="D1:D112"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/movimientos.xlsx
+++ b/data/movimientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCCD757-AEB2-404B-9080-CEEBF655825F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8A3EBD-8E53-49F4-9E46-3E15396AA6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{99072C7C-E32F-4A2F-800E-3105C8F1D176}"/>
   </bookViews>
@@ -1415,7 +1415,7 @@
         <v>30</v>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12">
         <v>0</v>

--- a/data/movimientos.xlsx
+++ b/data/movimientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8A3EBD-8E53-49F4-9E46-3E15396AA6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E300A5-4324-4FAE-BEF2-D08EF8C5F14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{99072C7C-E32F-4A2F-800E-3105C8F1D176}"/>
   </bookViews>
@@ -1365,7 +1365,7 @@
         <v>29</v>
       </c>
       <c r="D11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11">
         <v>0</v>
